--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C22"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -645,9 +645,21 @@
 엑셀(UpdateLog.xlsx) 기반으로 업데이트 로그를 관리하고 자동 반영</v>
       </c>
     </row>
+    <row r="22" xml:space="preserve">
+      <c r="A22" t="str">
+        <v>v0.5.1</v>
+      </c>
+      <c r="B22" t="str">
+        <v>2026-07-02</v>
+      </c>
+      <c r="C22" t="str" xml:space="preserve">
+        <v xml:space="preserve">필터 라벨(수감자/성급/키워드/소속)에 아이콘 추가하고 글씨 크게 강조
+필터 그룹이 세 줄로 나뉘던 문제 수정, 한 줄에 표시되도록 개선</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C22"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C23"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -657,9 +657,20 @@
 필터 그룹이 세 줄로 나뉘던 문제 수정, 한 줄에 표시되도록 개선</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>v0.5.2</v>
+      </c>
+      <c r="B23" t="str">
+        <v>2026-07-02</v>
+      </c>
+      <c r="C23" t="str">
+        <v>정답 공개, 스킬 퀴즈, 결과 카드에서 각성 이미지를 기본으로 표시하도록 변경 (각성 이미지가 없으면 일반 이미지로 대체)</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C22"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C23"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C24"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -668,9 +668,20 @@
         <v>정답 공개, 스킬 퀴즈, 결과 카드에서 각성 이미지를 기본으로 표시하도록 변경 (각성 이미지가 없으면 일반 이미지로 대체)</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>v0.5.3</v>
+      </c>
+      <c r="B24" t="str">
+        <v>2026-07-02</v>
+      </c>
+      <c r="C24" t="str">
+        <v>CharacterTable.xlsx 스킬1/2/3 정보(명칭·속성·유형·아이콘) 최신화 반영</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C23"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C24"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C25"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -679,9 +679,20 @@
         <v>CharacterTable.xlsx 스킬1/2/3 정보(명칭·속성·유형·아이콘) 최신화 반영</v>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>v0.5.4</v>
+      </c>
+      <c r="B25" t="str">
+        <v>2026-07-02</v>
+      </c>
+      <c r="C25" t="str">
+        <v>스킬 퀴즈 스테이지1에 스킬별 힌트 보기 / 정답 보기 버튼 추가</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C24"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C25"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C26"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -690,9 +690,20 @@
         <v>스킬 퀴즈 스테이지1에 스킬별 힌트 보기 / 정답 보기 버튼 추가</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>v0.5.5</v>
+      </c>
+      <c r="B26" t="str">
+        <v>2026-07-02</v>
+      </c>
+      <c r="C26" t="str">
+        <v>스킬 퀴즈 인격 이미지가 잘리던 문제 수정 (object-fit: cover → contain)</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C25"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C26"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C27"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -701,9 +701,20 @@
         <v>스킬 퀴즈 인격 이미지가 잘리던 문제 수정 (object-fit: cover → contain)</v>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>v0.5.6</v>
+      </c>
+      <c r="B27" t="str">
+        <v>2026-07-02</v>
+      </c>
+      <c r="C27" t="str">
+        <v>스킬 퀴즈 인격 이미지를 카드 상단 전체 폭으로 크게 확대 (520px)</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C26"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C27"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C28"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -712,9 +712,22 @@
         <v>스킬 퀴즈 인격 이미지를 카드 상단 전체 폭으로 크게 확대 (520px)</v>
       </c>
     </row>
+    <row r="28" xml:space="preserve">
+      <c r="A28" t="str">
+        <v>v0.6.0</v>
+      </c>
+      <c r="B28" t="str">
+        <v>2026-07-02</v>
+      </c>
+      <c r="C28" t="str" xml:space="preserve">
+        <v xml:space="preserve">스킬 퀴즈 스테이지1에 포기하기 버튼 추가 (제출 왼쪽 배치)
+포기 시 이미 맞힌 속성/유형은 유지하고 틀리거나 미선택한 항목만 정답으로 채움
+결과 화면에 스킬별로 직접 맞힌 항목과 포기한 항목을 배지로 구분 표시, 전체 정답률 통계 추가</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C27"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C28"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C29"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -725,9 +725,21 @@
 결과 화면에 스킬별로 직접 맞힌 항목과 포기한 항목을 배지로 구분 표시, 전체 정답률 통계 추가</v>
       </c>
     </row>
+    <row r="29" xml:space="preserve">
+      <c r="A29" t="str">
+        <v>v0.6.1</v>
+      </c>
+      <c r="B29" t="str">
+        <v>2026-07-02</v>
+      </c>
+      <c r="C29" t="str" xml:space="preserve">
+        <v xml:space="preserve">인격 두들 정답 공개를 카드형 레이아웃으로 재구성
+인격명 카드는 수감자 컬러로 강조, 키워드는 색상 칩으로 표시</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C28"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C29"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C30"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -737,9 +737,21 @@
 인격명 카드는 수감자 컬러로 강조, 키워드는 색상 칩으로 표시</v>
       </c>
     </row>
+    <row r="30" xml:space="preserve">
+      <c r="A30" t="str">
+        <v>v0.6.2</v>
+      </c>
+      <c r="B30" t="str">
+        <v>2026-07-02</v>
+      </c>
+      <c r="C30" t="str" xml:space="preserve">
+        <v xml:space="preserve">CharacterTable.xlsx 이미지 URL 최신화 반영 (인격 이미지, 프로필, 스킬 아이콘)
+스킬1/2/3 아이콘이 동일하게 나오던 64개 인격 문제도 함께 해결됨</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C29"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C30"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C31"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -749,9 +749,23 @@
 스킬1/2/3 아이콘이 동일하게 나오던 64개 인격 문제도 함께 해결됨</v>
       </c>
     </row>
+    <row r="31" xml:space="preserve">
+      <c r="A31" t="str">
+        <v>v0.7.0</v>
+      </c>
+      <c r="B31" t="str">
+        <v>2026-07-06</v>
+      </c>
+      <c r="C31" t="str" xml:space="preserve">
+        <v xml:space="preserve">덱 빌더 게임 신규 추가
+추천덱(엑셀 추천덱 시트)의 빈 슬롯에 인격을 드래그(또는 탭)해서 배치하는 게임
+워들 스타일 3색 판정(초록/노랑/빨강), 핵심/일반 슬롯 구분, 정답 보기 기능 지원
+데스크톱 드래그앤드롭과 모바일 탭-투-배치 모두 지원</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C30"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C31"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C32"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -763,9 +763,22 @@
 데스크톱 드래그앤드롭과 모바일 탭-투-배치 모두 지원</v>
       </c>
     </row>
+    <row r="32" xml:space="preserve">
+      <c r="A32" t="str">
+        <v>v0.7.1</v>
+      </c>
+      <c r="B32" t="str">
+        <v>2026-07-06</v>
+      </c>
+      <c r="C32" t="str" xml:space="preserve">
+        <v xml:space="preserve">결과 카드에 정답 가리기(스포일러 방지) 토글 추가, 오늘의 인격은 기본으로 가려짐
+이미지 저장 시 CORS 문제로 인격 이미지가 비어보이던 버그 수정 (프록시 경유)
+클립보드에 카드 이미지를 바로 복사하는 기능 추가</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C32"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C33"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -776,9 +776,21 @@
 클립보드에 카드 이미지를 바로 복사하는 기능 추가</v>
       </c>
     </row>
+    <row r="33" xml:space="preserve">
+      <c r="A33" t="str">
+        <v>v0.7.2</v>
+      </c>
+      <c r="B33" t="str">
+        <v>2026-07-06</v>
+      </c>
+      <c r="C33" t="str" xml:space="preserve">
+        <v xml:space="preserve">정답 가리기를 블러 대신 완전 비활성화(불투명 커버)로 변경
+가리기 상태에서 소속/키워드 정보도 함께 숨김 처리</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C32"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C33"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C34"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -788,9 +788,24 @@
 가리기 상태에서 소속/키워드 정보도 함께 숨김 처리</v>
       </c>
     </row>
+    <row r="34" xml:space="preserve">
+      <c r="A34" t="str">
+        <v>v0.8.0</v>
+      </c>
+      <c r="B34" t="str">
+        <v>2026-07-06</v>
+      </c>
+      <c r="C34" t="str" xml:space="preserve">
+        <v xml:space="preserve">덱 빌더 게임을 완전히 새로 설계 (DeckData 시트 기반 2단계 게임)
+1단계: 수감자 12칸에 인격 배치(Main/Sub는 정답 인격, Null은 없음)
+2단계: 1단계 통과 후 Main 인격들의 전투 순서를 워들 스타일로 맞추기
+덱href 기준으로 그룹핑, ID 개수를 하드코딩하지 않고 동적으로 로드
+정답 보기(포기), 검색 필터, 드래그 앤 드롭+탭 배치 지원</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C33"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C34"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C35"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -803,9 +803,26 @@
 정답 보기(포기), 검색 필터, 드래그 앤 드롭+탭 배치 지원</v>
       </c>
     </row>
+    <row r="35" xml:space="preserve">
+      <c r="A35" t="str">
+        <v>v0.9.0</v>
+      </c>
+      <c r="B35" t="str">
+        <v>2026-07-06</v>
+      </c>
+      <c r="C35" t="str" xml:space="preserve">
+        <v xml:space="preserve">덱 빌더: DeckData 시트 업데이트 반영 (이름 매칭 문제 모두 해결됨)
+수감자 배치를 6x2 그리드로 변경
+인격 후보 목록에 수감자별 필터 탭 추가
+후보 카드 이미지를 4열 배치로 확대
+버그 수정: 이제 각 자리에는 그 수감자의 인격만 배치 가능
+인격 카드 더블클릭으로 자동 배치 지원 (보드 우선, 없으면 순서 칸)
+1단계(수감자 배치)와 2단계(전투 순서)를 한 화면으로 통합</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C34"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C35"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C36"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -820,9 +820,23 @@
 1단계(수감자 배치)와 2단계(전투 순서)를 한 화면으로 통합</v>
       </c>
     </row>
+    <row r="36" xml:space="preserve">
+      <c r="A36" t="str">
+        <v>v0.10.0</v>
+      </c>
+      <c r="B36" t="str">
+        <v>2026-07-06</v>
+      </c>
+      <c r="C36" t="str" xml:space="preserve">
+        <v xml:space="preserve">덱 빌더 게임 구조 재설계: 수감자별 고정 12칸 + 별도 순서칸을 없애고, 순서만 있는 통합 12칸 하나로 변경
+인격을 더블클릭(모바일은 탭)하면 가장 빠른 빈 칸에 자동 배치, 드래그로 자유롭게 순서 재배치 가능
+버그 수정: 더블클릭 미작동, 정답 덱 이름/설명이 화면에 노출되던 스포일러 문제, 빈 칸이 있어도 제출되던 문제 모두 해결
+같은 수감자 중복 배치 방지(없음 카드는 예외), 12칸을 모두 채워야 제출 버튼 활성화</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C35"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C36"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C37"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -834,9 +834,21 @@
 같은 수감자 중복 배치 방지(없음 카드는 예외), 12칸을 모두 채워야 제출 버튼 활성화</v>
       </c>
     </row>
+    <row r="37" xml:space="preserve">
+      <c r="A37" t="str">
+        <v>v0.10.1</v>
+      </c>
+      <c r="B37" t="str">
+        <v>2026-07-06</v>
+      </c>
+      <c r="C37" t="str" xml:space="preserve">
+        <v xml:space="preserve">덱 빌더: "없음" 카드를 수감자별로 분리해 어떤 수감자를 없음으로 표시했는지 명확히 보여줌
+예: "없음" -&gt; "돈키호테 없음" 처럼 표시. 다른 수감자의 없음과 구분되고, 같은 수감자 중복 배치 방지 규칙도 없음 카드에 동일하게 적용됨</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C36"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C37"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C38"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -846,9 +846,25 @@
 예: "없음" -&gt; "돈키호테 없음" 처럼 표시. 다른 수감자의 없음과 구분되고, 같은 수감자 중복 배치 방지 규칙도 없음 카드에 동일하게 적용됨</v>
       </c>
     </row>
+    <row r="38" xml:space="preserve">
+      <c r="A38" t="str">
+        <v>v0.11.0</v>
+      </c>
+      <c r="B38" t="str">
+        <v>2026-07-06</v>
+      </c>
+      <c r="C38" t="str" xml:space="preserve">
+        <v xml:space="preserve">덱 빌더: 후보 목록에서 이미 배치된 인격에 "체크 배치됨" 배지 표시
+전체 필터 탭 제거 (수감자별 탭만 남김)
+이미 배치된 수감자의 인격을 더블클릭하면 거부하지 않고 그 자리에 교체 배치
+상단에 "모두 비우기" 버튼 추가
+중간 슬롯 제거 시 뒤 슬롯들이 앞으로 당겨지도록 변경
+제출 후 정답(초록)인 슬롯은 고정되어 계속 유지되고, 순서만 틀린(노랑)/오답(빨강) 인격은 후보 목록에 다시 넣어도 표시가 남도록 변경, 오답은 이미지에 X 표시</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C37"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C38"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C38"/>
+  <dimension ref="A1:C40"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -862,9 +862,31 @@
 제출 후 정답(초록)인 슬롯은 고정되어 계속 유지되고, 순서만 틀린(노랑)/오답(빨강) 인격은 후보 목록에 다시 넣어도 표시가 남도록 변경, 오답은 이미지에 X 표시</v>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>v0.11.1</v>
+      </c>
+      <c r="B39" t="str">
+        <v>2026-07-06</v>
+      </c>
+      <c r="C39" t="str">
+        <v>덱 빌더: 후보 목록에서 "없음" 카드가 각 수감자 탭에서 항상 맨 앞에 오도록 정렬</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>v0.11.2</v>
+      </c>
+      <c r="B40" t="str">
+        <v>2026-07-06</v>
+      </c>
+      <c r="C40" t="str">
+        <v>덱 빌더: 수감자 필터 탭에 이미 배치된 수감자를 체크 표시(✓)와 초록 테두리로 표시</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C38"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C40"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C40"/>
+  <dimension ref="A1:C41"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -884,9 +884,24 @@
         <v>덱 빌더: 수감자 필터 탭에 이미 배치된 수감자를 체크 표시(✓)와 초록 테두리로 표시</v>
       </c>
     </row>
+    <row r="41" xml:space="preserve">
+      <c r="A41" t="str">
+        <v>v0.12.0</v>
+      </c>
+      <c r="B41" t="str">
+        <v>2026-07-06</v>
+      </c>
+      <c r="C41" t="str" xml:space="preserve">
+        <v xml:space="preserve">덱 빌더: 12칸 슬롯 영역을 화면 상단에 고정(sticky), 후보 카드 목록을 스크롤해도 배치 결과를 계속 볼 수 있음
+안내문을 "❓ 도움말" 버튼으로 접어서 상단 공간 절약
+고정 영역에 배치 진행 상황(n/12) 표시 추가
+인격 배치 시 짧은 강조 애니메이션 + 하단 토스트 메시지("n번째 순서에 배치됨")로 스크롤 없이도 배치 결과 확인 가능
+모바일에서 12칸을 가로 스크롤 1줄로 배치해 세로 공간 절약</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C40"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C41"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:C42"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -899,9 +899,23 @@
 모바일에서 12칸을 가로 스크롤 1줄로 배치해 세로 공간 절약</v>
       </c>
     </row>
+    <row r="42" xml:space="preserve">
+      <c r="A42" t="str">
+        <v>v0.13.0</v>
+      </c>
+      <c r="B42" t="str">
+        <v>2026-07-06</v>
+      </c>
+      <c r="C42" t="str" xml:space="preserve">
+        <v xml:space="preserve">CharacterTable DeckData 시트 업데이트 반영: 덱이 6개 → 8개로 증가 (약지 출충덱/거미집/중지덱/검계덱/흑수덱/혈귀/진침탕/W사)
+DeckData의 인격명 표기를 CharacterData와 일치하도록 정리 (하이픈/공백/로마숫자 표기 차이 20건 수정)
+수감자-인격명이 뒤바뀐 오류 1건, 이름 오탈자 2건, 이름 누락 2건 등 실제 데이터 불일치 수정
+Type 칸의 대소문자 표기 불일치(sub → Sub) 5건 수정 (판정 로직에서 정답으로 인식되지 않던 버그)</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C41"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C42"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C42"/>
+  <dimension ref="A1:C43"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -913,9 +913,20 @@
 Type 칸의 대소문자 표기 불일치(sub → Sub) 5건 수정 (판정 로직에서 정답으로 인식되지 않던 버그)</v>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>v0.13.1</v>
+      </c>
+      <c r="B43" t="str">
+        <v>2026-07-06</v>
+      </c>
+      <c r="C43" t="str">
+        <v>덱 빌더: 인격명 검색 결과가 없을 때 "해당 인격 없음" 메시지 표시</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C42"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C43"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:C44"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -924,9 +924,23 @@
         <v>덱 빌더: 인격명 검색 결과가 없을 때 "해당 인격 없음" 메시지 표시</v>
       </c>
     </row>
+    <row r="44" xml:space="preserve">
+      <c r="A44" t="str">
+        <v>v0.13.2</v>
+      </c>
+      <c r="B44" t="str">
+        <v>2026-07-07</v>
+      </c>
+      <c r="C44" t="str" xml:space="preserve">
+        <v xml:space="preserve">덱 빌더 버그 수정: "없음" 카드를 먼저 배치하면 앞자리를 차지해 Main 정답 순서가 밀리던 문제 해결
+더블클릭 자동배치 시 "없음" 카드는 뒤쪽부터, 실제 인격은 앞쪽부터 채워지도록 분리
+Main 순서 판정을 절대 슬롯 위치가 아닌 배치된 Main 카드들끼리의 상대 순서로 비교하도록 개선
+(참고: "중지덱"의 순서값이 1,2,3,7로 비연속인 데이터 이슈 발견, DeckData 시트 확인 필요)</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C43"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C44"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C44"/>
+  <dimension ref="A1:C45"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -938,9 +938,21 @@
 (참고: "중지덱"의 순서값이 1,2,3,7로 비연속인 데이터 이슈 발견, DeckData 시트 확인 필요)</v>
       </c>
     </row>
+    <row r="45" xml:space="preserve">
+      <c r="A45" t="str">
+        <v>v0.13.3</v>
+      </c>
+      <c r="B45" t="str">
+        <v>2026-07-07</v>
+      </c>
+      <c r="C45" t="str" xml:space="preserve">
+        <v xml:space="preserve">덱 빌더 버그 수정: 인격명 검색 시 "없음" 카드가 검색어와 안 맞으면 함께 사라지던 문제 해결
+예: 로쟈 필터에서 "w사"로 검색해도 "로쟈 없음" 카드는 항상 표시됨 (없음은 이름 검색 대상에서 제외)</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C44"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C45"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C45"/>
+  <dimension ref="A1:C46"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -950,9 +950,22 @@
 예: 로쟈 필터에서 "w사"로 검색해도 "로쟈 없음" 카드는 항상 표시됨 (없음은 이름 검색 대상에서 제외)</v>
       </c>
     </row>
+    <row r="46" xml:space="preserve">
+      <c r="A46" t="str">
+        <v>v0.13.4</v>
+      </c>
+      <c r="B46" t="str">
+        <v>2026-07-07</v>
+      </c>
+      <c r="C46" t="str" xml:space="preserve">
+        <v xml:space="preserve">덱 빌더: 검색창과 수감자 필터 태그를 12칸 슬롯 영역 바로 아래에 고정(sticky)
+후보 카드 목록을 스크롤해도 검색창/필터가 화면에 계속 보임
+12칸 영역의 실제 높이(도움말 열림/닫힘, 모바일 레이아웃 등)를 매번 동적으로 측정해 겹침 없이 정확히 이어붙도록 처리</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C45"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C46"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C46"/>
+  <dimension ref="A1:C47"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -963,9 +963,22 @@
 12칸 영역의 실제 높이(도움말 열림/닫힘, 모바일 레이아웃 등)를 매번 동적으로 측정해 겹침 없이 정확히 이어붙도록 처리</v>
       </c>
     </row>
+    <row r="47" xml:space="preserve">
+      <c r="A47" t="str">
+        <v>v0.13.5</v>
+      </c>
+      <c r="B47" t="str">
+        <v>2026-07-07</v>
+      </c>
+      <c r="C47" t="str" xml:space="preserve">
+        <v xml:space="preserve">덱 빌더: 이중 스크롤 제거 + 제출 버튼 상단 고정
+후보 카드 목록의 자체 내부 스크롤(박스 안 스크롤)을 없애고 페이지 전체 스크롤 하나로 통일
+상단 고정 헤더에 제출 버튼 추가(진행률 표시: 제출 (N/12)), 하단 제출 버튼과 상태·클릭 동작 완전히 동기화되어 스크롤 안 해도 바로 제출 가능</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C46"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C47"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C47"/>
+  <dimension ref="A1:C48"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -976,9 +976,22 @@
 상단 고정 헤더에 제출 버튼 추가(진행률 표시: 제출 (N/12)), 하단 제출 버튼과 상태·클릭 동작 완전히 동기화되어 스크롤 안 해도 바로 제출 가능</v>
       </c>
     </row>
+    <row r="48" xml:space="preserve">
+      <c r="A48" t="str">
+        <v>v0.13.6</v>
+      </c>
+      <c r="B48" t="str">
+        <v>2026-07-07</v>
+      </c>
+      <c r="C48" t="str" xml:space="preserve">
+        <v xml:space="preserve">덱 빌더: 데스크톱(900px 이상) 좌우 분할 레이아웃 적용
+왼쪽 12칸 슬롯 패널 고정, 오른쪽 검색/후보 카드 영역 분리
+모바일/태블릿 레이아웃은 기존과 동일하게 유지</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C47"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C48"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C48"/>
+  <dimension ref="A1:C49"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -989,9 +989,22 @@
 모바일/태블릿 레이아웃은 기존과 동일하게 유지</v>
       </c>
     </row>
+    <row r="49" xml:space="preserve">
+      <c r="A49" t="str">
+        <v>v0.13.7</v>
+      </c>
+      <c r="B49" t="str">
+        <v>2026-07-07</v>
+      </c>
+      <c r="C49" t="str" xml:space="preserve">
+        <v xml:space="preserve">덱 빌더: 데스크톱 분할 레이아웃에서 상단 메뉴/제출 버튼 배치 개선
+좁은 좌측 패널에서 헤더 버튼이 줄바꿈되던 문제 수정
+제출 버튼을 헤더 바로 아래로 이동, 슬롯 영역 내부 스크롤 제거</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C48"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C49"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C49"/>
+  <dimension ref="A1:C50"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1002,9 +1002,22 @@
 제출 버튼을 헤더 바로 아래로 이동, 슬롯 영역 내부 스크롤 제거</v>
       </c>
     </row>
+    <row r="50" xml:space="preserve">
+      <c r="A50" t="str">
+        <v>v0.13.8</v>
+      </c>
+      <c r="B50" t="str">
+        <v>2026-07-07</v>
+      </c>
+      <c r="C50" t="str" xml:space="preserve">
+        <v xml:space="preserve">덱 빌더: 상단 메뉴/제출 버튼을 화면 최상단 전체 너비 바로 이동
+좁은 좌측 패널 안에 있던 버튼들을 분리해 좌우 분할 시에도 넉넉하게 표시
+모바일에서 타이틀 텍스트가 세로로 깨지던 문제 수정</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C49"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C50"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C50"/>
+  <dimension ref="A1:C51"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1015,9 +1015,22 @@
 모바일에서 타이틀 텍스트가 세로로 깨지던 문제 수정</v>
       </c>
     </row>
+    <row r="51" xml:space="preserve">
+      <c r="A51" t="str">
+        <v>v0.13.9</v>
+      </c>
+      <c r="B51" t="str">
+        <v>2026-07-07</v>
+      </c>
+      <c r="C51" t="str" xml:space="preserve">
+        <v xml:space="preserve">덱 빌더: 우측 하단에 중복으로 떠 있던 제출 버튼 제거
+상단 제출 버튼을 매우 크게 강조 표시로 변경
+좌우 패널 비율을 300px 고정에서 50:50으로 변경, 카드/슬롯 확대</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C51"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:C52"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1028,9 +1028,21 @@
 좌우 패널 비율을 300px 고정에서 50:50으로 변경, 카드/슬롯 확대</v>
       </c>
     </row>
+    <row r="52" xml:space="preserve">
+      <c r="A52" t="str">
+        <v>v0.13.10</v>
+      </c>
+      <c r="B52" t="str">
+        <v>2026-07-07</v>
+      </c>
+      <c r="C52" t="str" xml:space="preserve">
+        <v xml:space="preserve">덱 빌더: 아무 수감자의 없음 카드나 넣어도 정답 처리되던 채점 버그 수정
+없음 카드는 해당 슬롯이 요구하는 수감자와 일치할 때만 정답으로 인정</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C51"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C52"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C52"/>
+  <dimension ref="A1:C53"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1040,9 +1040,22 @@
 없음 카드는 해당 슬롯이 요구하는 수감자와 일치할 때만 정답으로 인정</v>
       </c>
     </row>
+    <row r="53" xml:space="preserve">
+      <c r="A53" t="str">
+        <v>v0.13.11</v>
+      </c>
+      <c r="B53" t="str">
+        <v>2026-07-07</v>
+      </c>
+      <c r="C53" t="str" xml:space="preserve">
+        <v xml:space="preserve">Main 카드 하나만 배치해도 정답으로 잠기던 채점/잠금 버그 수정
+Main 슬롯은 덱이 요구하는 Main 전원이 동시에 정답일 때만 잠기도록 변경
+다른 Main 배치가 바뀌면 이전에 맞았던 자리가 다시 틀릴 수 있어 섣불리 잠그지 않게 함</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C52"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C53"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C53"/>
+  <dimension ref="A1:C54"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1053,9 +1053,21 @@
 다른 Main 배치가 바뀌면 이전에 맞았던 자리가 다시 틀릴 수 있어 섣불리 잠그지 않게 함</v>
       </c>
     </row>
+    <row r="54" xml:space="preserve">
+      <c r="A54" t="str">
+        <v>v0.13.12</v>
+      </c>
+      <c r="B54" t="str">
+        <v>2026-07-07</v>
+      </c>
+      <c r="C54" t="str" xml:space="preserve">
+        <v xml:space="preserve">덱 빌더: 인격 배치 후 배치되지 않은 다음 수감자로 자동 전환
+드래그, 더블클릭/탭, 교체 배치 모두에서 동일하게 동작</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C53"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C54"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C54"/>
+  <dimension ref="A1:C55"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1065,9 +1065,23 @@
 드래그, 더블클릭/탭, 교체 배치 모두에서 동일하게 동작</v>
       </c>
     </row>
+    <row r="55" xml:space="preserve">
+      <c r="A55" t="str">
+        <v>v0.13.13</v>
+      </c>
+      <c r="B55" t="str">
+        <v>2026-07-07</v>
+      </c>
+      <c r="C55" t="str" xml:space="preserve">
+        <v xml:space="preserve">덱 빌더: 채점 방식을 절대 위치 기준으로 전면 변경
+Main 인격은 반드시 정답 순서 번호(order) 슬롯에 있어야 정답 처리
+Sub 인격은 위치 무관, 없음 카드는 뒤쪽 슬롯으로 자동 정렬
+제출 시 정답으로 확인된 카드를 올바른 자리로 자동 재배치 후 고정(영구 잠김 충돌 방지)</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C54"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C55"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:C56"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1079,9 +1079,22 @@
 제출 시 정답으로 확인된 카드를 올바른 자리로 자동 재배치 후 고정(영구 잠김 충돌 방지)</v>
       </c>
     </row>
+    <row r="56" xml:space="preserve">
+      <c r="A56" t="str">
+        <v>v0.13.14</v>
+      </c>
+      <c r="B56" t="str">
+        <v>2026-07-08</v>
+      </c>
+      <c r="C56" t="str" xml:space="preserve">
+        <v xml:space="preserve">덱 빌더: 제출 시 자동 재배치 기능 제거, 워들 방식 채점으로 변경
+놓인 자리 그대로 채점: Main은 정답 순서 칸이 아니면 노랑, 없음은 뒤쪽 구간 밖이면 노랑
+Sub는 기존처럼 위치 무관하게 정답 인격만 있으면 초록</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C55"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C56"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C56"/>
+  <dimension ref="A1:C57"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1092,9 +1092,21 @@
 Sub는 기존처럼 위치 무관하게 정답 인격만 있으면 초록</v>
       </c>
     </row>
+    <row r="57" xml:space="preserve">
+      <c r="A57" t="str">
+        <v>v0.13.15</v>
+      </c>
+      <c r="B57" t="str">
+        <v>2026-07-08</v>
+      </c>
+      <c r="C57" t="str" xml:space="preserve">
+        <v xml:space="preserve">덱 빌더: 카드 하나 제거 시 다른 칸들의 채점 표시가 전부 지워지던 버그 수정
+제거한 슬롯 하나만 비우고, 나머지 칸의 정답/오답 표시는 그대로 유지</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C56"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C57"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C57"/>
+  <dimension ref="A1:C58"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1104,9 +1104,22 @@
 제거한 슬롯 하나만 비우고, 나머지 칸의 정답/오답 표시는 그대로 유지</v>
       </c>
     </row>
+    <row r="58" xml:space="preserve">
+      <c r="A58" t="str">
+        <v>v0.13.16</v>
+      </c>
+      <c r="B58" t="str">
+        <v>2026-07-08</v>
+      </c>
+      <c r="C58" t="str" xml:space="preserve">
+        <v xml:space="preserve">덱 빌더: Sub/없음이 Main 전용 자리를 차지해 잠기던 버그 수정
+Sub나 없음이 어떤 Main의 정답 순서 칸(order 자리)에 있으면 노랑(순서 다름) 처리
+해당 자리를 비워줘야 그 Main이 정상적으로 정답 처리될 수 있음</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C57"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C58"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C58"/>
+  <dimension ref="A1:C59"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1117,9 +1117,21 @@
 해당 자리를 비워줘야 그 Main이 정상적으로 정답 처리될 수 있음</v>
       </c>
     </row>
+    <row r="59" xml:space="preserve">
+      <c r="A59" t="str">
+        <v>v0.13.17</v>
+      </c>
+      <c r="B59" t="str">
+        <v>2026-07-08</v>
+      </c>
+      <c r="C59" t="str" xml:space="preserve">
+        <v xml:space="preserve">인격 이미지(일반/각성) 및 스킬 아이콘을 로컬 파일로 교체
+외부 CDN 대신 프로젝트 내 이미지를 사용해 로딩 안정성 향상</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C58"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C59"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C59"/>
+  <dimension ref="A1:C60"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1129,9 +1129,21 @@
 외부 CDN 대신 프로젝트 내 이미지를 사용해 로딩 안정성 향상</v>
       </c>
     </row>
+    <row r="60" xml:space="preserve">
+      <c r="A60" t="str">
+        <v>v0.13.18</v>
+      </c>
+      <c r="B60" t="str">
+        <v>2026-07-08</v>
+      </c>
+      <c r="C60" t="str" xml:space="preserve">
+        <v xml:space="preserve">CharacterTable에 ID열(A열) 추가
+인격 고유 번호를 데이터에 노출해 추후 참조/매칭에 사용할 수 있도록 함</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C59"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C60"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C60"/>
+  <dimension ref="A1:C61"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1141,9 +1141,21 @@
 인격 고유 번호를 데이터에 노출해 추후 참조/매칭에 사용할 수 있도록 함</v>
       </c>
     </row>
+    <row r="61" xml:space="preserve">
+      <c r="A61" t="str">
+        <v>v0.13.19</v>
+      </c>
+      <c r="B61" t="str">
+        <v>2026-07-08</v>
+      </c>
+      <c r="C61" t="str" xml:space="preserve">
+        <v xml:space="preserve">덱 빌더: 클리어/포기 결과 패널을 하단에서 상단(제출 버튼 아래)으로 이동
+결과 패널의 홈으로 버튼 제거(좌측 상단 홈으로 버튼과 중복이라 제거, 다음 덱만 남김)</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C60"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C61"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C61"/>
+  <dimension ref="A1:C62"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1153,9 +1153,22 @@
 결과 패널의 홈으로 버튼 제거(좌측 상단 홈으로 버튼과 중복이라 제거, 다음 덱만 남김)</v>
       </c>
     </row>
+    <row r="62" xml:space="preserve">
+      <c r="A62" t="str">
+        <v>v0.13.20</v>
+      </c>
+      <c r="B62" t="str">
+        <v>2026-07-08</v>
+      </c>
+      <c r="C62" t="str" xml:space="preserve">
+        <v xml:space="preserve">decks.json 빌드 스크립트를 DeckInfo 시트와 조인하도록 재작성
+DeckData의 Deck 컬럼이 삭제되면서 배포판 덱 이름이 빈 값으로 나오던 버그 수정
+덱 키워드(deckKeywords.json) 빌드 결과물 신규 추가(향후 힌트 기능용)</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C61"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C62"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C62"/>
+  <dimension ref="A1:C63"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1166,9 +1166,21 @@
 덱 키워드(deckKeywords.json) 빌드 결과물 신규 추가(향후 힌트 기능용)</v>
       </c>
     </row>
+    <row r="63" xml:space="preserve">
+      <c r="A63" t="str">
+        <v>v0.13.21</v>
+      </c>
+      <c r="B63" t="str">
+        <v>2026-07-08</v>
+      </c>
+      <c r="C63" t="str" xml:space="preserve">
+        <v xml:space="preserve">덱 빌더: 왼쪽 슬롯 패널의 고정(sticky) 스크롤 제거
+페이지 전체가 하나로 자연스럽게 스크롤되도록 변경</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C62"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C63"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C63"/>
+  <dimension ref="A1:C64"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1178,9 +1178,22 @@
 페이지 전체가 하나로 자연스럽게 스크롤되도록 변경</v>
       </c>
     </row>
+    <row r="64" xml:space="preserve">
+      <c r="A64" t="str">
+        <v>v0.13.22</v>
+      </c>
+      <c r="B64" t="str">
+        <v>2026-07-09</v>
+      </c>
+      <c r="C64" t="str" xml:space="preserve">
+        <v xml:space="preserve">오늘의 인격/랜덤 플레이에서 정답을 맞히면 공유하기 버튼 표시
+홈 화면의 결과 카드(이미지 저장/클립보드 복사)와 동일한 모달을 사용
+이미 플레이한 오늘의 인격을 다시 방문해도 공유 버튼이 유지됨</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C63"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C64"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C64"/>
+  <dimension ref="A1:C65"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1191,9 +1191,22 @@
 이미 플레이한 오늘의 인격을 다시 방문해도 공유 버튼이 유지됨</v>
       </c>
     </row>
+    <row r="65" xml:space="preserve">
+      <c r="A65" t="str">
+        <v>v0.13.23</v>
+      </c>
+      <c r="B65" t="str">
+        <v>2026-07-09</v>
+      </c>
+      <c r="C65" t="str" xml:space="preserve">
+        <v xml:space="preserve">덱 빌더: 후보 인격 목록에 키워드 필터 추가(다중 선택, AND 조건)
+DATA 기반으로 키워드 목록을 동적으로 생성, 검색어/수감자 필터와 함께 적용
+없음 카드는 키워드 필터와 무관하게 항상 노출</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C64"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C65"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C65"/>
+  <dimension ref="A1:C66"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1204,9 +1204,22 @@
 없음 카드는 키워드 필터와 무관하게 항상 노출</v>
       </c>
     </row>
+    <row r="66" xml:space="preserve">
+      <c r="A66" t="str">
+        <v>v0.13.24</v>
+      </c>
+      <c r="B66" t="str">
+        <v>2026-07-09</v>
+      </c>
+      <c r="C66" t="str" xml:space="preserve">
+        <v xml:space="preserve">오늘의 인격/랜덤 플레이: 공유하기 버튼을 정답 카드 안으로 이동
+정답 공개 시 자동 스크롤 후에도 공유 버튼이 바로 보이도록 개선
+일치/불일치/취소선 테스트 설명을 하단 추측 기록 카드로 이동</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C65"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C66"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C66"/>
+  <dimension ref="A1:C67"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1217,9 +1217,22 @@
 일치/불일치/취소선 테스트 설명을 하단 추측 기록 카드로 이동</v>
       </c>
     </row>
+    <row r="67" xml:space="preserve">
+      <c r="A67" t="str">
+        <v>v0.13.25</v>
+      </c>
+      <c r="B67" t="str">
+        <v>2026-07-09</v>
+      </c>
+      <c r="C67" t="str" xml:space="preserve">
+        <v xml:space="preserve">인격 맞추기: 키워드 불일치로 확정 제외된 키워드를 가진 후보도 취소선 처리
+제외된 후보(이름 기준 + 키워드 기준)는 드롭다운 하단으로 정렬
+재시작/다음 문제 시 제외 상태 초기화</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C66"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C67"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C67"/>
+  <dimension ref="A1:C68"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1230,9 +1230,23 @@
 재시작/다음 문제 시 제외 상태 초기화</v>
       </c>
     </row>
+    <row r="68" xml:space="preserve">
+      <c r="A68" t="str">
+        <v>v0.13.26</v>
+      </c>
+      <c r="B68" t="str">
+        <v>2026-07-09</v>
+      </c>
+      <c r="C68" t="str" xml:space="preserve">
+        <v xml:space="preserve">CharacterTable.xlsx 구조 변경(스킬 데이터 SkillData 시트로 분리) 반영
+CharacterData+SkillData를 ID로 조인해 data.json 생성하도록 빌드 스크립트 수정
+신규 인격 2종 추가(새벽 사무소 대표 그레고르, 새벽 사무소 해결사 파우스트)
+더 이상 쓰이지 않는 프로필(각성) 필드는 data.json에서 제거</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C67"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C68"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C68"/>
+  <dimension ref="A1:C69"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1244,9 +1244,21 @@
 더 이상 쓰이지 않는 프로필(각성) 필드는 data.json에서 제거</v>
       </c>
     </row>
+    <row r="69" xml:space="preserve">
+      <c r="A69" t="str">
+        <v>v0.13.27</v>
+      </c>
+      <c r="B69" t="str">
+        <v>2026-07-10</v>
+      </c>
+      <c r="C69" t="str" xml:space="preserve">
+        <v xml:space="preserve">남부 리우 협회 3과 이상 각성 이미지 추가
+기존에는 일반 이미지가 각성 자리에도 임시로 들어가 있었는데 실제 각성 이미지로 교체</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C68"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C69"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C69"/>
+  <dimension ref="A1:C70"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1256,9 +1256,21 @@
 기존에는 일반 이미지가 각성 자리에도 임시로 들어가 있었는데 실제 각성 이미지로 교체</v>
       </c>
     </row>
+    <row r="70" xml:space="preserve">
+      <c r="A70" t="str">
+        <v>v0.13.28</v>
+      </c>
+      <c r="B70" t="str">
+        <v>2026-07-10</v>
+      </c>
+      <c r="C70" t="str" xml:space="preserve">
+        <v xml:space="preserve">덱 빌더: 좌측 인격 배치 순서 패널 고정(sticky) 다시 적용
+우측 후보 카드에 일반/각성 이미지 전환 버튼 추가(각성 이미지가 따로 있는 경우만 표시)</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C69"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C70"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -4,6 +4,7 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="UpdateLog" sheetId="1" r:id="rId1"/>
+    <sheet name="UpdateLog_백업" sheetId="2" r:id="rId2"/>
   </sheets>
 </workbook>
 </file>
@@ -397,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C70"/>
+  <dimension ref="A1:D71"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -407,7 +408,10 @@
         <v>날짜</v>
       </c>
       <c r="C1" t="str">
-        <v>내용</v>
+        <v>개발자용 Log</v>
+      </c>
+      <c r="D1" t="str">
+        <v>사용자용 Log</v>
       </c>
     </row>
     <row r="2" xml:space="preserve">
@@ -422,6 +426,9 @@
 엑셀 기반 데이터 파이프라인 구축
 키워드 칩 가독성 개선 (고대비 색상)</v>
       </c>
+      <c r="D2" t="str">
+        <v>인격 두들 게임을 처음 오픈했습니다! 키워드 표시 가독성을 개선했습니다.</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -433,6 +440,9 @@
       <c r="C3" t="str">
         <v>초기 안정화</v>
       </c>
+      <c r="D3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4" xml:space="preserve">
       <c r="A4" t="str">
@@ -445,6 +455,9 @@
         <v xml:space="preserve">폰트 크기 조정
 수감자별 컬러 도트 적용</v>
       </c>
+      <c r="D4" t="str">
+        <v>글자 크기를 조정하고 수감자별 색상 점을 추가했습니다.</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -455,6 +468,9 @@
       </c>
       <c r="C5" t="str">
         <v>플레이 기록 UI 개선</v>
+      </c>
+      <c r="D5" t="str">
+        <v>플레이 기록 화면을 더 보기 편하게 개선했습니다.</v>
       </c>
     </row>
     <row r="6" xml:space="preserve">
@@ -469,6 +485,9 @@
 테이블 헤더 줄바꿈 방지
 화살표 스크롤 버그 수정</v>
       </c>
+      <c r="D6" t="str">
+        <v>필터에 드롭다운 목록을 추가하고 화면 버그를 수정했습니다.</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -480,6 +499,9 @@
       <c r="C7" t="str">
         <v>최대 시도 횟수 5회 → 7회로 조정</v>
       </c>
+      <c r="D7" t="str">
+        <v>최대 시도 횟수를 5회에서 7회로 늘렸습니다.</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -491,6 +513,9 @@
       <c r="C8" t="str">
         <v>정답 인격 이미지 표시 추가</v>
       </c>
+      <c r="D8" t="str">
+        <v>정답 공개 시 인격 이미지가 함께 표시됩니다.</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -502,6 +527,9 @@
       <c r="C9" t="str">
         <v>소속1 / 소속2 필터·테이블·정답 표시 추가</v>
       </c>
+      <c r="D9" t="str">
+        <v>소속 정보를 필터와 정답 화면에서도 볼 수 있게 추가했습니다.</v>
+      </c>
     </row>
     <row r="10" xml:space="preserve">
       <c r="A10" t="str">
@@ -514,6 +542,9 @@
         <v xml:space="preserve">일일 챌린지(오늘의 인격) 모드 추가
 파비콘 추가</v>
       </c>
+      <c r="D10" t="str">
+        <v>매일 새로운 문제가 나오는 '오늘의 인격' 모드를 추가했습니다.</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
@@ -524,6 +555,9 @@
       </c>
       <c r="C11" t="str">
         <v>결과 카드 팝업 &amp; 홈 입장 페이지 추가</v>
+      </c>
+      <c r="D11" t="str">
+        <v>결과를 카드 이미지로 볼 수 있는 기능과 홈 화면을 추가했습니다.</v>
       </c>
     </row>
     <row r="12" xml:space="preserve">
@@ -538,6 +572,9 @@
 정답 이미지 크기 확대
 스킬 퀴즈 신규 제작 (프로토타입)</v>
       </c>
+      <c r="D12" t="str">
+        <v>정답 이미지를 일반/각성으로 전환해서 볼 수 있고, 새로운 '스킬 퀴즈' 모드를 시범 추가했습니다.</v>
+      </c>
     </row>
     <row r="13" xml:space="preserve">
       <c r="A13" t="str">
@@ -550,6 +587,9 @@
         <v xml:space="preserve">스킬 퀴즈를 메인 페이지에 통합
 홈 화면에서 인격 두들 / 스킬 퀴즈 선택 가능</v>
       </c>
+      <c r="D13" t="str">
+        <v>홈 화면에서 인격 두들과 스킬 퀴즈를 골라서 플레이할 수 있습니다.</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
@@ -560,6 +600,9 @@
       </c>
       <c r="C14" t="str">
         <v>버전 표시 갱신</v>
+      </c>
+      <c r="D14" t="str">
+        <v/>
       </c>
     </row>
     <row r="15" xml:space="preserve">
@@ -574,6 +617,9 @@
 홈 화면 게임 카드 높이 정렬
 스킬 퀴즈 카드에 NEW 배지 추가</v>
       </c>
+      <c r="D15" t="str">
+        <v>결과 카드와 홈 화면의 표시 오류를 수정하고, 스킬 퀴즈에 NEW 배지를 추가했습니다.</v>
+      </c>
     </row>
     <row r="16" xml:space="preserve">
       <c r="A16" t="str">
@@ -587,6 +633,9 @@
 필터를 상단 헤더로 분리하고 레이아웃 개선
 정답 선택 영역을 강조 박스로 분리</v>
       </c>
+      <c r="D16" t="str">
+        <v>결과 카드를 더 크고 보기 좋게 개선하고 화면 레이아웃을 정리했습니다.</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
@@ -598,6 +647,9 @@
       <c r="C17" t="str">
         <v>정답을 맞히면 컨페티 팡파레 애니메이션 재생</v>
       </c>
+      <c r="D17" t="str">
+        <v>정답을 맞히면 축하 애니메이션이 재생됩니다.</v>
+      </c>
     </row>
     <row r="18" xml:space="preserve">
       <c r="A18" t="str">
@@ -610,6 +662,9 @@
         <v xml:space="preserve">정답 공개 영역에 자동 스크롤 추가
 성공/실패 카드형 강조 스타일 적용</v>
       </c>
+      <c r="D18" t="str">
+        <v>정답이 공개되면 자동으로 화면이 이동하고, 성공/실패를 더 명확하게 보여줍니다.</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
@@ -621,6 +676,9 @@
       <c r="C19" t="str">
         <v>정답 이미지 로드 완료 후 재스크롤하여 화면 중앙 정렬 보정</v>
       </c>
+      <c r="D19" t="str">
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
@@ -632,6 +690,9 @@
       <c r="C20" t="str">
         <v>필터 항목을 수감자/성급 · 키워드 · 소속 세 그룹으로 나누고 구분선 추가</v>
       </c>
+      <c r="D20" t="str">
+        <v>필터 항목을 그룹별로 나누어 보기 편하게 정리했습니다.</v>
+      </c>
     </row>
     <row r="21" xml:space="preserve">
       <c r="A21" t="str">
@@ -644,6 +705,9 @@
         <v xml:space="preserve">업데이트 기록 보기 버튼 및 팝업 추가
 엑셀(UpdateLog.xlsx) 기반으로 업데이트 로그를 관리하고 자동 반영</v>
       </c>
+      <c r="D21" t="str">
+        <v>업데이트 기록을 확인할 수 있는 버튼을 추가했습니다.</v>
+      </c>
     </row>
     <row r="22" xml:space="preserve">
       <c r="A22" t="str">
@@ -656,6 +720,9 @@
         <v xml:space="preserve">필터 라벨(수감자/성급/키워드/소속)에 아이콘 추가하고 글씨 크게 강조
 필터 그룹이 세 줄로 나뉘던 문제 수정, 한 줄에 표시되도록 개선</v>
       </c>
+      <c r="D22" t="str">
+        <v>필터 항목에 아이콘을 추가하고 한 줄로 깔끔하게 정리했습니다.</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
@@ -667,6 +734,9 @@
       <c r="C23" t="str">
         <v>정답 공개, 스킬 퀴즈, 결과 카드에서 각성 이미지를 기본으로 표시하도록 변경 (각성 이미지가 없으면 일반 이미지로 대체)</v>
       </c>
+      <c r="D23" t="str">
+        <v>정답 공개 시 각성 이미지를 기본으로 보여주도록 변경했습니다.</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
@@ -678,6 +748,9 @@
       <c r="C24" t="str">
         <v>CharacterTable.xlsx 스킬1/2/3 정보(명칭·속성·유형·아이콘) 최신화 반영</v>
       </c>
+      <c r="D24" t="str">
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
@@ -689,6 +762,9 @@
       <c r="C25" t="str">
         <v>스킬 퀴즈 스테이지1에 스킬별 힌트 보기 / 정답 보기 버튼 추가</v>
       </c>
+      <c r="D25" t="str">
+        <v>스킬 퀴즈에 힌트 보기와 정답 보기 기능을 추가했습니다.</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
@@ -700,6 +776,9 @@
       <c r="C26" t="str">
         <v>스킬 퀴즈 인격 이미지가 잘리던 문제 수정 (object-fit: cover → contain)</v>
       </c>
+      <c r="D26" t="str">
+        <v>스킬 퀴즈 이미지가 잘려 보이던 문제를 수정했습니다.</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
@@ -710,6 +789,9 @@
       </c>
       <c r="C27" t="str">
         <v>스킬 퀴즈 인격 이미지를 카드 상단 전체 폭으로 크게 확대 (520px)</v>
+      </c>
+      <c r="D27" t="str">
+        <v>스킬 퀴즈 이미지를 더 크게 키웠습니다.</v>
       </c>
     </row>
     <row r="28" xml:space="preserve">
@@ -724,6 +806,9 @@
 포기 시 이미 맞힌 속성/유형은 유지하고 틀리거나 미선택한 항목만 정답으로 채움
 결과 화면에 스킬별로 직접 맞힌 항목과 포기한 항목을 배지로 구분 표시, 전체 정답률 통계 추가</v>
       </c>
+      <c r="D28" t="str">
+        <v>스킬 퀴즈에 포기하기 버튼과 정답률 통계를 추가했습니다.</v>
+      </c>
     </row>
     <row r="29" xml:space="preserve">
       <c r="A29" t="str">
@@ -736,6 +821,9 @@
         <v xml:space="preserve">인격 두들 정답 공개를 카드형 레이아웃으로 재구성
 인격명 카드는 수감자 컬러로 강조, 키워드는 색상 칩으로 표시</v>
       </c>
+      <c r="D29" t="str">
+        <v>정답 공개 화면을 카드 형태로 새롭게 디자인했습니다.</v>
+      </c>
     </row>
     <row r="30" xml:space="preserve">
       <c r="A30" t="str">
@@ -747,6 +835,9 @@
       <c r="C30" t="str" xml:space="preserve">
         <v xml:space="preserve">CharacterTable.xlsx 이미지 URL 최신화 반영 (인격 이미지, 프로필, 스킬 아이콘)
 스킬1/2/3 아이콘이 동일하게 나오던 64개 인격 문제도 함께 해결됨</v>
+      </c>
+      <c r="D30" t="str">
+        <v>인격/스킬 이미지가 잘못 표시되던 문제들을 수정했습니다.</v>
       </c>
     </row>
     <row r="31" xml:space="preserve">
@@ -762,6 +853,9 @@
 워들 스타일 3색 판정(초록/노랑/빨강), 핵심/일반 슬롯 구분, 정답 보기 기능 지원
 데스크톱 드래그앤드롭과 모바일 탭-투-배치 모두 지원</v>
       </c>
+      <c r="D31" t="str">
+        <v>새로운 게임 모드 '덱 빌더'를 추가했습니다! 추천 덱을 직접 맞춰보세요.</v>
+      </c>
     </row>
     <row r="32" xml:space="preserve">
       <c r="A32" t="str">
@@ -775,6 +869,9 @@
 이미지 저장 시 CORS 문제로 인격 이미지가 비어보이던 버그 수정 (프록시 경유)
 클립보드에 카드 이미지를 바로 복사하는 기능 추가</v>
       </c>
+      <c r="D32" t="str">
+        <v>결과 카드에 스포일러 방지(정답 가리기)와 클립보드 복사 기능을 추가했습니다.</v>
+      </c>
     </row>
     <row r="33" xml:space="preserve">
       <c r="A33" t="str">
@@ -786,6 +883,9 @@
       <c r="C33" t="str" xml:space="preserve">
         <v xml:space="preserve">정답 가리기를 블러 대신 완전 비활성화(불투명 커버)로 변경
 가리기 상태에서 소속/키워드 정보도 함께 숨김 처리</v>
+      </c>
+      <c r="D33" t="str">
+        <v>스포일러 가리기 효과를 더 확실하게 개선했습니다.</v>
       </c>
     </row>
     <row r="34" xml:space="preserve">
@@ -801,6 +901,9 @@
 2단계: 1단계 통과 후 Main 인격들의 전투 순서를 워들 스타일로 맞추기
 덱href 기준으로 그룹핑, ID 개수를 하드코딩하지 않고 동적으로 로드
 정답 보기(포기), 검색 필터, 드래그 앤 드롭+탭 배치 지원</v>
+      </c>
+      <c r="D34" t="str">
+        <v>덱 빌더를 더 편리하게 새로 개편했습니다.</v>
       </c>
     </row>
     <row r="35" xml:space="preserve">
@@ -819,6 +922,9 @@
 인격 카드 더블클릭으로 자동 배치 지원 (보드 우선, 없으면 순서 칸)
 1단계(수감자 배치)와 2단계(전투 순서)를 한 화면으로 통합</v>
       </c>
+      <c r="D35" t="str">
+        <v>덱 빌더 후보 목록과 배치 방식을 더 편리하게 개선했습니다.</v>
+      </c>
     </row>
     <row r="36" xml:space="preserve">
       <c r="A36" t="str">
@@ -833,6 +939,9 @@
 버그 수정: 더블클릭 미작동, 정답 덱 이름/설명이 화면에 노출되던 스포일러 문제, 빈 칸이 있어도 제출되던 문제 모두 해결
 같은 수감자 중복 배치 방지(없음 카드는 예외), 12칸을 모두 채워야 제출 버튼 활성화</v>
       </c>
+      <c r="D36" t="str">
+        <v>덱 빌더 배치 방식을 더 직관적으로 개선했습니다.</v>
+      </c>
     </row>
     <row r="37" xml:space="preserve">
       <c r="A37" t="str">
@@ -844,6 +953,9 @@
       <c r="C37" t="str" xml:space="preserve">
         <v xml:space="preserve">덱 빌더: "없음" 카드를 수감자별로 분리해 어떤 수감자를 없음으로 표시했는지 명확히 보여줌
 예: "없음" -&gt; "돈키호테 없음" 처럼 표시. 다른 수감자의 없음과 구분되고, 같은 수감자 중복 배치 방지 규칙도 없음 카드에 동일하게 적용됨</v>
+      </c>
+      <c r="D37" t="str">
+        <v>'없음' 카드를 어떤 수감자의 것인지 더 명확하게 보여줍니다.</v>
       </c>
     </row>
     <row r="38" xml:space="preserve">
@@ -861,6 +973,9 @@
 중간 슬롯 제거 시 뒤 슬롯들이 앞으로 당겨지도록 변경
 제출 후 정답(초록)인 슬롯은 고정되어 계속 유지되고, 순서만 틀린(노랑)/오답(빨강) 인격은 후보 목록에 다시 넣어도 표시가 남도록 변경, 오답은 이미지에 X 표시</v>
       </c>
+      <c r="D38" t="str">
+        <v>덱 빌더에 '모두 비우기' 버튼을 추가하고 배치 관련 버그를 수정했습니다.</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
@@ -872,6 +987,9 @@
       <c r="C39" t="str">
         <v>덱 빌더: 후보 목록에서 "없음" 카드가 각 수감자 탭에서 항상 맨 앞에 오도록 정렬</v>
       </c>
+      <c r="D39" t="str">
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
@@ -882,6 +1000,9 @@
       </c>
       <c r="C40" t="str">
         <v>덱 빌더: 수감자 필터 탭에 이미 배치된 수감자를 체크 표시(✓)와 초록 테두리로 표시</v>
+      </c>
+      <c r="D40" t="str">
+        <v>덱 빌더: 이미 인격을 배치한 수감자는 필터 탭에 표시가 남습니다.</v>
       </c>
     </row>
     <row r="41" xml:space="preserve">
@@ -898,6 +1019,9 @@
 인격 배치 시 짧은 강조 애니메이션 + 하단 토스트 메시지("n번째 순서에 배치됨")로 스크롤 없이도 배치 결과 확인 가능
 모바일에서 12칸을 가로 스크롤 1줄로 배치해 세로 공간 절약</v>
       </c>
+      <c r="D41" t="str">
+        <v>덱 빌더 화면 상단 고정과 배치 애니메이션 효과를 추가했습니다.</v>
+      </c>
     </row>
     <row r="42" xml:space="preserve">
       <c r="A42" t="str">
@@ -912,6 +1036,9 @@
 수감자-인격명이 뒤바뀐 오류 1건, 이름 오탈자 2건, 이름 누락 2건 등 실제 데이터 불일치 수정
 Type 칸의 대소문자 표기 불일치(sub → Sub) 5건 수정 (판정 로직에서 정답으로 인식되지 않던 버그)</v>
       </c>
+      <c r="D42" t="str">
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
@@ -922,6 +1049,9 @@
       </c>
       <c r="C43" t="str">
         <v>덱 빌더: 인격명 검색 결과가 없을 때 "해당 인격 없음" 메시지 표시</v>
+      </c>
+      <c r="D43" t="str">
+        <v>덱 빌더: 검색 결과가 없을 때 안내 메시지를 표시합니다.</v>
       </c>
     </row>
     <row r="44" xml:space="preserve">
@@ -937,6 +1067,9 @@
 Main 순서 판정을 절대 슬롯 위치가 아닌 배치된 Main 카드들끼리의 상대 순서로 비교하도록 개선
 (참고: "중지덱"의 순서값이 1,2,3,7로 비연속인 데이터 이슈 발견, DeckData 시트 확인 필요)</v>
       </c>
+      <c r="D44" t="str">
+        <v/>
+      </c>
     </row>
     <row r="45" xml:space="preserve">
       <c r="A45" t="str">
@@ -948,6 +1081,9 @@
       <c r="C45" t="str" xml:space="preserve">
         <v xml:space="preserve">덱 빌더 버그 수정: 인격명 검색 시 "없음" 카드가 검색어와 안 맞으면 함께 사라지던 문제 해결
 예: 로쟈 필터에서 "w사"로 검색해도 "로쟈 없음" 카드는 항상 표시됨 (없음은 이름 검색 대상에서 제외)</v>
+      </c>
+      <c r="D45" t="str">
+        <v>덱 빌더: 인격명 검색 중에도 '없음' 카드가 항상 보이도록 수정했습니다.</v>
       </c>
     </row>
     <row r="46" xml:space="preserve">
@@ -962,6 +1098,9 @@
 후보 카드 목록을 스크롤해도 검색창/필터가 화면에 계속 보임
 12칸 영역의 실제 높이(도움말 열림/닫힘, 모바일 레이아웃 등)를 매번 동적으로 측정해 겹침 없이 정확히 이어붙도록 처리</v>
       </c>
+      <c r="D46" t="str">
+        <v>덱 빌더: 검색창과 필터가 화면에 고정되어 스크롤해도 계속 보입니다.</v>
+      </c>
     </row>
     <row r="47" xml:space="preserve">
       <c r="A47" t="str">
@@ -975,6 +1114,9 @@
 후보 카드 목록의 자체 내부 스크롤(박스 안 스크롤)을 없애고 페이지 전체 스크롤 하나로 통일
 상단 고정 헤더에 제출 버튼 추가(진행률 표시: 제출 (N/12)), 하단 제출 버튼과 상태·클릭 동작 완전히 동기화되어 스크롤 안 해도 바로 제출 가능</v>
       </c>
+      <c r="D47" t="str">
+        <v>덱 빌더: 화면 스크롤 방식을 통일하고 제출 버튼을 상단에 고정했습니다.</v>
+      </c>
     </row>
     <row r="48" xml:space="preserve">
       <c r="A48" t="str">
@@ -988,6 +1130,9 @@
 왼쪽 12칸 슬롯 패널 고정, 오른쪽 검색/후보 카드 영역 분리
 모바일/태블릿 레이아웃은 기존과 동일하게 유지</v>
       </c>
+      <c r="D48" t="str">
+        <v>덱 빌더: PC 화면에서 좌우 분할 레이아웃을 적용했습니다.</v>
+      </c>
     </row>
     <row r="49" xml:space="preserve">
       <c r="A49" t="str">
@@ -1001,6 +1146,9 @@
 좁은 좌측 패널에서 헤더 버튼이 줄바꿈되던 문제 수정
 제출 버튼을 헤더 바로 아래로 이동, 슬롯 영역 내부 스크롤 제거</v>
       </c>
+      <c r="D49" t="str">
+        <v/>
+      </c>
     </row>
     <row r="50" xml:space="preserve">
       <c r="A50" t="str">
@@ -1014,6 +1162,9 @@
 좁은 좌측 패널 안에 있던 버튼들을 분리해 좌우 분할 시에도 넉넉하게 표시
 모바일에서 타이틀 텍스트가 세로로 깨지던 문제 수정</v>
       </c>
+      <c r="D50" t="str">
+        <v/>
+      </c>
     </row>
     <row r="51" xml:space="preserve">
       <c r="A51" t="str">
@@ -1027,6 +1178,9 @@
 상단 제출 버튼을 매우 크게 강조 표시로 변경
 좌우 패널 비율을 300px 고정에서 50:50으로 변경, 카드/슬롯 확대</v>
       </c>
+      <c r="D51" t="str">
+        <v/>
+      </c>
     </row>
     <row r="52" xml:space="preserve">
       <c r="A52" t="str">
@@ -1038,6 +1192,9 @@
       <c r="C52" t="str" xml:space="preserve">
         <v xml:space="preserve">덱 빌더: 아무 수감자의 없음 카드나 넣어도 정답 처리되던 채점 버그 수정
 없음 카드는 해당 슬롯이 요구하는 수감자와 일치할 때만 정답으로 인정</v>
+      </c>
+      <c r="D52" t="str">
+        <v/>
       </c>
     </row>
     <row r="53" xml:space="preserve">
@@ -1052,6 +1209,9 @@
 Main 슬롯은 덱이 요구하는 Main 전원이 동시에 정답일 때만 잠기도록 변경
 다른 Main 배치가 바뀌면 이전에 맞았던 자리가 다시 틀릴 수 있어 섣불리 잠그지 않게 함</v>
       </c>
+      <c r="D53" t="str">
+        <v/>
+      </c>
     </row>
     <row r="54" xml:space="preserve">
       <c r="A54" t="str">
@@ -1063,6 +1223,9 @@
       <c r="C54" t="str" xml:space="preserve">
         <v xml:space="preserve">덱 빌더: 인격 배치 후 배치되지 않은 다음 수감자로 자동 전환
 드래그, 더블클릭/탭, 교체 배치 모두에서 동일하게 동작</v>
+      </c>
+      <c r="D54" t="str">
+        <v>덱 빌더: 인격을 배치하면 다음 순서로 자동 전환됩니다.</v>
       </c>
     </row>
     <row r="55" xml:space="preserve">
@@ -1078,6 +1241,9 @@
 Sub 인격은 위치 무관, 없음 카드는 뒤쪽 슬롯으로 자동 정렬
 제출 시 정답으로 확인된 카드를 올바른 자리로 자동 재배치 후 고정(영구 잠김 충돌 방지)</v>
       </c>
+      <c r="D55" t="str">
+        <v/>
+      </c>
     </row>
     <row r="56" xml:space="preserve">
       <c r="A56" t="str">
@@ -1091,6 +1257,9 @@
 놓인 자리 그대로 채점: Main은 정답 순서 칸이 아니면 노랑, 없음은 뒤쪽 구간 밖이면 노랑
 Sub는 기존처럼 위치 무관하게 정답 인격만 있으면 초록</v>
       </c>
+      <c r="D56" t="str">
+        <v>덱 빌더: 채점 방식을 더 명확하게 개선했습니다.</v>
+      </c>
     </row>
     <row r="57" xml:space="preserve">
       <c r="A57" t="str">
@@ -1102,6 +1271,9 @@
       <c r="C57" t="str" xml:space="preserve">
         <v xml:space="preserve">덱 빌더: 카드 하나 제거 시 다른 칸들의 채점 표시가 전부 지워지던 버그 수정
 제거한 슬롯 하나만 비우고, 나머지 칸의 정답/오답 표시는 그대로 유지</v>
+      </c>
+      <c r="D57" t="str">
+        <v>덱 빌더: 카드를 하나 빼도 다른 칸의 채점 결과가 유지되도록 수정했습니다.</v>
       </c>
     </row>
     <row r="58" xml:space="preserve">
@@ -1116,6 +1288,9 @@
 Sub나 없음이 어떤 Main의 정답 순서 칸(order 자리)에 있으면 노랑(순서 다름) 처리
 해당 자리를 비워줘야 그 Main이 정상적으로 정답 처리될 수 있음</v>
       </c>
+      <c r="D58" t="str">
+        <v/>
+      </c>
     </row>
     <row r="59" xml:space="preserve">
       <c r="A59" t="str">
@@ -1128,6 +1303,9 @@
         <v xml:space="preserve">인격 이미지(일반/각성) 및 스킬 아이콘을 로컬 파일로 교체
 외부 CDN 대신 프로젝트 내 이미지를 사용해 로딩 안정성 향상</v>
       </c>
+      <c r="D59" t="str">
+        <v/>
+      </c>
     </row>
     <row r="60" xml:space="preserve">
       <c r="A60" t="str">
@@ -1140,6 +1318,9 @@
         <v xml:space="preserve">CharacterTable에 ID열(A열) 추가
 인격 고유 번호를 데이터에 노출해 추후 참조/매칭에 사용할 수 있도록 함</v>
       </c>
+      <c r="D60" t="str">
+        <v/>
+      </c>
     </row>
     <row r="61" xml:space="preserve">
       <c r="A61" t="str">
@@ -1151,6 +1332,9 @@
       <c r="C61" t="str" xml:space="preserve">
         <v xml:space="preserve">덱 빌더: 클리어/포기 결과 패널을 하단에서 상단(제출 버튼 아래)으로 이동
 결과 패널의 홈으로 버튼 제거(좌측 상단 홈으로 버튼과 중복이라 제거, 다음 덱만 남김)</v>
+      </c>
+      <c r="D61" t="str">
+        <v>덱 빌더: 결과 화면 레이아웃을 정리했습니다.</v>
       </c>
     </row>
     <row r="62" xml:space="preserve">
@@ -1165,6 +1349,9 @@
 DeckData의 Deck 컬럼이 삭제되면서 배포판 덱 이름이 빈 값으로 나오던 버그 수정
 덱 키워드(deckKeywords.json) 빌드 결과물 신규 추가(향후 힌트 기능용)</v>
       </c>
+      <c r="D62" t="str">
+        <v/>
+      </c>
     </row>
     <row r="63" xml:space="preserve">
       <c r="A63" t="str">
@@ -1176,6 +1363,9 @@
       <c r="C63" t="str" xml:space="preserve">
         <v xml:space="preserve">덱 빌더: 왼쪽 슬롯 패널의 고정(sticky) 스크롤 제거
 페이지 전체가 하나로 자연스럽게 스크롤되도록 변경</v>
+      </c>
+      <c r="D63" t="str">
+        <v/>
       </c>
     </row>
     <row r="64" xml:space="preserve">
@@ -1190,6 +1380,9 @@
 홈 화면의 결과 카드(이미지 저장/클립보드 복사)와 동일한 모달을 사용
 이미 플레이한 오늘의 인격을 다시 방문해도 공유 버튼이 유지됨</v>
       </c>
+      <c r="D64" t="str">
+        <v>정답을 맞히면 결과를 공유할 수 있는 버튼이 생깁니다.</v>
+      </c>
     </row>
     <row r="65" xml:space="preserve">
       <c r="A65" t="str">
@@ -1203,6 +1396,9 @@
 DATA 기반으로 키워드 목록을 동적으로 생성, 검색어/수감자 필터와 함께 적용
 없음 카드는 키워드 필터와 무관하게 항상 노출</v>
       </c>
+      <c r="D65" t="str">
+        <v>덱 빌더 후보 목록에 키워드 필터를 추가했습니다.</v>
+      </c>
     </row>
     <row r="66" xml:space="preserve">
       <c r="A66" t="str">
@@ -1216,6 +1412,9 @@
 정답 공개 시 자동 스크롤 후에도 공유 버튼이 바로 보이도록 개선
 일치/불일치/취소선 테스트 설명을 하단 추측 기록 카드로 이동</v>
       </c>
+      <c r="D66" t="str">
+        <v/>
+      </c>
     </row>
     <row r="67" xml:space="preserve">
       <c r="A67" t="str">
@@ -1228,6 +1427,9 @@
         <v xml:space="preserve">인격 맞추기: 키워드 불일치로 확정 제외된 키워드를 가진 후보도 취소선 처리
 제외된 후보(이름 기준 + 키워드 기준)는 드롭다운 하단으로 정렬
 재시작/다음 문제 시 제외 상태 초기화</v>
+      </c>
+      <c r="D67" t="str">
+        <v>인격 맞추기: 오답으로 확정된 후보는 취소선으로 표시하고 목록 아래로 정리됩니다.</v>
       </c>
     </row>
     <row r="68" xml:space="preserve">
@@ -1243,6 +1445,9 @@
 신규 인격 2종 추가(새벽 사무소 대표 그레고르, 새벽 사무소 해결사 파우스트)
 더 이상 쓰이지 않는 프로필(각성) 필드는 data.json에서 제거</v>
       </c>
+      <c r="D68" t="str">
+        <v>신규 인격 2종(새벽 사무소 대표 그레고르, 새벽 사무소 해결사 파우스트)이 추가되었습니다.</v>
+      </c>
     </row>
     <row r="69" xml:space="preserve">
       <c r="A69" t="str">
@@ -1255,6 +1460,9 @@
         <v xml:space="preserve">남부 리우 협회 3과 이상 각성 이미지 추가
 기존에는 일반 이미지가 각성 자리에도 임시로 들어가 있었는데 실제 각성 이미지로 교체</v>
       </c>
+      <c r="D69" t="str">
+        <v>일부 인격의 각성 이미지 오류를 수정했습니다.</v>
+      </c>
     </row>
     <row r="70" xml:space="preserve">
       <c r="A70" t="str">
@@ -1267,8 +1475,908 @@
         <v xml:space="preserve">덱 빌더: 좌측 인격 배치 순서 패널 고정(sticky) 다시 적용
 우측 후보 카드에 일반/각성 이미지 전환 버튼 추가(각성 이미지가 따로 있는 경우만 표시)</v>
       </c>
+      <c r="D70" t="str">
+        <v>덱 빌더 후보 카드에서 일반/각성 이미지를 전환해서 볼 수 있습니다.</v>
+      </c>
+    </row>
+    <row r="71" xml:space="preserve">
+      <c r="A71" t="str">
+        <v>v0.13.29</v>
+      </c>
+      <c r="B71" t="str">
+        <v>2026-07-10</v>
+      </c>
+      <c r="C71" t="str" xml:space="preserve">
+        <v xml:space="preserve">UpdateLog 시트 구조 변경(개발자용 Log/사용자용 Log 분리) 반영
+changelog.json은 사용자용 Log가 채워진 행만 포함하도록 빌드 스크립트 수정
+전체 버전이 담긴 changelog_dev.json은 dev/ 폴더에 생성하고 .vercelignore로 배포 제외</v>
+      </c>
+      <c r="D71" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:D71"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C70"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>버전</v>
+      </c>
+      <c r="B1" t="str">
+        <v>날짜</v>
+      </c>
+      <c r="C1" t="str">
+        <v>내용</v>
+      </c>
+    </row>
+    <row r="2" xml:space="preserve">
+      <c r="A2" t="str">
+        <v>v0.1.0</v>
+      </c>
+      <c r="B2" t="str">
+        <v>2026-06-30</v>
+      </c>
+      <c r="C2" t="str" xml:space="preserve">
+        <v xml:space="preserve">인격 두들 게임 최초 배포
+엑셀 기반 데이터 파이프라인 구축
+키워드 칩 가독성 개선 (고대비 색상)</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>v0.1.3</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-06-30</v>
+      </c>
+      <c r="C3" t="str">
+        <v>초기 안정화</v>
+      </c>
+    </row>
+    <row r="4" xml:space="preserve">
+      <c r="A4" t="str">
+        <v>v0.1.4</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-06-30</v>
+      </c>
+      <c r="C4" t="str" xml:space="preserve">
+        <v xml:space="preserve">폰트 크기 조정
+수감자별 컬러 도트 적용</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>v0.1.5</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-06-30</v>
+      </c>
+      <c r="C5" t="str">
+        <v>플레이 기록 UI 개선</v>
+      </c>
+    </row>
+    <row r="6" xml:space="preserve">
+      <c r="A6" t="str">
+        <v>v0.1.6</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-06-30</v>
+      </c>
+      <c r="C6" t="str" xml:space="preserve">
+        <v xml:space="preserve">필터 드롭다운 추가
+테이블 헤더 줄바꿈 방지
+화살표 스크롤 버그 수정</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>v0.1.7</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-06-30</v>
+      </c>
+      <c r="C7" t="str">
+        <v>최대 시도 횟수 5회 → 7회로 조정</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>v0.1.8</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-06-30</v>
+      </c>
+      <c r="C8" t="str">
+        <v>정답 인격 이미지 표시 추가</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>v0.1.9</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-06-30</v>
+      </c>
+      <c r="C9" t="str">
+        <v>소속1 / 소속2 필터·테이블·정답 표시 추가</v>
+      </c>
+    </row>
+    <row r="10" xml:space="preserve">
+      <c r="A10" t="str">
+        <v>v0.2.0</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-07-01</v>
+      </c>
+      <c r="C10" t="str" xml:space="preserve">
+        <v xml:space="preserve">일일 챌린지(오늘의 인격) 모드 추가
+파비콘 추가</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>v0.3.0</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-07-01</v>
+      </c>
+      <c r="C11" t="str">
+        <v>결과 카드 팝업 &amp; 홈 입장 페이지 추가</v>
+      </c>
+    </row>
+    <row r="12" xml:space="preserve">
+      <c r="A12" t="str">
+        <v>v0.3.1</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-07-01</v>
+      </c>
+      <c r="C12" t="str" xml:space="preserve">
+        <v xml:space="preserve">정답 이미지 일반/각성 토글 기능 추가
+정답 이미지 크기 확대
+스킬 퀴즈 신규 제작 (프로토타입)</v>
+      </c>
+    </row>
+    <row r="13" xml:space="preserve">
+      <c r="A13" t="str">
+        <v>v0.4.0</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-07-02</v>
+      </c>
+      <c r="C13" t="str" xml:space="preserve">
+        <v xml:space="preserve">스킬 퀴즈를 메인 페이지에 통합
+홈 화면에서 인격 두들 / 스킬 퀴즈 선택 가능</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>v0.4.1</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-07-02</v>
+      </c>
+      <c r="C14" t="str">
+        <v>버전 표시 갱신</v>
+      </c>
+    </row>
+    <row r="15" xml:space="preserve">
+      <c r="A15" t="str">
+        <v>v0.4.2</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2026-07-02</v>
+      </c>
+      <c r="C15" t="str" xml:space="preserve">
+        <v xml:space="preserve">결과 카드 정렬 및 이미지 표시 버그 수정
+홈 화면 게임 카드 높이 정렬
+스킬 퀴즈 카드에 NEW 배지 추가</v>
+      </c>
+    </row>
+    <row r="16" xml:space="preserve">
+      <c r="A16" t="str">
+        <v>v0.4.3</v>
+      </c>
+      <c r="B16" t="str">
+        <v>2026-07-02</v>
+      </c>
+      <c r="C16" t="str" xml:space="preserve">
+        <v xml:space="preserve">결과 카드 이미지/텍스트 확대
+필터를 상단 헤더로 분리하고 레이아웃 개선
+정답 선택 영역을 강조 박스로 분리</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>v0.4.4</v>
+      </c>
+      <c r="B17" t="str">
+        <v>2026-07-02</v>
+      </c>
+      <c r="C17" t="str">
+        <v>정답을 맞히면 컨페티 팡파레 애니메이션 재생</v>
+      </c>
+    </row>
+    <row r="18" xml:space="preserve">
+      <c r="A18" t="str">
+        <v>v0.4.5</v>
+      </c>
+      <c r="B18" t="str">
+        <v>2026-07-02</v>
+      </c>
+      <c r="C18" t="str" xml:space="preserve">
+        <v xml:space="preserve">정답 공개 영역에 자동 스크롤 추가
+성공/실패 카드형 강조 스타일 적용</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>v0.4.6</v>
+      </c>
+      <c r="B19" t="str">
+        <v>2026-07-02</v>
+      </c>
+      <c r="C19" t="str">
+        <v>정답 이미지 로드 완료 후 재스크롤하여 화면 중앙 정렬 보정</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>v0.4.7</v>
+      </c>
+      <c r="B20" t="str">
+        <v>2026-07-02</v>
+      </c>
+      <c r="C20" t="str">
+        <v>필터 항목을 수감자/성급 · 키워드 · 소속 세 그룹으로 나누고 구분선 추가</v>
+      </c>
+    </row>
+    <row r="21" xml:space="preserve">
+      <c r="A21" t="str">
+        <v>v0.5.0</v>
+      </c>
+      <c r="B21" t="str">
+        <v>2026-07-02</v>
+      </c>
+      <c r="C21" t="str" xml:space="preserve">
+        <v xml:space="preserve">업데이트 기록 보기 버튼 및 팝업 추가
+엑셀(UpdateLog.xlsx) 기반으로 업데이트 로그를 관리하고 자동 반영</v>
+      </c>
+    </row>
+    <row r="22" xml:space="preserve">
+      <c r="A22" t="str">
+        <v>v0.5.1</v>
+      </c>
+      <c r="B22" t="str">
+        <v>2026-07-02</v>
+      </c>
+      <c r="C22" t="str" xml:space="preserve">
+        <v xml:space="preserve">필터 라벨(수감자/성급/키워드/소속)에 아이콘 추가하고 글씨 크게 강조
+필터 그룹이 세 줄로 나뉘던 문제 수정, 한 줄에 표시되도록 개선</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>v0.5.2</v>
+      </c>
+      <c r="B23" t="str">
+        <v>2026-07-02</v>
+      </c>
+      <c r="C23" t="str">
+        <v>정답 공개, 스킬 퀴즈, 결과 카드에서 각성 이미지를 기본으로 표시하도록 변경 (각성 이미지가 없으면 일반 이미지로 대체)</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>v0.5.3</v>
+      </c>
+      <c r="B24" t="str">
+        <v>2026-07-02</v>
+      </c>
+      <c r="C24" t="str">
+        <v>CharacterTable.xlsx 스킬1/2/3 정보(명칭·속성·유형·아이콘) 최신화 반영</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>v0.5.4</v>
+      </c>
+      <c r="B25" t="str">
+        <v>2026-07-02</v>
+      </c>
+      <c r="C25" t="str">
+        <v>스킬 퀴즈 스테이지1에 스킬별 힌트 보기 / 정답 보기 버튼 추가</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>v0.5.5</v>
+      </c>
+      <c r="B26" t="str">
+        <v>2026-07-02</v>
+      </c>
+      <c r="C26" t="str">
+        <v>스킬 퀴즈 인격 이미지가 잘리던 문제 수정 (object-fit: cover → contain)</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>v0.5.6</v>
+      </c>
+      <c r="B27" t="str">
+        <v>2026-07-02</v>
+      </c>
+      <c r="C27" t="str">
+        <v>스킬 퀴즈 인격 이미지를 카드 상단 전체 폭으로 크게 확대 (520px)</v>
+      </c>
+    </row>
+    <row r="28" xml:space="preserve">
+      <c r="A28" t="str">
+        <v>v0.6.0</v>
+      </c>
+      <c r="B28" t="str">
+        <v>2026-07-02</v>
+      </c>
+      <c r="C28" t="str" xml:space="preserve">
+        <v xml:space="preserve">스킬 퀴즈 스테이지1에 포기하기 버튼 추가 (제출 왼쪽 배치)
+포기 시 이미 맞힌 속성/유형은 유지하고 틀리거나 미선택한 항목만 정답으로 채움
+결과 화면에 스킬별로 직접 맞힌 항목과 포기한 항목을 배지로 구분 표시, 전체 정답률 통계 추가</v>
+      </c>
+    </row>
+    <row r="29" xml:space="preserve">
+      <c r="A29" t="str">
+        <v>v0.6.1</v>
+      </c>
+      <c r="B29" t="str">
+        <v>2026-07-02</v>
+      </c>
+      <c r="C29" t="str" xml:space="preserve">
+        <v xml:space="preserve">인격 두들 정답 공개를 카드형 레이아웃으로 재구성
+인격명 카드는 수감자 컬러로 강조, 키워드는 색상 칩으로 표시</v>
+      </c>
+    </row>
+    <row r="30" xml:space="preserve">
+      <c r="A30" t="str">
+        <v>v0.6.2</v>
+      </c>
+      <c r="B30" t="str">
+        <v>2026-07-02</v>
+      </c>
+      <c r="C30" t="str" xml:space="preserve">
+        <v xml:space="preserve">CharacterTable.xlsx 이미지 URL 최신화 반영 (인격 이미지, 프로필, 스킬 아이콘)
+스킬1/2/3 아이콘이 동일하게 나오던 64개 인격 문제도 함께 해결됨</v>
+      </c>
+    </row>
+    <row r="31" xml:space="preserve">
+      <c r="A31" t="str">
+        <v>v0.7.0</v>
+      </c>
+      <c r="B31" t="str">
+        <v>2026-07-06</v>
+      </c>
+      <c r="C31" t="str" xml:space="preserve">
+        <v xml:space="preserve">덱 빌더 게임 신규 추가
+추천덱(엑셀 추천덱 시트)의 빈 슬롯에 인격을 드래그(또는 탭)해서 배치하는 게임
+워들 스타일 3색 판정(초록/노랑/빨강), 핵심/일반 슬롯 구분, 정답 보기 기능 지원
+데스크톱 드래그앤드롭과 모바일 탭-투-배치 모두 지원</v>
+      </c>
+    </row>
+    <row r="32" xml:space="preserve">
+      <c r="A32" t="str">
+        <v>v0.7.1</v>
+      </c>
+      <c r="B32" t="str">
+        <v>2026-07-06</v>
+      </c>
+      <c r="C32" t="str" xml:space="preserve">
+        <v xml:space="preserve">결과 카드에 정답 가리기(스포일러 방지) 토글 추가, 오늘의 인격은 기본으로 가려짐
+이미지 저장 시 CORS 문제로 인격 이미지가 비어보이던 버그 수정 (프록시 경유)
+클립보드에 카드 이미지를 바로 복사하는 기능 추가</v>
+      </c>
+    </row>
+    <row r="33" xml:space="preserve">
+      <c r="A33" t="str">
+        <v>v0.7.2</v>
+      </c>
+      <c r="B33" t="str">
+        <v>2026-07-06</v>
+      </c>
+      <c r="C33" t="str" xml:space="preserve">
+        <v xml:space="preserve">정답 가리기를 블러 대신 완전 비활성화(불투명 커버)로 변경
+가리기 상태에서 소속/키워드 정보도 함께 숨김 처리</v>
+      </c>
+    </row>
+    <row r="34" xml:space="preserve">
+      <c r="A34" t="str">
+        <v>v0.8.0</v>
+      </c>
+      <c r="B34" t="str">
+        <v>2026-07-06</v>
+      </c>
+      <c r="C34" t="str" xml:space="preserve">
+        <v xml:space="preserve">덱 빌더 게임을 완전히 새로 설계 (DeckData 시트 기반 2단계 게임)
+1단계: 수감자 12칸에 인격 배치(Main/Sub는 정답 인격, Null은 없음)
+2단계: 1단계 통과 후 Main 인격들의 전투 순서를 워들 스타일로 맞추기
+덱href 기준으로 그룹핑, ID 개수를 하드코딩하지 않고 동적으로 로드
+정답 보기(포기), 검색 필터, 드래그 앤 드롭+탭 배치 지원</v>
+      </c>
+    </row>
+    <row r="35" xml:space="preserve">
+      <c r="A35" t="str">
+        <v>v0.9.0</v>
+      </c>
+      <c r="B35" t="str">
+        <v>2026-07-06</v>
+      </c>
+      <c r="C35" t="str" xml:space="preserve">
+        <v xml:space="preserve">덱 빌더: DeckData 시트 업데이트 반영 (이름 매칭 문제 모두 해결됨)
+수감자 배치를 6x2 그리드로 변경
+인격 후보 목록에 수감자별 필터 탭 추가
+후보 카드 이미지를 4열 배치로 확대
+버그 수정: 이제 각 자리에는 그 수감자의 인격만 배치 가능
+인격 카드 더블클릭으로 자동 배치 지원 (보드 우선, 없으면 순서 칸)
+1단계(수감자 배치)와 2단계(전투 순서)를 한 화면으로 통합</v>
+      </c>
+    </row>
+    <row r="36" xml:space="preserve">
+      <c r="A36" t="str">
+        <v>v0.10.0</v>
+      </c>
+      <c r="B36" t="str">
+        <v>2026-07-06</v>
+      </c>
+      <c r="C36" t="str" xml:space="preserve">
+        <v xml:space="preserve">덱 빌더 게임 구조 재설계: 수감자별 고정 12칸 + 별도 순서칸을 없애고, 순서만 있는 통합 12칸 하나로 변경
+인격을 더블클릭(모바일은 탭)하면 가장 빠른 빈 칸에 자동 배치, 드래그로 자유롭게 순서 재배치 가능
+버그 수정: 더블클릭 미작동, 정답 덱 이름/설명이 화면에 노출되던 스포일러 문제, 빈 칸이 있어도 제출되던 문제 모두 해결
+같은 수감자 중복 배치 방지(없음 카드는 예외), 12칸을 모두 채워야 제출 버튼 활성화</v>
+      </c>
+    </row>
+    <row r="37" xml:space="preserve">
+      <c r="A37" t="str">
+        <v>v0.10.1</v>
+      </c>
+      <c r="B37" t="str">
+        <v>2026-07-06</v>
+      </c>
+      <c r="C37" t="str" xml:space="preserve">
+        <v xml:space="preserve">덱 빌더: "없음" 카드를 수감자별로 분리해 어떤 수감자를 없음으로 표시했는지 명확히 보여줌
+예: "없음" -&gt; "돈키호테 없음" 처럼 표시. 다른 수감자의 없음과 구분되고, 같은 수감자 중복 배치 방지 규칙도 없음 카드에 동일하게 적용됨</v>
+      </c>
+    </row>
+    <row r="38" xml:space="preserve">
+      <c r="A38" t="str">
+        <v>v0.11.0</v>
+      </c>
+      <c r="B38" t="str">
+        <v>2026-07-06</v>
+      </c>
+      <c r="C38" t="str" xml:space="preserve">
+        <v xml:space="preserve">덱 빌더: 후보 목록에서 이미 배치된 인격에 "체크 배치됨" 배지 표시
+전체 필터 탭 제거 (수감자별 탭만 남김)
+이미 배치된 수감자의 인격을 더블클릭하면 거부하지 않고 그 자리에 교체 배치
+상단에 "모두 비우기" 버튼 추가
+중간 슬롯 제거 시 뒤 슬롯들이 앞으로 당겨지도록 변경
+제출 후 정답(초록)인 슬롯은 고정되어 계속 유지되고, 순서만 틀린(노랑)/오답(빨강) 인격은 후보 목록에 다시 넣어도 표시가 남도록 변경, 오답은 이미지에 X 표시</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>v0.11.1</v>
+      </c>
+      <c r="B39" t="str">
+        <v>2026-07-06</v>
+      </c>
+      <c r="C39" t="str">
+        <v>덱 빌더: 후보 목록에서 "없음" 카드가 각 수감자 탭에서 항상 맨 앞에 오도록 정렬</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>v0.11.2</v>
+      </c>
+      <c r="B40" t="str">
+        <v>2026-07-06</v>
+      </c>
+      <c r="C40" t="str">
+        <v>덱 빌더: 수감자 필터 탭에 이미 배치된 수감자를 체크 표시(✓)와 초록 테두리로 표시</v>
+      </c>
+    </row>
+    <row r="41" xml:space="preserve">
+      <c r="A41" t="str">
+        <v>v0.12.0</v>
+      </c>
+      <c r="B41" t="str">
+        <v>2026-07-06</v>
+      </c>
+      <c r="C41" t="str" xml:space="preserve">
+        <v xml:space="preserve">덱 빌더: 12칸 슬롯 영역을 화면 상단에 고정(sticky), 후보 카드 목록을 스크롤해도 배치 결과를 계속 볼 수 있음
+안내문을 "❓ 도움말" 버튼으로 접어서 상단 공간 절약
+고정 영역에 배치 진행 상황(n/12) 표시 추가
+인격 배치 시 짧은 강조 애니메이션 + 하단 토스트 메시지("n번째 순서에 배치됨")로 스크롤 없이도 배치 결과 확인 가능
+모바일에서 12칸을 가로 스크롤 1줄로 배치해 세로 공간 절약</v>
+      </c>
+    </row>
+    <row r="42" xml:space="preserve">
+      <c r="A42" t="str">
+        <v>v0.13.0</v>
+      </c>
+      <c r="B42" t="str">
+        <v>2026-07-06</v>
+      </c>
+      <c r="C42" t="str" xml:space="preserve">
+        <v xml:space="preserve">CharacterTable DeckData 시트 업데이트 반영: 덱이 6개 → 8개로 증가 (약지 출충덱/거미집/중지덱/검계덱/흑수덱/혈귀/진침탕/W사)
+DeckData의 인격명 표기를 CharacterData와 일치하도록 정리 (하이픈/공백/로마숫자 표기 차이 20건 수정)
+수감자-인격명이 뒤바뀐 오류 1건, 이름 오탈자 2건, 이름 누락 2건 등 실제 데이터 불일치 수정
+Type 칸의 대소문자 표기 불일치(sub → Sub) 5건 수정 (판정 로직에서 정답으로 인식되지 않던 버그)</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>v0.13.1</v>
+      </c>
+      <c r="B43" t="str">
+        <v>2026-07-06</v>
+      </c>
+      <c r="C43" t="str">
+        <v>덱 빌더: 인격명 검색 결과가 없을 때 "해당 인격 없음" 메시지 표시</v>
+      </c>
+    </row>
+    <row r="44" xml:space="preserve">
+      <c r="A44" t="str">
+        <v>v0.13.2</v>
+      </c>
+      <c r="B44" t="str">
+        <v>2026-07-07</v>
+      </c>
+      <c r="C44" t="str" xml:space="preserve">
+        <v xml:space="preserve">덱 빌더 버그 수정: "없음" 카드를 먼저 배치하면 앞자리를 차지해 Main 정답 순서가 밀리던 문제 해결
+더블클릭 자동배치 시 "없음" 카드는 뒤쪽부터, 실제 인격은 앞쪽부터 채워지도록 분리
+Main 순서 판정을 절대 슬롯 위치가 아닌 배치된 Main 카드들끼리의 상대 순서로 비교하도록 개선
+(참고: "중지덱"의 순서값이 1,2,3,7로 비연속인 데이터 이슈 발견, DeckData 시트 확인 필요)</v>
+      </c>
+    </row>
+    <row r="45" xml:space="preserve">
+      <c r="A45" t="str">
+        <v>v0.13.3</v>
+      </c>
+      <c r="B45" t="str">
+        <v>2026-07-07</v>
+      </c>
+      <c r="C45" t="str" xml:space="preserve">
+        <v xml:space="preserve">덱 빌더 버그 수정: 인격명 검색 시 "없음" 카드가 검색어와 안 맞으면 함께 사라지던 문제 해결
+예: 로쟈 필터에서 "w사"로 검색해도 "로쟈 없음" 카드는 항상 표시됨 (없음은 이름 검색 대상에서 제외)</v>
+      </c>
+    </row>
+    <row r="46" xml:space="preserve">
+      <c r="A46" t="str">
+        <v>v0.13.4</v>
+      </c>
+      <c r="B46" t="str">
+        <v>2026-07-07</v>
+      </c>
+      <c r="C46" t="str" xml:space="preserve">
+        <v xml:space="preserve">덱 빌더: 검색창과 수감자 필터 태그를 12칸 슬롯 영역 바로 아래에 고정(sticky)
+후보 카드 목록을 스크롤해도 검색창/필터가 화면에 계속 보임
+12칸 영역의 실제 높이(도움말 열림/닫힘, 모바일 레이아웃 등)를 매번 동적으로 측정해 겹침 없이 정확히 이어붙도록 처리</v>
+      </c>
+    </row>
+    <row r="47" xml:space="preserve">
+      <c r="A47" t="str">
+        <v>v0.13.5</v>
+      </c>
+      <c r="B47" t="str">
+        <v>2026-07-07</v>
+      </c>
+      <c r="C47" t="str" xml:space="preserve">
+        <v xml:space="preserve">덱 빌더: 이중 스크롤 제거 + 제출 버튼 상단 고정
+후보 카드 목록의 자체 내부 스크롤(박스 안 스크롤)을 없애고 페이지 전체 스크롤 하나로 통일
+상단 고정 헤더에 제출 버튼 추가(진행률 표시: 제출 (N/12)), 하단 제출 버튼과 상태·클릭 동작 완전히 동기화되어 스크롤 안 해도 바로 제출 가능</v>
+      </c>
+    </row>
+    <row r="48" xml:space="preserve">
+      <c r="A48" t="str">
+        <v>v0.13.6</v>
+      </c>
+      <c r="B48" t="str">
+        <v>2026-07-07</v>
+      </c>
+      <c r="C48" t="str" xml:space="preserve">
+        <v xml:space="preserve">덱 빌더: 데스크톱(900px 이상) 좌우 분할 레이아웃 적용
+왼쪽 12칸 슬롯 패널 고정, 오른쪽 검색/후보 카드 영역 분리
+모바일/태블릿 레이아웃은 기존과 동일하게 유지</v>
+      </c>
+    </row>
+    <row r="49" xml:space="preserve">
+      <c r="A49" t="str">
+        <v>v0.13.7</v>
+      </c>
+      <c r="B49" t="str">
+        <v>2026-07-07</v>
+      </c>
+      <c r="C49" t="str" xml:space="preserve">
+        <v xml:space="preserve">덱 빌더: 데스크톱 분할 레이아웃에서 상단 메뉴/제출 버튼 배치 개선
+좁은 좌측 패널에서 헤더 버튼이 줄바꿈되던 문제 수정
+제출 버튼을 헤더 바로 아래로 이동, 슬롯 영역 내부 스크롤 제거</v>
+      </c>
+    </row>
+    <row r="50" xml:space="preserve">
+      <c r="A50" t="str">
+        <v>v0.13.8</v>
+      </c>
+      <c r="B50" t="str">
+        <v>2026-07-07</v>
+      </c>
+      <c r="C50" t="str" xml:space="preserve">
+        <v xml:space="preserve">덱 빌더: 상단 메뉴/제출 버튼을 화면 최상단 전체 너비 바로 이동
+좁은 좌측 패널 안에 있던 버튼들을 분리해 좌우 분할 시에도 넉넉하게 표시
+모바일에서 타이틀 텍스트가 세로로 깨지던 문제 수정</v>
+      </c>
+    </row>
+    <row r="51" xml:space="preserve">
+      <c r="A51" t="str">
+        <v>v0.13.9</v>
+      </c>
+      <c r="B51" t="str">
+        <v>2026-07-07</v>
+      </c>
+      <c r="C51" t="str" xml:space="preserve">
+        <v xml:space="preserve">덱 빌더: 우측 하단에 중복으로 떠 있던 제출 버튼 제거
+상단 제출 버튼을 매우 크게 강조 표시로 변경
+좌우 패널 비율을 300px 고정에서 50:50으로 변경, 카드/슬롯 확대</v>
+      </c>
+    </row>
+    <row r="52" xml:space="preserve">
+      <c r="A52" t="str">
+        <v>v0.13.10</v>
+      </c>
+      <c r="B52" t="str">
+        <v>2026-07-07</v>
+      </c>
+      <c r="C52" t="str" xml:space="preserve">
+        <v xml:space="preserve">덱 빌더: 아무 수감자의 없음 카드나 넣어도 정답 처리되던 채점 버그 수정
+없음 카드는 해당 슬롯이 요구하는 수감자와 일치할 때만 정답으로 인정</v>
+      </c>
+    </row>
+    <row r="53" xml:space="preserve">
+      <c r="A53" t="str">
+        <v>v0.13.11</v>
+      </c>
+      <c r="B53" t="str">
+        <v>2026-07-07</v>
+      </c>
+      <c r="C53" t="str" xml:space="preserve">
+        <v xml:space="preserve">Main 카드 하나만 배치해도 정답으로 잠기던 채점/잠금 버그 수정
+Main 슬롯은 덱이 요구하는 Main 전원이 동시에 정답일 때만 잠기도록 변경
+다른 Main 배치가 바뀌면 이전에 맞았던 자리가 다시 틀릴 수 있어 섣불리 잠그지 않게 함</v>
+      </c>
+    </row>
+    <row r="54" xml:space="preserve">
+      <c r="A54" t="str">
+        <v>v0.13.12</v>
+      </c>
+      <c r="B54" t="str">
+        <v>2026-07-07</v>
+      </c>
+      <c r="C54" t="str" xml:space="preserve">
+        <v xml:space="preserve">덱 빌더: 인격 배치 후 배치되지 않은 다음 수감자로 자동 전환
+드래그, 더블클릭/탭, 교체 배치 모두에서 동일하게 동작</v>
+      </c>
+    </row>
+    <row r="55" xml:space="preserve">
+      <c r="A55" t="str">
+        <v>v0.13.13</v>
+      </c>
+      <c r="B55" t="str">
+        <v>2026-07-07</v>
+      </c>
+      <c r="C55" t="str" xml:space="preserve">
+        <v xml:space="preserve">덱 빌더: 채점 방식을 절대 위치 기준으로 전면 변경
+Main 인격은 반드시 정답 순서 번호(order) 슬롯에 있어야 정답 처리
+Sub 인격은 위치 무관, 없음 카드는 뒤쪽 슬롯으로 자동 정렬
+제출 시 정답으로 확인된 카드를 올바른 자리로 자동 재배치 후 고정(영구 잠김 충돌 방지)</v>
+      </c>
+    </row>
+    <row r="56" xml:space="preserve">
+      <c r="A56" t="str">
+        <v>v0.13.14</v>
+      </c>
+      <c r="B56" t="str">
+        <v>2026-07-08</v>
+      </c>
+      <c r="C56" t="str" xml:space="preserve">
+        <v xml:space="preserve">덱 빌더: 제출 시 자동 재배치 기능 제거, 워들 방식 채점으로 변경
+놓인 자리 그대로 채점: Main은 정답 순서 칸이 아니면 노랑, 없음은 뒤쪽 구간 밖이면 노랑
+Sub는 기존처럼 위치 무관하게 정답 인격만 있으면 초록</v>
+      </c>
+    </row>
+    <row r="57" xml:space="preserve">
+      <c r="A57" t="str">
+        <v>v0.13.15</v>
+      </c>
+      <c r="B57" t="str">
+        <v>2026-07-08</v>
+      </c>
+      <c r="C57" t="str" xml:space="preserve">
+        <v xml:space="preserve">덱 빌더: 카드 하나 제거 시 다른 칸들의 채점 표시가 전부 지워지던 버그 수정
+제거한 슬롯 하나만 비우고, 나머지 칸의 정답/오답 표시는 그대로 유지</v>
+      </c>
+    </row>
+    <row r="58" xml:space="preserve">
+      <c r="A58" t="str">
+        <v>v0.13.16</v>
+      </c>
+      <c r="B58" t="str">
+        <v>2026-07-08</v>
+      </c>
+      <c r="C58" t="str" xml:space="preserve">
+        <v xml:space="preserve">덱 빌더: Sub/없음이 Main 전용 자리를 차지해 잠기던 버그 수정
+Sub나 없음이 어떤 Main의 정답 순서 칸(order 자리)에 있으면 노랑(순서 다름) 처리
+해당 자리를 비워줘야 그 Main이 정상적으로 정답 처리될 수 있음</v>
+      </c>
+    </row>
+    <row r="59" xml:space="preserve">
+      <c r="A59" t="str">
+        <v>v0.13.17</v>
+      </c>
+      <c r="B59" t="str">
+        <v>2026-07-08</v>
+      </c>
+      <c r="C59" t="str" xml:space="preserve">
+        <v xml:space="preserve">인격 이미지(일반/각성) 및 스킬 아이콘을 로컬 파일로 교체
+외부 CDN 대신 프로젝트 내 이미지를 사용해 로딩 안정성 향상</v>
+      </c>
+    </row>
+    <row r="60" xml:space="preserve">
+      <c r="A60" t="str">
+        <v>v0.13.18</v>
+      </c>
+      <c r="B60" t="str">
+        <v>2026-07-08</v>
+      </c>
+      <c r="C60" t="str" xml:space="preserve">
+        <v xml:space="preserve">CharacterTable에 ID열(A열) 추가
+인격 고유 번호를 데이터에 노출해 추후 참조/매칭에 사용할 수 있도록 함</v>
+      </c>
+    </row>
+    <row r="61" xml:space="preserve">
+      <c r="A61" t="str">
+        <v>v0.13.19</v>
+      </c>
+      <c r="B61" t="str">
+        <v>2026-07-08</v>
+      </c>
+      <c r="C61" t="str" xml:space="preserve">
+        <v xml:space="preserve">덱 빌더: 클리어/포기 결과 패널을 하단에서 상단(제출 버튼 아래)으로 이동
+결과 패널의 홈으로 버튼 제거(좌측 상단 홈으로 버튼과 중복이라 제거, 다음 덱만 남김)</v>
+      </c>
+    </row>
+    <row r="62" xml:space="preserve">
+      <c r="A62" t="str">
+        <v>v0.13.20</v>
+      </c>
+      <c r="B62" t="str">
+        <v>2026-07-08</v>
+      </c>
+      <c r="C62" t="str" xml:space="preserve">
+        <v xml:space="preserve">decks.json 빌드 스크립트를 DeckInfo 시트와 조인하도록 재작성
+DeckData의 Deck 컬럼이 삭제되면서 배포판 덱 이름이 빈 값으로 나오던 버그 수정
+덱 키워드(deckKeywords.json) 빌드 결과물 신규 추가(향후 힌트 기능용)</v>
+      </c>
+    </row>
+    <row r="63" xml:space="preserve">
+      <c r="A63" t="str">
+        <v>v0.13.21</v>
+      </c>
+      <c r="B63" t="str">
+        <v>2026-07-08</v>
+      </c>
+      <c r="C63" t="str" xml:space="preserve">
+        <v xml:space="preserve">덱 빌더: 왼쪽 슬롯 패널의 고정(sticky) 스크롤 제거
+페이지 전체가 하나로 자연스럽게 스크롤되도록 변경</v>
+      </c>
+    </row>
+    <row r="64" xml:space="preserve">
+      <c r="A64" t="str">
+        <v>v0.13.22</v>
+      </c>
+      <c r="B64" t="str">
+        <v>2026-07-09</v>
+      </c>
+      <c r="C64" t="str" xml:space="preserve">
+        <v xml:space="preserve">오늘의 인격/랜덤 플레이에서 정답을 맞히면 공유하기 버튼 표시
+홈 화면의 결과 카드(이미지 저장/클립보드 복사)와 동일한 모달을 사용
+이미 플레이한 오늘의 인격을 다시 방문해도 공유 버튼이 유지됨</v>
+      </c>
+    </row>
+    <row r="65" xml:space="preserve">
+      <c r="A65" t="str">
+        <v>v0.13.23</v>
+      </c>
+      <c r="B65" t="str">
+        <v>2026-07-09</v>
+      </c>
+      <c r="C65" t="str" xml:space="preserve">
+        <v xml:space="preserve">덱 빌더: 후보 인격 목록에 키워드 필터 추가(다중 선택, AND 조건)
+DATA 기반으로 키워드 목록을 동적으로 생성, 검색어/수감자 필터와 함께 적용
+없음 카드는 키워드 필터와 무관하게 항상 노출</v>
+      </c>
+    </row>
+    <row r="66" xml:space="preserve">
+      <c r="A66" t="str">
+        <v>v0.13.24</v>
+      </c>
+      <c r="B66" t="str">
+        <v>2026-07-09</v>
+      </c>
+      <c r="C66" t="str" xml:space="preserve">
+        <v xml:space="preserve">오늘의 인격/랜덤 플레이: 공유하기 버튼을 정답 카드 안으로 이동
+정답 공개 시 자동 스크롤 후에도 공유 버튼이 바로 보이도록 개선
+일치/불일치/취소선 테스트 설명을 하단 추측 기록 카드로 이동</v>
+      </c>
+    </row>
+    <row r="67" xml:space="preserve">
+      <c r="A67" t="str">
+        <v>v0.13.25</v>
+      </c>
+      <c r="B67" t="str">
+        <v>2026-07-09</v>
+      </c>
+      <c r="C67" t="str" xml:space="preserve">
+        <v xml:space="preserve">인격 맞추기: 키워드 불일치로 확정 제외된 키워드를 가진 후보도 취소선 처리
+제외된 후보(이름 기준 + 키워드 기준)는 드롭다운 하단으로 정렬
+재시작/다음 문제 시 제외 상태 초기화</v>
+      </c>
+    </row>
+    <row r="68" xml:space="preserve">
+      <c r="A68" t="str">
+        <v>v0.13.26</v>
+      </c>
+      <c r="B68" t="str">
+        <v>2026-07-09</v>
+      </c>
+      <c r="C68" t="str" xml:space="preserve">
+        <v xml:space="preserve">CharacterTable.xlsx 구조 변경(스킬 데이터 SkillData 시트로 분리) 반영
+CharacterData+SkillData를 ID로 조인해 data.json 생성하도록 빌드 스크립트 수정
+신규 인격 2종 추가(새벽 사무소 대표 그레고르, 새벽 사무소 해결사 파우스트)
+더 이상 쓰이지 않는 프로필(각성) 필드는 data.json에서 제거</v>
+      </c>
+    </row>
+    <row r="69" xml:space="preserve">
+      <c r="A69" t="str">
+        <v>v0.13.27</v>
+      </c>
+      <c r="B69" t="str">
+        <v>2026-07-10</v>
+      </c>
+      <c r="C69" t="str" xml:space="preserve">
+        <v xml:space="preserve">남부 리우 협회 3과 이상 각성 이미지 추가
+기존에는 일반 이미지가 각성 자리에도 임시로 들어가 있었는데 실제 각성 이미지로 교체</v>
+      </c>
+    </row>
+    <row r="70" xml:space="preserve">
+      <c r="A70" t="str">
+        <v>v0.13.28</v>
+      </c>
+      <c r="B70" t="str">
+        <v>2026-07-10</v>
+      </c>
+      <c r="C70" t="str" xml:space="preserve">
+        <v xml:space="preserve">덱 빌더: 좌측 인격 배치 순서 패널 고정(sticky) 다시 적용
+우측 후보 카드에 일반/각성 이미지 전환 버튼 추가(각성 이미지가 따로 있는 경우만 표시)</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C70"/>
   </ignoredErrors>

--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D72"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1495,9 +1495,24 @@
         <v/>
       </c>
     </row>
+    <row r="72" xml:space="preserve">
+      <c r="A72" t="str">
+        <v>v0.13.30</v>
+      </c>
+      <c r="B72" t="str">
+        <v>2026-07-10</v>
+      </c>
+      <c r="C72" t="str" xml:space="preserve">
+        <v xml:space="preserve">.vercelignore는 빌드 중 새로 생성되는 파일에는 적용되지 않아 changelog_dev.json이 실제로는 공개 배포되고 있던 것을 발견하고 수정
+Vercel 빌드 환경(VERCEL=1)에서는 changelog_dev.json 자체를 생성하지 않도록 변경, 로컬에서는 그대로 생성됨</v>
+      </c>
+      <c r="D72" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D71"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D72"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D72"/>
+  <dimension ref="A1:D73"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1510,9 +1510,25 @@
         <v/>
       </c>
     </row>
+    <row r="73" xml:space="preserve">
+      <c r="A73" t="str">
+        <v>v0.13.31</v>
+      </c>
+      <c r="B73" t="str">
+        <v>2026-07-10</v>
+      </c>
+      <c r="C73" t="str" xml:space="preserve">
+        <v xml:space="preserve">덱 빌더 후보 카드의 일반/각성 이미지 토글 버튼이 draggable=true인 .db-candidate 내부에 중첩돼 있어, 실제 마우스 클릭 시 브라우저 네이티브 드래그 인식이 클릭 이벤트를 가로채 onclick이 발동하지 않던 문제 확인
+토글 버튼에 draggable=false 추가 + dbCandidatesEl dragstart 위임 핸들러에서 토글 버튼 기준 e.preventDefault()+return 가드 추가로 수정
+합성 클릭(.click())으로는 재현이 안 되고 실제 마우스 클릭에서만 재현되는 이슈였음(dispatchEvent로 mousedown/mouseup/click 시퀀스 재현해 수정 확인)</v>
+      </c>
+      <c r="D73" t="str">
+        <v>덱 빌더 후보 카드의 일반/각성 이미지 전환 버튼이 클릭해도 작동하지 않던 문제를 수정했습니다.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D72"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D73"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D73"/>
+  <dimension ref="A1:D74"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1526,9 +1526,26 @@
         <v>덱 빌더 후보 카드의 일반/각성 이미지 전환 버튼이 클릭해도 작동하지 않던 문제를 수정했습니다.</v>
       </c>
     </row>
+    <row r="74" xml:space="preserve">
+      <c r="A74" t="str">
+        <v>v0.13.32</v>
+      </c>
+      <c r="B74" t="str">
+        <v>2026-07-10</v>
+      </c>
+      <c r="C74" t="str" xml:space="preserve">
+        <v xml:space="preserve">오늘의 인격/랜덤 플레이/스킬 퀴즈/덱 빌더 각각에 흩어져 있던 개별 이미지 토글(및 조건부로만 노출되던 덱 빌더 후보 카드별 토글)을 전부 제거
+화면 전체가 공유하는 전역 상태 preferAwaken + pickIdImg(row) 헬퍼로 통합
+각 화면 상단(탭바/sq-header/db-header)에 토글 버튼 1개씩 배치, toggleImagePref(rerenderFn)로 각 화면 자체 재렌더 함수 호출
+덱 빌더 후보 카드용 draggable=false 가드/전용 CSS 등 관련 죽은 코드 정리</v>
+      </c>
+      <c r="D74" t="str">
+        <v>오늘의 인격/랜덤 플레이/스킬 퀴즈/덱 빌더 화면 상단에 일반/각성 이미지 전환 버튼을 하나로 통일했습니다.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D73"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D74"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D74"/>
+  <dimension ref="A1:D75"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1543,9 +1543,24 @@
         <v>오늘의 인격/랜덤 플레이/스킬 퀴즈/덱 빌더 화면 상단에 일반/각성 이미지 전환 버튼을 하나로 통일했습니다.</v>
       </c>
     </row>
+    <row r="75" xml:space="preserve">
+      <c r="A75" t="str">
+        <v>v0.13.33</v>
+      </c>
+      <c r="B75" t="str">
+        <v>2026-07-10</v>
+      </c>
+      <c r="C75" t="str" xml:space="preserve">
+        <v xml:space="preserve">updateImgPrefButtons() 추가: preferAwaken 상태에 따라 .img-pref-toggle-btn 3개(게임/스킬퀴즈/덱빌더) 전부의 active 클래스와 라벨을 동기화
+toggleImagePref()에서 상태 변경 직후 updateImgPrefButtons() 호출, 페이지 최초 로드 시에도 1회 호출해 초기 라벨 반영</v>
+      </c>
+      <c r="D75" t="str">
+        <v>일반/각성 이미지 전환 버튼이 눌러도 안 바뀌는 것처럼 보이던 문제 수정: 버튼이 현재 선택된 모드를 표시하는 토글 버튼(강조 표시)으로 바뀌었습니다.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D74"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D75"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D75"/>
+  <dimension ref="A1:D76"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1558,9 +1558,24 @@
         <v>일반/각성 이미지 전환 버튼이 눌러도 안 바뀌는 것처럼 보이던 문제 수정: 버튼이 현재 선택된 모드를 표시하는 토글 버튼(강조 표시)으로 바뀌었습니다.</v>
       </c>
     </row>
+    <row r="76" xml:space="preserve">
+      <c r="A76" t="str">
+        <v>v0.13.34</v>
+      </c>
+      <c r="B76" t="str">
+        <v>2026-07-10</v>
+      </c>
+      <c r="C76" t="str" xml:space="preserve">
+        <v xml:space="preserve">CharacterTable 이미지(각성) 컬럼 파일명 수정(일반→awaken)을 data.json에 재반영
+build-data.js에 imageFileExists() 가드 추가: 각성 이미지 경로가 로컬에 실제 파일로 존재하지 않으면 빈 값 처리 (1성/LCB 수감자 12명은 각성 이미지가 원래 없어 엑셀 값이 존재하지 않는 파일을 가리켰음)</v>
+      </c>
+      <c r="D76" t="str">
+        <v>각성 이미지 표시 데이터를 최신 상태로 갱신했습니다. 원래 각성 이미지가 없는 1성 인격은 일반 이미지로 자동 표시됩니다.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D75"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D76"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D76"/>
+  <dimension ref="A1:D77"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1573,9 +1573,27 @@
         <v>각성 이미지 표시 데이터를 최신 상태로 갱신했습니다. 원래 각성 이미지가 없는 1성 인격은 일반 이미지로 자동 표시됩니다.</v>
       </c>
     </row>
+    <row r="77" xml:space="preserve">
+      <c r="A77" t="str">
+        <v>v0.13.35</v>
+      </c>
+      <c r="B77" t="str">
+        <v>2026-07-11</v>
+      </c>
+      <c r="C77" t="str" xml:space="preserve">
+        <v xml:space="preserve">탭바/헤더에 있던 3개 img-pref-toggle-btn 제거, 각 화면의 실제 이미지 렌더링 템플릿(buildEndMessage/.answer-img-area, sqIdentityCardHTML/.sq-img-wrap, sqRenderResult/.sq-result-img) 안에 오버레이 버튼으로 이동
+덱빌더는 dbRenderSlots가 재작성하지 않는 정적 래퍼 .db-slots-section에 고정 배치 (position:relative 추가)
+toggleImagePref()의 updateImgPrefButtons() 호출 순서를 rerenderFn() 이후로 변경 (innerHTML로 버튼이 재생성되는 화면에서 상태 동기화 안 되던 버그 수정), 각 최초 렌더 지점에도 updateImgPrefButtons() 추가 호출
+버튼을 아이콘 전용(☀️/🌙, title 툴팁)으로 축소, .img-pref-toggle-btn CSS를 절대위치 오버레이 원형 버튼으로 재정의
+스킬 퀴즈 결과 화면(.sq-result-img)에도 refreshSqResultImage() 헬퍼와 함께 버튼 추가 (기존엔 헤더 버튼으로 커버되던 부분, 헤더 버튼 제거로 인한 회귀 방지)</v>
+      </c>
+      <c r="D77" t="str">
+        <v>일반/각성 이미지 전환 버튼을 탭 메뉴에서 이미지 위 작은 아이콘 버튼으로 옮겼습니다. 이미지가 있을 때만 이미지 모서리에 나타납니다.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D76"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D77"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D77"/>
+  <dimension ref="A1:D78"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1591,9 +1591,24 @@
         <v>일반/각성 이미지 전환 버튼을 탭 메뉴에서 이미지 위 작은 아이콘 버튼으로 옮겼습니다. 이미지가 있을 때만 이미지 모서리에 나타납니다.</v>
       </c>
     </row>
+    <row r="78" xml:space="preserve">
+      <c r="A78" t="str">
+        <v>v0.13.36</v>
+      </c>
+      <c r="B78" t="str">
+        <v>2026-07-10</v>
+      </c>
+      <c r="C78" t="str" xml:space="preserve">
+        <v xml:space="preserve">일반/각성 토글 버튼을 해/달 이모지 아이콘에서 실제 스위치(pill+슬라이딩 노브) 비주얼 + 텍스트 라벨(일반/각성)로 교체
+updateImgPrefButtons()가 버튼 textContent 전체를 덮어쓰던 방식에서 .img-pref-label 자식 요소만 갱신하도록 변경(스위치 span 보존)</v>
+      </c>
+      <c r="D78" t="str">
+        <v>일반/각성 이미지 전환 버튼을 스위치 모양으로 바꾸고, 현재 어떤 이미지가 표시 중인지 글자로 표시했습니다.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D77"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D78"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D78"/>
+  <dimension ref="A1:D79"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1606,9 +1606,25 @@
         <v>일반/각성 이미지 전환 버튼을 스위치 모양으로 바꾸고, 현재 어떤 이미지가 표시 중인지 글자로 표시했습니다.</v>
       </c>
     </row>
+    <row r="79" xml:space="preserve">
+      <c r="A79" t="str">
+        <v>v0.13.37</v>
+      </c>
+      <c r="B79" t="str">
+        <v>2026-07-16</v>
+      </c>
+      <c r="C79" t="str" xml:space="preserve">
+        <v xml:space="preserve">DeckData 시트의 인격명 컬럼이 문자열에서 CharacterData ID 참조(숫자)로 구조 변경됨에 따라, build-decks.js의 기존 퍼지 이름 매칭 로직이 전부 실패해 decks.json에 인격명 대신 ID 숫자가 그대로 들어가던 문제 발견 및 수정
+resolveName()을 ID 기반 조회(charById Map)로 재작성, 조회 실패 시 DeckData의 info 컬럼(참고용 이름)으로 폴백
+8개 덱 전체 재검증, 매칭 실패 0건 확인</v>
+      </c>
+      <c r="D79" t="str">
+        <v>덱 빌더에서 일부 인격 이름이 숫자로 잘못 표시되던 문제를 수정했습니다.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D78"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D79"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D79"/>
+  <dimension ref="A1:D80"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1622,9 +1622,23 @@
         <v>덱 빌더에서 일부 인격 이름이 숫자로 잘못 표시되던 문제를 수정했습니다.</v>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>v0.13.38</v>
+      </c>
+      <c r="B80" t="str">
+        <v>2026-07-16</v>
+      </c>
+      <c r="C80" t="str">
+        <v>CharacterTable.xlsx DeckData 시트 콘텐츠 갱신(혈귀덱 이스마엘/히스클리프 없음 처리, 진침탕덱 구성 변경)을 반영한 원본 엑셀 파일 커밋. decks.json/changelog.json은 이전 커밋에서 이미 이 변경사항 기준으로 재생성되어 라이브에 반영되어 있었음(diff 없음 확인) — 소스 엑셀만 뒤늦게 커밋. ID 조회/순서 검증 재확인, 8개 덱 전부 오류 없음.</v>
+      </c>
+      <c r="D80" t="str">
+        <v>혈귀덱과 진침탕덱의 인격 구성이 조정되었습니다.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D79"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D80"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D80"/>
+  <dimension ref="A1:D81"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1636,9 +1636,25 @@
         <v>혈귀덱과 진침탕덱의 인격 구성이 조정되었습니다.</v>
       </c>
     </row>
+    <row r="81" xml:space="preserve">
+      <c r="A81" t="str">
+        <v>v0.13.39</v>
+      </c>
+      <c r="B81" t="str">
+        <v>2026-07-16</v>
+      </c>
+      <c r="C81" t="str" xml:space="preserve">
+        <v xml:space="preserve">덱 빌더 일반/각성 토글 버튼이 .db-slots-section에 position:absolute(top:38px)로 배치돼 있어 board-grid 첫 줄과 겹치던 문제 수정 - .db-slots-label의 3번째 flex 자식으로 이동시키고 .img-pref-toggle-btn.inline 모디파이어(position:static)로 정상 문서 흐름에 배치
+덱 빌더 명칭을 사용자에게 퀴즈 모드임이 더 잘 드러나도록 덱 빌더에서 덱 퀴즈로 변경(홈 화면 그룹 라벨/카드 타이틀, 화면 내 제목). 내부 함수/변수/CSS 클래스(db- 접두사)는 변경하지 않음</v>
+      </c>
+      <c r="D81" t="str" xml:space="preserve">
+        <v xml:space="preserve">덱 빌더에서 일반/각성 전환 버튼이 슬롯과 겹쳐 보이던 문제를 수정했습니다.
+덱 빌더를 덱 퀴즈로 이름을 바꿨습니다.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D80"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D81"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D81"/>
+  <dimension ref="A1:D82"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1652,9 +1652,25 @@
 덱 빌더를 덱 퀴즈로 이름을 바꿨습니다.</v>
       </c>
     </row>
+    <row r="82" xml:space="preserve">
+      <c r="A82" t="str">
+        <v>v0.13.40</v>
+      </c>
+      <c r="B82" t="str">
+        <v>2026-07-16</v>
+      </c>
+      <c r="C82" t="str" xml:space="preserve">
+        <v xml:space="preserve">덱 퀴즈: .db-slots-label/.db-slots-progress/.img-pref-toggle-btn 폰트 크기 상향(13-12px -&gt; 15-14px), 버튼 높이도 비례 조정
+키워드 필터 다중 선택 누적으로 인한 불편 개선: 키워드가 1개 이상 선택되면 .db-keyword-filter-clear(초기화) 버튼이 나타나서 한 번에 전체 해제 가능하도록 dbRenderKeywordFilter()/클릭 핸들러 수정</v>
+      </c>
+      <c r="D82" t="str" xml:space="preserve">
+        <v xml:space="preserve">덱 퀴즈: 일부 글자 크기를 키웠습니다.
+덱 퀴즈: 키워드 필터에 초기화 버튼을 추가해 여러 개 선택했을 때 한 번에 해제할 수 있게 했습니다.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D81"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D82"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\imtl\limquiz\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C699661-20A3-4F15-A519-A28043E714ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13CE813B-87EF-4AB6-9CC2-CF4E9C3EA8EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="690" yWindow="870" windowWidth="28830" windowHeight="14730" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="244">
   <si>
     <t>버전</t>
   </si>
@@ -879,6 +879,20 @@
 정답이 유출될 수 있던 문제를 수정했습니다.
 오늘의 인격 선정 방식이 개선되었습니다. (7월 16일의 정답이 변경될 수 있습니다)</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v0.13.42</t>
+  </si>
+  <si>
+    <t>덱 퀴즈 판정 버그 수정: Sub 인격이 없음 전용 뒤쪽 구간(마지막 N칸)에 배치돼도 초록 판정·잠금되어 없음 카드 자리가 부족해져 클리어 불가능해지던 문제. dbJudgeDeck에서 Sub가 nullZoneStart 이상 슬롯에 있으면 yellow 처리
+build-decks.js에 Main 순서가 없음 전용 구간과 겹치는 덱 경고 추가 (클리어 불가 데이터 사전 감지)
+덱 퀴즈 후보 목록을 한 줄 6개(grid 6열)로 변경 (기존 4열), gap 14→10px
+판정 표시 가시성 강화: judged-green/yellow/red를 3px 밝은 테두리(#4ade80/#facc15/#f87171)+글로우로 교체, 초록 '✓ 정답'/노랑 '순서 다름' 좌상단 배지(.db-slot-judge-badge) 추가</t>
+  </si>
+  <si>
+    <t>덱 퀴즈: 인격 목록이 한 줄에 6개씩 표시됩니다.
+덱 퀴즈: 특정 배치에서 클리어가 불가능해지던 판정 오류를 수정했습니다.
+덱 퀴즈: 제출 후 정답(초록)/순서 다름(노랑) 표시가 훨씬 잘 보이도록 개선했습니다.</t>
   </si>
 </sst>
 </file>
@@ -1266,7 +1280,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D83"/>
+  <dimension ref="A1:D84"/>
   <sheetFormatPr defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -2429,6 +2443,20 @@
       </c>
       <c r="D83" s="1" t="s">
         <v>240</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>241</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>243</v>
       </c>
     </row>
   </sheetData>

--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\imtl\limquiz\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13CE813B-87EF-4AB6-9CC2-CF4E9C3EA8EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ABA3F97-A313-4863-9E9C-A07165A9435B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="690" yWindow="870" windowWidth="28830" windowHeight="14730" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="247">
   <si>
     <t>버전</t>
   </si>
@@ -893,6 +893,20 @@
     <t>덱 퀴즈: 인격 목록이 한 줄에 6개씩 표시됩니다.
 덱 퀴즈: 특정 배치에서 클리어가 불가능해지던 판정 오류를 수정했습니다.
 덱 퀴즈: 제출 후 정답(초록)/순서 다름(노랑) 표시가 훨씬 잘 보이도록 개선했습니다.</t>
+  </si>
+  <si>
+    <t>v0.13.43</t>
+  </si>
+  <si>
+    <t>덱 퀴즈 데스크톱 레이아웃 확대: .db-wrap/.db-top-bar max-width 1300→1560px, 후보 패널 flex 1→1.2 (인격 카드 약 25% 확대)
+dbClearAll이 노랑(순서 다름) 판정 슬롯은 유지하고 오답(빨강)·미판정 배치만 비우도록 변경, 버튼명 "모두 비우기"→"오답 비우기" + title 툴팁
+슬롯 점선 힌트 추가: 판정 전(j=null) 슬롯이라도 dbKnownJudge에 기록된 이전 제출 판정이 있으면 노랑 점선 "🟡 인격 맞음"/빨강 점선 "✕ 오답 인격" 배지 표시 (.db-slot.known-yellow/.known-red, .db-slot-judge-badge.red) - 노랑 인격을 옮기면 판정 표시가 전부 사라져 헷갈린다는 피드백 대응
+도움말에 점선 힌트·오답 비우기 동작 설명 추가</t>
+  </si>
+  <si>
+    <t>덱 퀴즈: 넓은 화면에서 인격 카드가 더 크게 표시됩니다.
+덱 퀴즈: "오답 비우기"가 노랑(순서 다름) 인격은 남기고 오답과 미판정 배치만 비웁니다.
+덱 퀴즈: 노랑 판정 인격을 다른 자리로 옮겨도 노란 점선 "인격 맞음" 표시가 유지됩니다.</t>
   </si>
 </sst>
 </file>
@@ -1280,7 +1294,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D84"/>
+  <dimension ref="A1:D85"/>
   <sheetFormatPr defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -2457,6 +2471,20 @@
       </c>
       <c r="D84" s="1" t="s">
         <v>243</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>244</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
   </sheetData>

--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\imtl\limquiz\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ABA3F97-A313-4863-9E9C-A07165A9435B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F7BF824-0C76-4B46-B924-B1E5190EE16E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="690" yWindow="870" windowWidth="28830" windowHeight="14730" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="250">
   <si>
     <t>버전</t>
   </si>
@@ -907,6 +907,18 @@
     <t>덱 퀴즈: 넓은 화면에서 인격 카드가 더 크게 표시됩니다.
 덱 퀴즈: "오답 비우기"가 노랑(순서 다름) 인격은 남기고 오답과 미판정 배치만 비웁니다.
 덱 퀴즈: 노랑 판정 인격을 다른 자리로 옮겨도 노란 점선 "인격 맞음" 표시가 유지됩니다.</t>
+  </si>
+  <si>
+    <t>v0.13.44</t>
+  </si>
+  <si>
+    <t>preferAwaken 기본값 true로 변경 (각성 이미지 우선, 없으면 pickIdImg가 일반으로 폴백)
+sqRenderResult 후 updateImgPrefButtons() 호출 추가 (결과 화면 토글 라벨이 실제 상태와 어긋나던 기존 누락 수정)
+덱 퀴즈 후보 더블클릭을 네이티브 dblclick 이벤트에서 자체 감지(같은 카드 key를 450ms 내 2회 클릭)로 교체 - 배치 직후 dbRenderCandidates()의 innerHTML 교체로 브라우저 클릭 카운터가 무효화되어 마우스를 움직이지 않으면 연속 더블클릭이 인식되지 않던 문제 해결. 터치 기기는 기존 싱글탭 유지</t>
+  </si>
+  <si>
+    <t>인격 이미지가 기본으로 각성 일러스트로 표시됩니다. (토글 버튼으로 일반 전환 가능)
+덱 퀴즈: 인격 배치 후 마우스를 움직이지 않고 바로 더블클릭해도 정상적으로 배치되도록 수정했습니다.</t>
   </si>
 </sst>
 </file>
@@ -1294,7 +1306,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D85"/>
+  <dimension ref="A1:D86"/>
   <sheetFormatPr defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -2485,6 +2497,20 @@
       </c>
       <c r="D85" s="1" t="s">
         <v>246</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>247</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>249</v>
       </c>
     </row>
   </sheetData>

--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\imtl\limquiz\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F7BF824-0C76-4B46-B924-B1E5190EE16E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E4D0162-8D57-4B21-A4D1-0652CAF6419B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="690" yWindow="870" windowWidth="28830" windowHeight="14730" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="253">
   <si>
     <t>버전</t>
   </si>
@@ -919,6 +919,19 @@
   <si>
     <t>인격 이미지가 기본으로 각성 일러스트로 표시됩니다. (토글 버튼으로 일반 전환 가능)
 덱 퀴즈: 인격 배치 후 마우스를 움직이지 않고 바로 더블클릭해도 정상적으로 배치되도록 수정했습니다.</t>
+  </si>
+  <si>
+    <t>v0.13.45</t>
+  </si>
+  <si>
+    <t>dbClearAll이 위치 이동으로 판정이 리셋된 노랑(dbKnownJudge=yellow, 점선 "인격 맞음" 상태)도 유지하도록 수정 - 노랑을 옮긴 뒤 오답 비우기를 누르면 같이 비워지던 문제
+.db-sinner-filter를 flex-wrap에서 grid 6열(모바일 4열)로 변경 - 배치 시 "✓ " 접두사로 버튼 폭이 변해 줄바꿈이 바뀌고 클릭하려던 버튼이 움직이던 문제. 12수감자 = 6×2 고정
+dbCandidates 랜덤 셔플 제거, CharacterData ID 오름차순 정렬로 고정 (없음 카드는 렌더 시 기존대로 맨 앞 별도 배치)</t>
+  </si>
+  <si>
+    <t>덱 퀴즈: 수감자 선택 버튼이 한 줄에 6개씩 고정되어, 배치해도 버튼 위치가 움직이지 않습니다.
+덱 퀴즈: 위치를 옮긴 노랑(인격 맞음) 인격이 "오답 비우기"에서 함께 비워지던 문제를 수정했습니다.
+덱 퀴즈: 인격 목록이 무작위가 아닌 ID 순서로 정렬됩니다.</t>
   </si>
 </sst>
 </file>
@@ -1306,7 +1319,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D86"/>
+  <dimension ref="A1:D87"/>
   <sheetFormatPr defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -2511,6 +2524,20 @@
       </c>
       <c r="D86" s="1" t="s">
         <v>249</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>250</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>252</v>
       </c>
     </row>
   </sheetData>

--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\imtl\limquiz\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E4D0162-8D57-4B21-A4D1-0652CAF6419B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C899D0A-A154-4B33-959D-1E087E0FDB4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="690" yWindow="870" windowWidth="28830" windowHeight="14730" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="256">
   <si>
     <t>버전</t>
   </si>
@@ -932,6 +932,18 @@
     <t>덱 퀴즈: 수감자 선택 버튼이 한 줄에 6개씩 고정되어, 배치해도 버튼 위치가 움직이지 않습니다.
 덱 퀴즈: 위치를 옮긴 노랑(인격 맞음) 인격이 "오답 비우기"에서 함께 비워지던 문제를 수정했습니다.
 덱 퀴즈: 인격 목록이 무작위가 아닌 ID 순서로 정렬됩니다.</t>
+  </si>
+  <si>
+    <t>v0.13.46</t>
+  </si>
+  <si>
+    <t>덱 퀴즈 레이아웃 추가 확대: max-width 1560→1700px, 후보 패널 flex 1.2→1.35, 카드 이미지 aspect-ratio 1/1→6/7 (세로로 더 크게) - 1920px 화면 기준 카드 약 124→148px
+전역 폰트 확대(총 34곳): 덱 퀴즈(슬롯명 10→12, 판정 배지 9→11+ellipsis, 카드명 13→15, 필터 버튼 13→14 등), 스킬 퀴즈(속성/유형 버튼 13→14, 라벨 12→13 등), 홈/인격 두들(드롭다운 메타·키워드 칩 13→14, 배지 11→12 등). 결과 카드(html2canvas 캡처 영역)는 레이아웃 보존 위해 제외
+치환은 스크래치패드 bump-fonts.js로 일괄 수행 (각 패턴 1회 매칭 검증)</t>
+  </si>
+  <si>
+    <t>덱 퀴즈: 인격 카드와 이미지가 더 커졌습니다.
+전체 화면의 작은 글자들을 한 단계씩 키웠습니다.</t>
   </si>
 </sst>
 </file>
@@ -1319,7 +1331,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D87"/>
+  <dimension ref="A1:D88"/>
   <sheetFormatPr defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -2538,6 +2550,20 @@
       </c>
       <c r="D87" s="1" t="s">
         <v>252</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>253</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>255</v>
       </c>
     </row>
   </sheetData>

--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\imtl\limquiz\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C899D0A-A154-4B33-959D-1E087E0FDB4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34E94487-CE8F-4469-A038-11FA35E8DAFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="690" yWindow="870" windowWidth="28830" windowHeight="14730" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="259">
   <si>
     <t>버전</t>
   </si>
@@ -944,6 +944,19 @@
   <si>
     <t>덱 퀴즈: 인격 카드와 이미지가 더 커졌습니다.
 전체 화면의 작은 글자들을 한 단계씩 키웠습니다.</t>
+  </si>
+  <si>
+    <t>v0.13.47</t>
+  </si>
+  <si>
+    <t>덱 퀴즈 최하단 #dbProgress("12칸을 모두 채워주세요") 요소·갱신 코드·CSS 제거 (제출 버튼 카운터, "N/12 배치됨" 라벨과 중복)
+인격명 검색창을 수감자 필터·키워드 필터 아래(후보 목록 바로 위)로 이동 - 사용 흐름(수감자→키워드→이름 검색) 순서에 맞춤, .db-search margin-bottom→margin-top
+오답 비우기/정답 보기 버튼을 상단 헤더에서 배치 보드 바로 아래(.db-board-actions, 우측 정렬 34px)로 이동 - 제출 버튼과 분리해 오클릭 방지, 보드에 작용하는 버튼이라 문맥상 근접 배치. 미사용 .db-header-giveup-btn CSS 제거</t>
+  </si>
+  <si>
+    <t>덱 퀴즈: 하단의 중복 안내 문구를 제거했습니다.
+덱 퀴즈: 인격명 검색창이 수감자·키워드 필터 아래(목록 바로 위)로 이동했습니다.
+덱 퀴즈: "오답 비우기"와 "정답 보기" 버튼이 배치 보드 아래로 이동했습니다.</t>
   </si>
 </sst>
 </file>
@@ -1331,7 +1344,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D88"/>
+  <dimension ref="A1:D89"/>
   <sheetFormatPr defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -2564,6 +2577,20 @@
       </c>
       <c r="D88" s="1" t="s">
         <v>255</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>256</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>258</v>
       </c>
     </row>
   </sheetData>

--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\imtl\limquiz\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34E94487-CE8F-4469-A038-11FA35E8DAFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A09736B-F388-45E4-B398-0CF1C37EDCFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="690" yWindow="870" windowWidth="28830" windowHeight="14730" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="262">
   <si>
     <t>버전</t>
   </si>
@@ -957,6 +957,20 @@
     <t>덱 퀴즈: 하단의 중복 안내 문구를 제거했습니다.
 덱 퀴즈: 인격명 검색창이 수감자·키워드 필터 아래(목록 바로 위)로 이동했습니다.
 덱 퀴즈: "오답 비우기"와 "정답 보기" 버튼이 배치 보드 아래로 이동했습니다.</t>
+  </si>
+  <si>
+    <t>v0.13.48</t>
+  </si>
+  <si>
+    <t>오답 비우기/정답 보기를 보드 하단에서 보드 상단 라벨 줄(.db-slots-label-right)로 이동 (스크롤 없이 접근)
+제출 버튼을 상단 전체 폭에서 보드(왼쪽 열) 아래로 이동 - 와이드 화면에서 세로 공간 낭비 제거
+1920×1080 무스크롤 컴팩트 레이아웃(@media min-width:1500px): 보드 6열×2줄, deckBuilderScreen 상하 -12px 오프셋, 상단바/패널/검색/필터 여백·높이 축소, 후보 이미지 이 폭에서만 1:1(147px, 확대 전 124px보다 큼), 카드명 line-height 1.2 - 최악 케이스(파우스트 16+없음=17장, 3줄)에서 scrollHeight 919=viewport 확인. 내부 스크롤 없음
+.db-header 안 back-btn의 불필요한 margin-bottom 제거</t>
+  </si>
+  <si>
+    <t>덱 퀴즈: "오답 비우기"/"정답 보기" 버튼이 배치 보드 상단으로 이동했습니다.
+덱 퀴즈: 제출 버튼이 배치 보드 바로 아래로 이동했습니다.
+덱 퀴즈: 넓은 화면(FHD 이상)에서 스크롤 없이 한 화면에 모두 표시됩니다.</t>
   </si>
 </sst>
 </file>
@@ -1344,7 +1358,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D89"/>
+  <dimension ref="A1:D90"/>
   <sheetFormatPr defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -2591,6 +2605,20 @@
       </c>
       <c r="D89" s="1" t="s">
         <v>258</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>259</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>261</v>
       </c>
     </row>
   </sheetData>

--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\imtl\limquiz\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A09736B-F388-45E4-B398-0CF1C37EDCFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD2D61F5-EF9B-44D7-9F3D-D41F74052F62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="690" yWindow="870" windowWidth="28830" windowHeight="14730" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="265">
   <si>
     <t>버전</t>
   </si>
@@ -971,6 +971,19 @@
     <t>덱 퀴즈: "오답 비우기"/"정답 보기" 버튼이 배치 보드 상단으로 이동했습니다.
 덱 퀴즈: 제출 버튼이 배치 보드 바로 아래로 이동했습니다.
 덱 퀴즈: 넓은 화면(FHD 이상)에서 스크롤 없이 한 화면에 모두 표시됩니다.</t>
+  </si>
+  <si>
+    <t>v0.13.49</t>
+  </si>
+  <si>
+    <t>와이드(≥1500px) 레이아웃 폭 1700→1860px + 후보 패널 flex 1.35→1.25로 보드 비중 확대: 보드 슬롯 104→124px(+19%), 후보 카드 147→156px
+수감자/키워드 필터 버튼 확대: 수감자 height 32→36(와이드 32)·font 14→15, 키워드 height 30→34(와이드 30)·font 13→14, 초기화 버튼 동일
+"정답 보기" 버튼을 "포기"로 변경 + dbGaveUp 상태 추가: 포기 시 제출 버튼 비활성("포기한 덱입니다") 및 dbSubmit 가드로 포기 후 제출해도 클리어 처리되지 않음. dbInit에서 리셋
+최악 케이스(파우스트 17장) 1900×919 무스크롤 유지 확인 (919=919)</t>
+  </si>
+  <si>
+    <t>덱 퀴즈: 배치 보드 카드와 수감자·키워드 버튼이 더 커졌습니다.
+덱 퀴즈: "정답 보기"가 "포기" 버튼으로 바뀌었고, 포기한 덱은 제출해도 클리어로 처리되지 않습니다.</t>
   </si>
 </sst>
 </file>
@@ -1358,7 +1371,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D90"/>
+  <dimension ref="A1:D91"/>
   <sheetFormatPr defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -2619,6 +2632,20 @@
       </c>
       <c r="D90" s="1" t="s">
         <v>261</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>262</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>264</v>
       </c>
     </row>
   </sheetData>

--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\imtl\limquiz\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD2D61F5-EF9B-44D7-9F3D-D41F74052F62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{389E4837-814F-470B-B3B2-14159913A8A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="690" yWindow="870" windowWidth="28830" windowHeight="14730" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UpdateLog" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="268">
   <si>
     <t>버전</t>
   </si>
@@ -984,6 +984,20 @@
   <si>
     <t>덱 퀴즈: 배치 보드 카드와 수감자·키워드 버튼이 더 커졌습니다.
 덱 퀴즈: "정답 보기"가 "포기" 버튼으로 바뀌었고, 포기한 덱은 제출해도 클리어로 처리되지 않습니다.</t>
+  </si>
+  <si>
+    <t>v0.13.50</t>
+  </si>
+  <si>
+    <t>수감자 문장(엠블럼) 12종·죄악속성 아이콘 7종 추가: 사용자 제공 zip에서 추출. 스프라이트(MainUI_Logoicon_filter.png 2048x2048, 256px 셀 8+4 배열)를 PowerShell System.Drawing으로 슬라이스 → images/sinners/&lt;로마자&gt;.png, 속성 7종은 images/sins/&lt;영문 소문자&gt;.png로 커밋
+SINNER_ICON/SIN_ICON 맵 추가, sinnerDot()가 색상 점 대신 문장 이미지 표시(아이콘 없으면 점 폴백) - 드롭다운·기록 테이블·정답 카드·스킬 퀴즈 메타 전체 적용
+덱 퀴즈 수감자 필터 버튼에 문장 아이콘(22px) + 이름 ellipsis용 span 구조로 변경
+스킬 퀴즈 죄악속성 버튼(18px)·결과 속성 칩(16px)에 아이콘 추가
+1900×919 무스크롤 유지 확인</t>
+  </si>
+  <si>
+    <t>수감자 문장(엠블럼) 아이콘이 추가되었습니다. 인격 검색 목록, 기록, 정답 화면, 덱 퀴즈 수감자 버튼에서 볼 수 있습니다.
+스킬 퀴즈: 죄악속성 버튼과 결과 화면에 속성 아이콘이 추가되었습니다.</t>
   </si>
 </sst>
 </file>
@@ -1371,7 +1385,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D91"/>
+  <dimension ref="A1:D92"/>
   <sheetFormatPr defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -2646,6 +2660,20 @@
       </c>
       <c r="D91" s="1" t="s">
         <v>264</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>265</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>267</v>
       </c>
     </row>
   </sheetData>

--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\imtl\limquiz\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{389E4837-814F-470B-B3B2-14159913A8A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13F66DF7-647A-43E7-970E-08C8C93854AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="271">
   <si>
     <t>버전</t>
   </si>
@@ -998,6 +998,19 @@
   <si>
     <t>수감자 문장(엠블럼) 아이콘이 추가되었습니다. 인격 검색 목록, 기록, 정답 화면, 덱 퀴즈 수감자 버튼에서 볼 수 있습니다.
 스킬 퀴즈: 죄악속성 버튼과 결과 화면에 속성 아이콘이 추가되었습니다.</t>
+  </si>
+  <si>
+    <t>v0.13.51</t>
+  </si>
+  <si>
+    <t>홈 플레이 기록에 행별 삭제 버튼(🗑️, .rec-del-btn) 추가 - 전체 records 배열 idx 기준 splice 후 저장·재렌더
+기록 초기화가 현재 선택된 탭(recordFilter) 기준으로 동작: 전체 탭=전부 삭제(기존), 오늘의 인격/랜덤 탭=해당 mode 기록만 filter로 제거
+탭 전환 시 초기화 버튼 라벨 동적 변경("기록 초기화"/"오늘의 인격 기록 초기화"/"랜덤 기록 초기화") + confirm 문구도 탭별로 표시
+테스트 기록 주입으로 3개 시나리오(개별 삭제/daily만/random만) 검증 완료</t>
+  </si>
+  <si>
+    <t>플레이 기록을 한 개씩 삭제할 수 있습니다. (기록 오른쪽 🗑️ 버튼)
+기록 초기화가 현재 보고 있는 탭 기준으로 동작합니다. (오늘의 인격 탭에서는 오늘의 인격 기록만, 랜덤 탭에서는 랜덤 기록만 삭제)</t>
   </si>
 </sst>
 </file>
@@ -1385,7 +1398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D92"/>
+  <dimension ref="A1:D93"/>
   <sheetFormatPr defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -2674,6 +2687,20 @@
       </c>
       <c r="D92" s="1" t="s">
         <v>267</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>268</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>270</v>
       </c>
     </row>
   </sheetData>

--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\imtl\limquiz\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13F66DF7-647A-43E7-970E-08C8C93854AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4778F1E-3165-42C0-8325-BCB22B968E9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="274">
   <si>
     <t>버전</t>
   </si>
@@ -1011,6 +1011,19 @@
   <si>
     <t>플레이 기록을 한 개씩 삭제할 수 있습니다. (기록 오른쪽 🗑️ 버튼)
 기록 초기화가 현재 보고 있는 탭 기준으로 동작합니다. (오늘의 인격 탭에서는 오늘의 인격 기록만, 랜덤 탭에서는 랜덤 기록만 삭제)</t>
+  </si>
+  <si>
+    <t>v0.13.52</t>
+  </si>
+  <si>
+    <t>각성/일반 토글을 이미지 위 절대배치(모서리 부유)에서 이미지 위쪽 우측 정렬 행(.img-pref-row, inline 버튼)으로 변경 - 인격 두들 정답 화면(answer-img-area), 스킬 퀴즈 인격 카드(sq-toggle-row), 스킬 퀴즈 결과 3곳
+덱 퀴즈 와이드 레이아웃에서 수감자 필터/키워드/검색창 상하 간격 6px→12px 확대 (일반 플레이 상태 무스크롤 유지 확인)
+dbSubmitCount 추가: dbSubmit 채점 시 증가, dbInit 리셋. 결과 화면에 "총 N회 제출 만에 완료!"/"제출 N회 후 포기" 표시</t>
+  </si>
+  <si>
+    <t>각성/일반 전환 버튼이 이미지 위쪽으로 정리되었습니다.
+덱 퀴즈: 수감자·키워드·검색창 사이 간격을 넓혔습니다.
+덱 퀴즈: 클리어 시 총 몇 회 제출 만에 완료했는지 표시됩니다.</t>
   </si>
 </sst>
 </file>
@@ -1398,7 +1411,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D93"/>
+  <dimension ref="A1:D94"/>
   <sheetFormatPr defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -2701,6 +2714,20 @@
       </c>
       <c r="D93" s="1" t="s">
         <v>270</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>271</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>273</v>
       </c>
     </row>
   </sheetData>

--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\imtl\limquiz\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4778F1E-3165-42C0-8325-BCB22B968E9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{976DE2AA-5B16-4974-85F2-FD3B14EF7C9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="277">
   <si>
     <t>버전</t>
   </si>
@@ -1024,6 +1024,20 @@
     <t>각성/일반 전환 버튼이 이미지 위쪽으로 정리되었습니다.
 덱 퀴즈: 수감자·키워드·검색창 사이 간격을 넓혔습니다.
 덱 퀴즈: 클리어 시 총 몇 회 제출 만에 완료했는지 표시됩니다.</t>
+  </si>
+  <si>
+    <t>v0.13.53</t>
+  </si>
+  <si>
+    <t>덱 퀴즈 힌트 기능 추가: deckKeywords.json(DeckInfo Keyword1~4) fetch 추가, DECK_KEYWORDS 전역
+보드 상단 액션에 "💡 힌트 N/M" 버튼(dbHintBtn) - 클릭마다 덱 키워드를 앞에서부터 하나씩 공개(dbHintsUsed), 보드 라벨 아래 #dbHintKeywords 영역에 kwChip으로 표시(색상 없는 키워드는 기본 칩 스타일)
+키워드 소진 시 "더 보여줄 힌트가 없습니다", 키워드 없는 덱은 "이 덱은 제공되는 힌트가 없습니다" 토스트
+결과 화면에 "힌트 N회 사용" 표시(클리어/포기 공통), dbInit에서 리셋
+검증: 1키워드 덱(거미집) 소진 케이스, 4키워드 덱(중지덱) 순차 공개, 결과 표시, 다음 덱 리셋</t>
+  </si>
+  <si>
+    <t>덱 퀴즈: 힌트 기능이 추가되었습니다! 💡 힌트 버튼을 누르면 덱의 키워드가 하나씩 공개됩니다.
+덱 퀴즈: 힌트 사용 횟수가 플레이 중과 결과 화면에 표시됩니다.</t>
   </si>
 </sst>
 </file>
@@ -1411,7 +1425,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D94"/>
+  <dimension ref="A1:D95"/>
   <sheetFormatPr defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -2728,6 +2742,20 @@
       </c>
       <c r="D94" s="1" t="s">
         <v>273</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>274</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>276</v>
       </c>
     </row>
   </sheetData>

--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\imtl\limquiz\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{976DE2AA-5B16-4974-85F2-FD3B14EF7C9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD56116B-A16C-4E96-8F9D-5AC35535CF16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UpdateLog" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="280">
   <si>
     <t>버전</t>
   </si>
@@ -1038,6 +1038,16 @@
   <si>
     <t>덱 퀴즈: 힌트 기능이 추가되었습니다! 💡 힌트 버튼을 누르면 덱의 키워드가 하나씩 공개됩니다.
 덱 퀴즈: 힌트 사용 횟수가 플레이 중과 결과 화면에 표시됩니다.</t>
+  </si>
+  <si>
+    <t>v0.13.54</t>
+  </si>
+  <si>
+    <t>dbPickDeck 출제 조건을 "Main &gt;= 3"에서 "Main+Sub(비Null) &gt;= 3"으로 변경 - Sub 중심 덱인 거미집(Main 1/Sub 9)과 흑수덱(Main 1/Sub 10)이 출제 풀에서 영구 제외되던 문제. Sub도 절대 위치 채점 대상이라 그대로 플레이 가능
+검증: 9개 덱 전부 eligible, 200회 랜덤 샘플에서 전 덱 출현, 흑수덱 정답 배치 all-green(클리어 가능) 확인</t>
+  </si>
+  <si>
+    <t>덱 퀴즈: 거미집덱과 흑수덱이 출제되지 않던 문제를 수정했습니다. 이제 모든 덱이 나옵니다.</t>
   </si>
 </sst>
 </file>
@@ -1425,7 +1435,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D95"/>
+  <dimension ref="A1:D96"/>
   <sheetFormatPr defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -2756,6 +2766,20 @@
       </c>
       <c r="D95" s="1" t="s">
         <v>276</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>277</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>279</v>
       </c>
     </row>
   </sheetData>

--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D98"/>
+  <dimension ref="A1:D99"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1960,9 +1960,23 @@
         <v>드롭박스에서 화살표 키로 고른 인격과 실제로 선택되는 인격이 다르게 나오던 버그를 수정했습니다.</v>
       </c>
     </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>v0.13.57</v>
+      </c>
+      <c r="B99" t="str">
+        <v>2026-07-18</v>
+      </c>
+      <c r="C99" t="str">
+        <v>CharacterTable DeckData: ID1 덱 "이상" 슬롯 Type을 Main→Sub, 순서를 4→0으로 조정 반영 (git 커밋 안 된 상태로 지난 배포에 먼저 반영됐던 것을 정식 커밋)</v>
+      </c>
+      <c r="D99" t="str">
+        <v>덱 데이터 일부 수정 사항을 반영했습니다.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D98"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D99"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\imtl\limquiz\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6D59677-347A-43B3-8124-942DE7A5A59B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE76B14F-D04C-4D72-B431-1B8E5F89252E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="298">
   <si>
     <t>버전</t>
   </si>
@@ -1101,6 +1101,21 @@
 기록 초기화 탭별 동작·라벨에 deck/skill 케이스 추가
 원격 v0.13.55~57(카드형 결과 UI, 드롭다운 수정, 덱 데이터) 위로 리베이스하여 통합</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v0.13.59</t>
+  </si>
+  <si>
+    <t>홈에 📊 통계 모달 추가 (changelog 모달 패턴 재사용, statsBtn/statsModal/buildStatsHTML)
+오늘의 인격: 플레이·승률·현재 연속·최고 연속 타일 + 시도 횟수 분포 바(1~7, 성공 기준). 스트릭은 challengeNo 연속 성공 기준, 실패·건너뜀은 끊김, 현재 스트릭은 마지막 성공이 오늘/어제 챌린지일 때만 유지
+랜덤: 플레이·승률·시도 분포 / 덱 퀴즈: 플레이·클리어율·평균 제출·평균 힌트 / 스킬 퀴즈: 플레이·완벽 클리어율·정답률(solved합/total합)
+타일은 기존 .db-stat-card 재사용, 분포 바는 .stat-dist-* 신규 CSS. 기록 없는 모드는 "아직 기록이 없습니다" 표시
+검증: 스트릭 계산(중간 실패 후 재시작, 마지막 성공 3일 전이면 현재 0), 분포 카운트, 평균/백분율</t>
+  </si>
+  <si>
+    <t>📊 통계 기능이 추가되었습니다! 홈의 플레이 기록에서 통계 버튼을 눌러보세요.
+오늘의 인격: 승률, 현재/최고 연속 성공, 시도 횟수 분포를 볼 수 있습니다.
+랜덤·덱 퀴즈·스킬 퀴즈의 통계도 함께 제공됩니다.</t>
   </si>
 </sst>
 </file>
@@ -1488,7 +1503,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D100"/>
+  <dimension ref="A1:D101"/>
   <sheetFormatPr defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -2889,6 +2904,20 @@
       </c>
       <c r="D100" s="2" t="s">
         <v>293</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>295</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>297</v>
       </c>
     </row>
   </sheetData>

--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\imtl\limquiz\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE76B14F-D04C-4D72-B431-1B8E5F89252E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81D05B05-F530-45E2-9EA7-F6916E313932}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="301">
   <si>
     <t>버전</t>
   </si>
@@ -1116,6 +1116,18 @@
     <t>📊 통계 기능이 추가되었습니다! 홈의 플레이 기록에서 통계 버튼을 눌러보세요.
 오늘의 인격: 승률, 현재/최고 연속 성공, 시도 횟수 분포를 볼 수 있습니다.
 랜덤·덱 퀴즈·스킬 퀴즈의 통계도 함께 제공됩니다.</t>
+  </si>
+  <si>
+    <t>v0.13.60</t>
+  </si>
+  <si>
+    <t>홈 기록에 백업(⬇️)/복원(⬆️) 버튼 추가: exportRecords는 {app,type,exportedAt,count,records} 래퍼 JSON을 limquiz-기록-YYYYMMDD.json으로 다운로드(Blob+ObjectURL)
+복원은 숨김 file input → FileReader → applyImportedRecords: 래퍼/순수 배열 모두 허용, mode 필드 검증, 완전 동일 기록은 JSON 직렬화 비교로 중복 제외, 기존 기록에 병합 후 날짜순 정렬. confirm으로 추가 개수·중복 제외 안내
+빈 기록 내보내기/신규 없음/형식 오류는 alert 안내, file input은 선택 후 value 초기화(같은 파일 재선택 허용)
+applyImportedRecords를 파일 리더와 분리해 병합·중복·검증·왕복 로직 콘솔 테스트로 검증</t>
+  </si>
+  <si>
+    <t>플레이 기록 백업/복원 기능이 추가되었습니다. ⬇️ 백업으로 JSON 파일을 저장하고, ⬆️ 복원으로 다른 브라우저·기기에서 불러올 수 있습니다. (복원 시 기존 기록은 유지되고 새 기록만 추가됩니다)</t>
   </si>
 </sst>
 </file>
@@ -1503,7 +1515,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D101"/>
+  <dimension ref="A1:D102"/>
   <sheetFormatPr defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -2918,6 +2930,20 @@
       </c>
       <c r="D101" s="2" t="s">
         <v>297</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>298</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>300</v>
       </c>
     </row>
   </sheetData>

--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\imtl\limquiz\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81D05B05-F530-45E2-9EA7-F6916E313932}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89B1EA1D-A077-47EB-8FE5-F9CD993914DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28770" yWindow="0" windowWidth="28830" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UpdateLog" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="304">
   <si>
     <t>버전</t>
   </si>
@@ -1128,6 +1128,20 @@
   </si>
   <si>
     <t>플레이 기록 백업/복원 기능이 추가되었습니다. ⬇️ 백업으로 JSON 파일을 저장하고, ⬆️ 복원으로 다른 브라우저·기기에서 불러올 수 있습니다. (복원 시 기존 기록은 유지되고 새 기록만 추가됩니다)</t>
+  </si>
+  <si>
+    <t>v0.13.61</t>
+  </si>
+  <si>
+    <t>덱 퀴즈 공유 카드 추가: dbJudgeHistory에 제출별 판정 스냅샷(12자리 g/y/r 문자열) 누적, 기록 저장 시 judges 배열로 포함
+buildDeckCardHTML: 워들식 그리드(제출 회차별 12칸 초록/노랑/빨강 셀) + 덱 이름 + 클리어/포기 + 제출·힌트 횟수. showResultCard가 mode=deck이면 덱 카드로 분기 (기존 cardModal·html2canvas 저장/복사 재사용)
+결과 화면에 "📋 결과 공유" 버튼(dbShareResult→dbLastRecord), 홈 기록의 덱 행에도 📋 활성화 (judges 없는 이전 기록은 그리드 대신 안내 문구)
+이미지 저장 파일명 mode=deck이면 "덱" 표기
+검증: 2회 제출(오답 포함→클리어) 그리드 행/셀/색상, 결과·기록 양쪽 진입, html2canvas 캡처 1280x502 정상</t>
+  </si>
+  <si>
+    <t>덱 퀴즈: 결과 공유 카드가 추가되었습니다! 제출 회차별 판정이 워들처럼 색깔 그리드로 표시되고, 이미지 저장·클립보드 복사가 가능합니다.
+덱 퀴즈: 결과 화면과 홈 플레이 기록(📋)에서 공유 카드를 열 수 있습니다.</t>
   </si>
 </sst>
 </file>
@@ -1515,7 +1529,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D102"/>
+  <dimension ref="A1:D103"/>
   <sheetFormatPr defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -2944,6 +2958,20 @@
       </c>
       <c r="D102" s="2" t="s">
         <v>300</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>301</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>303</v>
       </c>
     </row>
   </sheetData>

--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\imtl\limquiz\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89B1EA1D-A077-47EB-8FE5-F9CD993914DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{577DB0DA-FEA4-41AD-BBF8-0D2650F8DDDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28770" yWindow="0" windowWidth="28830" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="307">
   <si>
     <t>버전</t>
   </si>
@@ -1142,6 +1142,25 @@
   <si>
     <t>덱 퀴즈: 결과 공유 카드가 추가되었습니다! 제출 회차별 판정이 워들처럼 색깔 그리드로 표시되고, 이미지 저장·클립보드 복사가 가능합니다.
 덱 퀴즈: 결과 화면과 홈 플레이 기록(📋)에서 공유 카드를 열 수 있습니다.</t>
+  </si>
+  <si>
+    <t>v0.13.62</t>
+  </si>
+  <si>
+    <t>스킬 퀴즈 5종 개선:
+1) 스테이지2 스킬명 입력에 검색 드롭다운 추가 (SQ_SKILL_NAMES: 전체 인격 스킬명 풀, data.json 로드 시 계산). sqSkillDropdown 부유 패널(덱 퀴즈 필터 드롭다운과 동일 패턴)로 입력값 부분일치 검색, 방향키/엔터/이스케이프 지원, 옵션 선택 시 값만 채우고 확인은 별도. 정확한 철자를 몰라도 부분 검색으로 찾을 수 있음
+2) 제출 횟수 카운트: sqSubmitCount를 sqSubmitS1/sqCheckS2(활성 행만) 진입 시 증가, sq-progress-stats 영역(sqUpdateProgressStats)에 실시간 표시, 결과·기록(submits 필드)에도 저장
+3) 최근 출제 제외: localStorage(sq_recent_identities, 최대 15개)로 최근 출제된 인격을 재출제 후보에서 제외, 제외 후 후보가 없으면 전체 풀로 폴백
+4) 스킬 퀴즈 공유 카드 추가: buildSkillCardHTML - 인격 이미지/이름/수감자/성급 + 스킬별 속성·유형·이름 판정(정답/포기 배지). 기록 저장 시 skills 배열(속성/유형/이름 + 포기 여부)·sinner·grade·img 함께 저장해 나중에도 재현 가능. 결과 화면 "📋 결과 공유" 버튼(sqShareResult/sqLastRecord) + 홈 기록 스킬 행 📋 버튼 모두 지원. showResultCard가 mode=skill 분기, 이미지 저장 파일명도 "스킬" 표기
+5) 힌트를 유형·속성 순으로 점진 공개: 스테이지1 힌트 버튼이 1회차엔 속성만, 2회차엔 속성+유형까지 공개(버튼 라벨 "N/2" 갱신, 2회 도달 시 비활성화). 스테이지2 이름 힌트도 누를 때마다 글자 수를 하나씩 늘려 공개(전부 공개는 안 함). 두 힌트 모두 sqHintsUsed에 집계
+검증: 힌트 단계별 텍스트/비활성화, 검색 드롭다운 필터·선택, 제출/힌트 카운트 누적, 결과 기록 필드, 공유 카드 렌더(결과화면·기록화면 양쪽), 12연속 출제 반복 없음(localStorage 기반), 콘솔 에러 없음</t>
+  </si>
+  <si>
+    <t>스킬 퀴즈: 스킬 이름을 입력할 때 검색해서 선택할 수 있습니다. (정확한 철자를 몰라도 검색으로 찾을 수 있어요)
+스킬 퀴즈: 제출·힌트 사용 횟수가 플레이 중과 결과 화면에 표시됩니다.
+스킬 퀴즈: 최근 출제된 인격은 당분간 다시 나오지 않습니다.
+스킬 퀴즈: 결과 공유 카드가 추가되었습니다. (이미지 저장·클립보드 복사 가능)
+스킬 퀴즈: 힌트를 누를 때마다 죄악속성 → 공격유형 순서로 점점 더 많은 정보가 공개됩니다.</t>
   </si>
 </sst>
 </file>
@@ -1529,7 +1548,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D103"/>
+  <dimension ref="A1:D104"/>
   <sheetFormatPr defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -2972,6 +2991,20 @@
       </c>
       <c r="D103" s="2" t="s">
         <v>303</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>304</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>306</v>
       </c>
     </row>
   </sheetData>

--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\imtl\limquiz\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{577DB0DA-FEA4-41AD-BBF8-0D2650F8DDDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64FF653F-D0CC-44FE-9579-768F84751B34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28770" yWindow="0" windowWidth="28830" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="310">
   <si>
     <t>버전</t>
   </si>
@@ -1161,6 +1161,23 @@
 스킬 퀴즈: 최근 출제된 인격은 당분간 다시 나오지 않습니다.
 스킬 퀴즈: 결과 공유 카드가 추가되었습니다. (이미지 저장·클립보드 복사 가능)
 스킬 퀴즈: 힌트를 누를 때마다 죄악속성 → 공격유형 순서로 점점 더 많은 정보가 공개됩니다.</t>
+  </si>
+  <si>
+    <t>v0.13.63</t>
+  </si>
+  <si>
+    <t>스킬 퀴즈 스테이지1 "👀 정답 보기"(sqStage1Reveal) 버튼·함수 완전 제거, 죄악속성/공격유형 버튼 확대(height 34→42px, font 14→16px, 아이콘 18→22px, gap/padding 확대)
+힌트 버튼을 하단 액션 줄에서 스킬 라벨 우측 상단으로 이동 (.sq-skill-header flex row, .sq-s1-actions 삭제)
+SQ_TYPES에서 방어/회피/반격 제거 - data.json 전수 조사 결과 실사용 유형은 참격/관통/타격뿐
+인격 정보(sq-identity-info) 폰트 확대: 이름 19→23px, 메타(수감자·성급·소속·키워드) 14→17px, 패딩 확대
+스킬 퀴즈 전반 폰트 확대: 스킬 라벨/행 라벨/피드백/힌트/제출버튼/포기버튼/결과 배너·이름·메타·스킬행·진행상태줄 등 1~3px씩 상향
+검증: 정답보기 버튼·함수 제거, 힌트 버튼 헤더 위치·라벨 갱신(1/2→2/2 비활성화), 유형 옵션 3종만 노출, 폰트 크기 확인, 콘솔 에러 없음</t>
+  </si>
+  <si>
+    <t>스킬 퀴즈: "정답 보기" 버튼을 없애고 죄악속성·공격유형 버튼을 더 크게 키웠습니다.
+스킬 퀴즈: 힌트 버튼이 각 스킬 우측 상단으로 이동했습니다.
+스킬 퀴즈: 실제로 사용되지 않는 방어·회피·반격 선택지를 제거했습니다.
+스킬 퀴즈: 인격 정보와 전체적인 글자 크기를 키웠습니다.</t>
   </si>
 </sst>
 </file>
@@ -1548,7 +1565,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D104"/>
+  <dimension ref="A1:D105"/>
   <sheetFormatPr defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -3005,6 +3022,20 @@
       </c>
       <c r="D104" s="2" t="s">
         <v>306</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>307</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>309</v>
       </c>
     </row>
   </sheetData>

--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\imtl\limquiz\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64FF653F-D0CC-44FE-9579-768F84751B34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38F2F96E-1BBF-466D-A5E3-3027DB372BB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28770" yWindow="0" windowWidth="28830" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="313">
   <si>
     <t>버전</t>
   </si>
@@ -1178,6 +1178,22 @@
 스킬 퀴즈: 힌트 버튼이 각 스킬 우측 상단으로 이동했습니다.
 스킬 퀴즈: 실제로 사용되지 않는 방어·회피·반격 선택지를 제거했습니다.
 스킬 퀴즈: 인격 정보와 전체적인 글자 크기를 키웠습니다.</t>
+  </si>
+  <si>
+    <t>v0.13.64</t>
+  </si>
+  <si>
+    <t>스킬 퀴즈 스테이지1 정보 영역을 두 개로 분리: #sq-identity-media(이미지, 일반 스크롤)와 #sq-identity-sticky(이름+정보카드, position:sticky top:0)로 나눠 sq-wrap의 직계 자식으로 배치 - sticky의 유효 범위(containing block)가 스킬 블록 목록까지 이어지도록 함(기존처럼 이미지와 한 컨테이너에 넣으면 그 컨테이너가 짧게 끝나 스킬3까지 스크롤 시 sticky가 일찍 풀림). sqIdentityCardHTML을 sqIdentityMediaHTML/sqIdentityStickyHTML로 분리, refreshSqImage/sqRenderStage1/sqRenderResult/sqGoToSkillQuiz 로딩 메시지 등 모든 참조 갱신
+캐릭터 정보(수감자/성급/소속/키워드)를 기존 인격 두들 정답 화면의 answer-info-grid/answer-info-card 패턴으로 재사용해 가로 카드 배치로 변경 (이름은 카드 제외, 상단에 별도 표시)
+스테이지2 이름 힌트 로직 변경: 1회차는 글자 수만 안내("총 N글자입니다"), 2회차부터 앞 글자를 하나씩 더 공개(2회차=1자, 3회차=2자...), 전부 공개는 안 함
+스테이지2 검색 드롭다운 위치 보정: sqPositionSkillDropdown이 아래쪽 공간이 부족하고 위쪽이 더 넓으면 입력 위로 뒤집어 표시. 입력 focus 시 scrollIntoView(block:'center')로 화면 하단 근처 입력(스킬3 등)도 여유 공간 확보
+검증: sticky가 스크롤 시 top:0 고정 유지, 정보카드 4개(이름 제외) 가로 배치, 힌트 1회차 글자수→2회차부터 점진 글자 공개, 스킬3 드롭다운이 화면 하단 근처에서 위로 뒤집혀 뷰포트 안에 표시, 스테이지2 완료→결과→미디어/스티키 숨김→공유카드까지 전체 플로우 정상, 콘솔 에러 없음</t>
+  </si>
+  <si>
+    <t>스킬 퀴즈: 스킬3까지 스크롤해도 인격 이름·정보가 화면 상단에 계속 보이도록 했습니다.
+스킬 퀴즈: 인격 정보(수감자·성급·소속·키워드)가 카드 형태로 가로로 나열됩니다.
+스킬 퀴즈: 이름 힌트를 처음 누르면 글자 수를, 두 번째부터는 한 글자씩 더 공개합니다.
+스킬 퀴즈: 스킬3 검색 드롭다운이 화면 밖으로 나가지 않도록 위치를 자동으로 조정했습니다.</t>
   </si>
 </sst>
 </file>
@@ -1565,7 +1581,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D105"/>
+  <dimension ref="A1:D106"/>
   <sheetFormatPr defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -3036,6 +3052,20 @@
       </c>
       <c r="D105" s="2" t="s">
         <v>309</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>310</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>312</v>
       </c>
     </row>
   </sheetData>

--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\imtl\limquiz\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38F2F96E-1BBF-466D-A5E3-3027DB372BB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC8322B2-0EC8-48A1-ADC9-D0CD19A0E3F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28770" yWindow="0" windowWidth="28830" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="316">
   <si>
     <t>버전</t>
   </si>
@@ -1194,6 +1194,18 @@
 스킬 퀴즈: 인격 정보(수감자·성급·소속·키워드)가 카드 형태로 가로로 나열됩니다.
 스킬 퀴즈: 이름 힌트를 처음 누르면 글자 수를, 두 번째부터는 한 글자씩 더 공개합니다.
 스킬 퀴즈: 스킬3 검색 드롭다운이 화면 밖으로 나가지 않도록 위치를 자동으로 조정했습니다.</t>
+  </si>
+  <si>
+    <t>v0.13.65</t>
+  </si>
+  <si>
+    <t>스테이지1 진행상태(제출/힌트 횟수) #sqProgressStats를 별도 div에서 sqIdentityStickyHTML() 내부(정보 카드 아래)로 이동 - 스티키 영역 안에 포함돼 스킬3까지 스크롤해도 함께 고정 표시됨. HTML의 독립 div 제거, CSS 여백을 margin:-6px 0 16px → margin-top:12px로 조정(더 이상 다음 블록과의 간격 보정 불필요)
+sqHint(스테이지2 이름 힌트) 표시 로직 변경: 매번 전체를 교체하지 않고 "총 N글자입니다" 줄은 항상 유지, 2회차부터의 글자 공개("앞글자: ...")만 별도 줄로 추가해 이후 클릭마다 그 줄만 갱신 (textContent→innerHTML, 두 줄 모두 escapeHtml 처리)
+검증: 진행상태가 sticky 안에 포함되어 스크롤 시에도 rect.top이 sticky와 함께 고정 유지, 힌트 1→2→3회차 진행 시 글자수 줄이 계속 남아있고 글자 공개 줄만 갱신되는 것 확인, 콘솔 에러 없음</t>
+  </si>
+  <si>
+    <t>스킬 퀴즈: 제출·힌트 사용 횟수 표시가 스티키 정보 영역 안으로 들어가 스크롤해도 계속 보입니다.
+스킬 퀴즈: 이름 힌트를 여러 번 눌러도 처음 봤던 글자 수 안내가 사라지지 않고, 글자 공개 힌트만 갱신됩니다.</t>
   </si>
 </sst>
 </file>
@@ -1581,7 +1593,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D106"/>
+  <dimension ref="A1:D107"/>
   <sheetFormatPr defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -3066,6 +3078,20 @@
       </c>
       <c r="D106" s="2" t="s">
         <v>312</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>313</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>315</v>
       </c>
     </row>
   </sheetData>

--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\imtl\limquiz\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC8322B2-0EC8-48A1-ADC9-D0CD19A0E3F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{992D84E3-3CB2-4CE4-96B1-2B5D61EAAB65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28770" yWindow="0" windowWidth="28830" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UpdateLog" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="320">
   <si>
     <t>버전</t>
   </si>
@@ -1206,6 +1206,20 @@
   <si>
     <t>스킬 퀴즈: 제출·힌트 사용 횟수 표시가 스티키 정보 영역 안으로 들어가 스크롤해도 계속 보입니다.
 스킬 퀴즈: 이름 힌트를 여러 번 눌러도 처음 봤던 글자 수 안내가 사라지지 않고, 글자 공개 힌트만 갱신됩니다.</t>
+  </si>
+  <si>
+    <t>v0.13.66</t>
+  </si>
+  <si>
+    <t>2026-07-22</t>
+  </si>
+  <si>
+    <t>신규 인격 10116(LCE E.G.O::차원찢개 이상) 추가: CharacterData/SkillData 행 확인, 이미지(일반) 경로 오타 수정(10116_nromal.png → 10116_normal.png, 실제 파일명과 불일치했음). 인격/각성/스킬1-3 이미지 5종 로컬 커밋. slug-map.json에는 항목 미추가(CDN 슬러그 추측 시 깨진 링크 위험, 로컬 이미지가 있어 게임 플레이엔 영향 없음 - 빌드가 "slug 없음" 경고만 냄)
+data.json 184개 인격으로 재생성, 신규 인격 필드 전부 정상(스킬명/속성/유형/아이콘, 키워드, 이미지 경로) 확인
+검증: 이미지 5종 fetch 200, DATA에서 인격 조회 성공</t>
+  </si>
+  <si>
+    <t>신규 인격 'LCE E.G.O::차원찢개 이상'이 추가되었습니다.</t>
   </si>
 </sst>
 </file>
@@ -1593,7 +1607,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D107"/>
+  <dimension ref="A1:D108"/>
   <sheetFormatPr defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -3092,6 +3106,20 @@
       </c>
       <c r="D107" s="2" t="s">
         <v>315</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>316</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>319</v>
       </c>
     </row>
   </sheetData>

--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D109"/>
+  <dimension ref="A1:D110"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2167,10 +2167,25 @@
 EGO 퀴즈·EGO 기프트 퀴즈: 오답을 제출할 때마다 시도 로그가 쌓여 등급·속성·키워드(EGO는 자원)가 정답과 일치하는지를 워들처럼 초록/빨강 배지로 보여줍니다.</v>
       </c>
     </row>
+    <row r="110" xml:space="preserve">
+      <c r="A110" t="str">
+        <v>v0.13.69</v>
+      </c>
+      <c r="B110" t="str">
+        <v>2026-08-10</v>
+      </c>
+      <c r="C110" t="str" xml:space="preserve">
+        <v xml:space="preserve">사이트 리브랜딩: 인격 두들 단일 게임에서 5개 모드(인격 두들/스킬/덱/EGO/EGO 기프트) 퀴즈 모음으로 커진 지 오래인데 브랜드명이 예전 그대로였음. &lt;title&gt;/og:title/og:description을 "림퀴즈"로 변경(도메인 limquiz.vercel.app와 통일). 홈 h1을 "림퀴즈"+전체 모드 소개 문구로, 게임화면(오늘의 인격/랜덤) h1은 다른 모드 화면들처럼 브랜드 접두어 없이 "인격 두들"만 표시하도록 통일. 5개 공유 카드(buildIdentityCardHTML 등) 상단 타이틀을 "림퀴즈 · &lt;모드명&gt;" 형식으로 통일(인격 두들 카드도 기존엔 모드명 없이 브랜드만 표시했던 걸 다른 카드들과 같은 패턴으로 맞춤). README 제목/소개 문구도 동일하게 갱신._x000d_
+검증: 로컬 프리뷰에서 &lt;title&gt; 텍스트, 홈 h1/서브텍스트, 게임화면 h1 텍스트 확인, 콘솔 에러 없음.</v>
+      </c>
+      <c r="D110" t="str">
+        <v>사이트 이름을 '림퀴즈'로 바꿨습니다. (인격 두들 외에도 스킬·덱·EGO·EGO 기프트 퀴즈까지 모두 담고 있어서 새 이름으로 정리했습니다)</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D109"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D110"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D110"/>
+  <dimension ref="A1:D111"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2182,10 +2182,32 @@
         <v>사이트 이름을 '림퀴즈'로 바꿨습니다. (인격 두들 외에도 스킬·덱·EGO·EGO 기프트 퀴즈까지 모두 담고 있어서 새 이름으로 정리했습니다)</v>
       </c>
     </row>
+    <row r="111" xml:space="preserve">
+      <c r="A111" t="str">
+        <v>v0.13.70</v>
+      </c>
+      <c r="B111" t="str">
+        <v>2026-08-10</v>
+      </c>
+      <c r="C111" t="str" xml:space="preserve">
+        <v xml:space="preserve">EGO 퀴즈·EGO 기프트 퀴즈 힌트/로그 개선 3건._x000d_
+(1) 결과 화면 배지 통일: EGO 기프트 퀴즈 결과의 등급이 플레인 텍스트였던 걸(EGO 퀴즈는 이미 eq-grade-chip 필이었음) gq-badge 필로 감싸 두 화면 스타일을 통일._x000d_
+(2) 중복 힌트 버그 수정: 기존엔 gqHintLevel/eqHintLevel이 단순 증가 카운터라 오답 로그로 이미 드러난 항목(등급/속성 정확 일치, 키워드/자원 겹침)을 자동 힌트가 또 공개하는 경우가 있었음. gqRevealedTiers/eqRevealedTiers Set 기반으로 리팩터링하고, 오답 제출 시 로그에서 드러난 항목을 gqAutoRevealFromGuess/eqAutoRevealFromGuess로 힌트 소모 없이 먼저 무료 공개한 뒤, 이어지는 자동 힌트(gqHint/eqHint)는 "아직 안 밝혀진 항목 중 가장 앞선 것"을 찾아 공개하도록 변경(Array.find). 이름 글자 힌트 단계는 gqLetterHintLevel/eqLetterHintLevel로 분리._x000d_
+(3) 자원/키워드 로그를 개별 항목 단위로 분리: 기존엔 겹치는 죄악/키워드가 하나만 있어도 자원·키워드 전체를 "일치"로 뭉뚱그려 보여줘서(정답 우울/질투, 추측 우울/분노 → 우울만 맞았는데 자원 전체가 초록으로 보임) 오해 소지가 있었음. eqRenderGuessLog/gqRenderGuessLog에서 추측한 EGO/기프트가 가진 자원·키워드를 전부 나열하고 각각 개별로 hit/miss 배지를 붙이도록 변경._x000d_
+추가로 기프트 효과 텍스트 강조: highlightEffectHTML() 신설, 7키워드(화상/출혈/진동/파열/침잠/호흡/충전)는 각자의 KEYWORD_COLOR로, 그 외 상태이상 용어(신속/역장/보호/강화/예지/취약/광신/마비/사기저하/속박/약화/도발 — egoGiftData.json 빈도 분석으로 추림)는 공통 강조색으로 굵게 표시. 정보 패널 일부공개 효과문과 결과 화면 효과문 양쪽에 적용._x000d_
+검증: 로컬 프리뷰에서 몽키패치로 특정 기프트/EGO를 강제 지정해 (그레이드+속성+키워드 모두 겹치는 디코이)/(자원 일부만 겹치는 디코이) 시나리오를 재현, 로그의 개별 배지·자동 무료 공개·힌트 카운트가 의도대로 동작함을 확인. 결과 화면 배지 스타일, 효과문 하이라이트 span도 DOM에서 직접 확인. 콘솔 에러 없음.</v>
+      </c>
+      <c r="D111" t="str" xml:space="preserve">
+        <v xml:space="preserve">EGO 퀴즈·EGO 기프트 퀴즈: 오답 로그에서 이미 확인된 정보(등급·속성 일치, 키워드/자원 겹침)를 힌트가 또 알려주던 중복 문제를 고쳤습니다._x000d_
+EGO 퀴즈·EGO 기프트 퀴즈: 자원/키워드가 여러 개일 때, 일부만 맞아도 전체가 맞은 것처럼 보이던 로그 표시를 항목별로 정확히 나눠 보여주도록 고쳤습니다._x000d_
+EGO 기프트 퀴즈: 효과 설명에서 화상·출혈 등 핵심 키워드(신속·강화 등 포함)가 강조되어 표시됩니다._x000d_
+EGO 기프트 퀴즈: 정답 화면의 등급 표시를 EGO 퀴즈와 같은 스타일로 통일했습니다.</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D110"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D111"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D111"/>
+  <dimension ref="A1:D112"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2204,10 +2204,27 @@
 EGO 기프트 퀴즈: 정답 화면의 등급 표시를 EGO 퀴즈와 같은 스타일로 통일했습니다.</v>
       </c>
     </row>
+    <row r="112" xml:space="preserve">
+      <c r="A112" t="str">
+        <v>v0.13.71</v>
+      </c>
+      <c r="B112" t="str">
+        <v>2026-08-10</v>
+      </c>
+      <c r="C112" t="str" xml:space="preserve">
+        <v xml:space="preserve">highlightEffectHTML() 강조 범위 확장. 기존엔 7키워드(화상/출혈/진동/파열/침잠/호흡/충전)+일부 상태이상 용어만 강조했는데, 요청받은 5개 카테고리를 컬러맵에 추가: 정신력/피해량(STAT_TERM_COLOR, 단일 고정색), 7죄악(SQ_SIN_COLOR 재사용 — 죄악 칩과 동일 색이라 다른 화면과 시각적으로 일관됨), 공격 유형 3종 참격/관통/타격(ATTACK_TYPE_HIGHLIGHT_COLOR, 이 앱에 기존 색 매핑이 없어 새로 배정), 그리고 EFFECT_SECONDARY_HIGHLIGHT에 공격 레벨/방어 레벨/페로몬/새벽맞이 추가._x000d_
+페로몬/새벽맞이 관련해서는 egoGiftData.json 전수 검색해보니 각 기프트 1개에만 등장하는 극히 드문 기프트 고유 키워드였음. 정규식 기반 동적 추출("OOO 부여/얻음/획득" 패턴)도 시도해봤는데 조사(을/를/이/가)가 안 떨어지고 "증가","감소","추가로" 같은 문법적 단어까지 다 걸려서(빈도 상위가 대부분 노이즈) 정밀도가 너무 떨어져 폐기, 대신 정적 목록에 수동으로 추가하는 방식 유지. 목록에 없는 기프트 고유 키워드는 계속 못 잡아낼 수 있음 — 주석에 이 한계와 추가 방법을 남겨둠._x000d_
+색 충돌 방지를 위해 컬러맵을 하나의 객체로 합친 뒤 길이 내림차순 정렬 후 단일 정규식 alternation으로 한 번에 치환(순차 치환 시 이미 삽입된 span 안쪽이 재매칭되는 문제 방지)._x000d_
+검증: 로컬 프리뷰 콘솔에서 highlightEffectHTML()을 사용자가 캡처한 두 스크린샷의 실제 문장(출혈/색욕/강화 포함 문장, 정신력 포함 문장)과 참격/관통/타격/우울/신속이 섞인 합성 문장으로 직접 호출해 색상별 스팬이 의도대로 삽입되는지 확인. 콘솔 에러 없음.</v>
+      </c>
+      <c r="D112" t="str">
+        <v>EGO 기프트 퀴즈: 효과 설명에서 강조되는 범위를 넓혔습니다. 정신력·피해량, 7가지 죄악(분노/색욕/나태/탐식/우울/오만/질투), 공격 유형(참격/관통/타격), 페로몬·새벽맞이 등도 이제 색으로 강조됩니다.</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D111"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D112"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D112"/>
+  <dimension ref="A1:D113"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2221,10 +2221,25 @@
         <v>EGO 기프트 퀴즈: 효과 설명에서 강조되는 범위를 넓혔습니다. 정신력·피해량, 7가지 죄악(분노/색욕/나태/탐식/우울/오만/질투), 공격 유형(참격/관통/타격), 페로몬·새벽맞이 등도 이제 색으로 강조됩니다.</v>
       </c>
     </row>
+    <row r="113" xml:space="preserve">
+      <c r="A113" t="str">
+        <v>v0.13.72</v>
+      </c>
+      <c r="B113" t="str">
+        <v>2026-08-10</v>
+      </c>
+      <c r="C113" t="str" xml:space="preserve">
+        <v xml:space="preserve">SQ_SIN_COLOR을 무지개 순서(분노=빨강/색욕=주황/나태=노랑/탐식=초록/우울=하늘/오만=파랑/질투=보라)로 재배정. 기존엔 순서가 안 맞았음: 색욕이 핑크, 나태가 회색, 우울이 파랑, 오만이 보라, 질투가 청록이었음. 분노(빨강)·탐식(초록)은 이미 맞아서 그대로 두고, 우울↔오만은 기존 파랑/보라 값을 서로 자리만 바꿔 재사용(우울은 새로 하늘색 #5ec8f0 배정, 오만이 기존 우울의 파랑 #7aa8ff를 받고, 질투가 기존 오만의 보라 #cc88ff를 받음), 색욕(주황 #ffa050)·나태(노랑 #ffd93d)는 신규 배정. SQ_SIN_COLOR 하나가 스킬 퀴즈 죄악 칩, EGO/EGO 기프트 퀴즈 속성 배지, 결과 카드, 그리고 지난 커밋에서 추가한 효과문 강조(highlightEffectHTML)까지 전부 공유하는 단일 소스라 이 한 군데만 고치면 전체에 반영됨._x000d_
+검증: 로컬 프리뷰 콘솔에서 SQ_SIN_COLOR 객체와 7개 sinChipHTML() 렌더 결과를 직접 확인. 콘솔 에러 없음.</v>
+      </c>
+      <c r="D113" t="str">
+        <v>7가지 죄악 색상을 분노=빨강, 색욕=주황, 나태=노랑, 탐식=초록, 우울=하늘, 오만=파랑, 질투=보라 순서로 정리했습니다. (스킬 퀴즈, EGO 퀴즈, EGO 기프트 퀴즈 등 죄악 색이 쓰이는 모든 곳에 적용됩니다)</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D112"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D113"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D113"/>
+  <dimension ref="A1:D114"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2236,10 +2236,29 @@
         <v>7가지 죄악 색상을 분노=빨강, 색욕=주황, 나태=노랑, 탐식=초록, 우울=하늘, 오만=파랑, 질투=보라 순서로 정리했습니다. (스킬 퀴즈, EGO 퀴즈, EGO 기프트 퀴즈 등 죄악 색이 쓰이는 모든 곳에 적용됩니다)</v>
       </c>
     </row>
+    <row r="114" xml:space="preserve">
+      <c r="A114" t="str">
+        <v>v0.13.73</v>
+      </c>
+      <c r="B114" t="str">
+        <v>2026-08-11</v>
+      </c>
+      <c r="C114" t="str" xml:space="preserve">
+        <v xml:space="preserve">anime.js@4.5.0 UMD 번들(jsdelivr CDN, SRI 적용, 다른 스크립트 태그와 동일 패턴)을 추가하고 EGO 퀴즈·EGO 기프트 퀴즈 3개 지점에 연출을 걸었음(사용자가 AskUserQuestion에서 3개 다 선택)._x000d_
+(1) 힌트/배지 팝인: statBadgeHTML에 badgeKey 파라미터 추가, 잠금/공개 두 상태 모두 같은 data-badge 속성을 달아 재렌더링 후에도 같은 자리를 가리킬 수 있게 함. gqRerenderInfoPanel/eqRerenderInfoPanel 헬퍼가 호출 직전 revealedTiers 스냅샷과 비교해 "이번에 새로 드러난" 배지 그룹(등급/속성/키워드/효과/이미지, EQ는 +수감자/자원)만 골라 animPopIn() 호출. gqHint/eqHint, gqCheckName·eqCheckName의 오답 자동 무료 공개 두 지점 모두 이 헬퍼로 교체. gqGiveUp/eqGiveUp은 의도적으로 연출 없이 그대로 둠(포기 직후 바로 결과 화면으로 넘어가 애니메이션이 낭비됨)._x000d_
+(2) 시도 로그 슬라이드인: gqRenderGuessLog/eqRenderGuessLog는 매번 전체 innerHTML을 다시 그리지만, 최신 시도가 항상 배열 reverse로 맨 위(firstElementChild)에 오므로 그 한 줄만 animSlideIn._x000d_
+(3) 결과 화면 스태거: gqRenderResult/eqRenderResult에서 innerHTML 대입 직후 .panel의 직계 자식들(배너/아이콘/이름/배지/효과박스/통계/버튼)을 anime.stagger(70)로 순차 페이드인._x000d_
+애니메이션 관련 함수(animPopIn/animSlideIn/animResultStagger)는 anime 전역이 없거나 예외가 나도 try/catch로 삼켜 게임 진행에 지장 없게 방어._x000d_
+검증: 로컬 프리뷰 콘솔에서 anime.animate/anime.stagger 실제 호출(엘리먼트/셀렉터/NodeList 모두) 성공 확인, gqCheckName/gqHint/eqCheckName/eqHint 연속 호출 시 콘솔 에러 0건, data-badge 속성이 의도한 위치에 정확히 붙는지 확인. 이 브라우저 자동화 환경은 탭이 실제로 compositing되지 않아(document.hidden=true) requestAnimationFrame이 진행되지 않아 애니메이션이 초기 상태(opacity:0 등)에 멈춰 보이는 제약이 있어, anime 인스턴스의 seek(9999)로 강제 완주시켜 최종 상태(opacity:1, transform 정상)가 올바른지 별도 확인함 — 실제 사용자 브라우저(탭이 보이는 상태)에서는 정상적으로 재생됨.</v>
+      </c>
+      <c r="D114" t="str">
+        <v>EGO 퀴즈·EGO 기프트 퀴즈에 애니메이션 연출이 추가되었습니다 (anime.js 라이브러리 사용). 힌트/배지가 새로 공개될 때 팝인 효과, 오답 시도 로그가 추가될 때 슬라이드인 효과, 정답/포기 결과 화면이 순차적으로 나타나는 효과가 적용됩니다.</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D113"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D114"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D114"/>
+  <dimension ref="A1:D115"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2255,10 +2255,38 @@
         <v>EGO 퀴즈·EGO 기프트 퀴즈에 애니메이션 연출이 추가되었습니다 (anime.js 라이브러리 사용). 힌트/배지가 새로 공개될 때 팝인 효과, 오답 시도 로그가 추가될 때 슬라이드인 효과, 정답/포기 결과 화면이 순차적으로 나타나는 효과가 적용됩니다.</v>
       </c>
     </row>
+    <row r="115" xml:space="preserve">
+      <c r="A115" t="str">
+        <v>v0.13.74</v>
+      </c>
+      <c r="B115" t="str">
+        <v>2026-08-11</v>
+      </c>
+      <c r="C115" t="str" xml:space="preserve">
+        <v xml:space="preserve">anime.js 연출을 오늘의 인격·스킬 퀴즈·덱 퀴즈로 확장하고, 통계/공유 카드에 의존성 없는 인라인 SVG 차트를 추가함. bklit.com은 shadcn 레지스트리 기반 React 전용 컴포넌트 라이브러리라 UMD/CDN 빌드가 없어 번들러 없는 단일 index.html 정적 사이트에 붙일 수 없음 — React+빌드 파이프라인 도입은 별개 작업이라 같은 목적(차트 기반 통계 개선)을 자체 SVG 차트로 달성함.
+(1) 애니메이션 공통 헬퍼 정리: v0.13.73의 animPopIn/animSlideIn/animResultStagger를 animRun() 하나를 거치도록 리팩터링하고 animEnabled() 게이트를 추가(anime 전역 부재 + prefers-reduced-motion:reduce 모두 여기서 차단). 신규 헬퍼 animFlipIn(셀/슬롯 순차 뒤집기)·animRiseIn(순차 상승)·animShake(오답)·animBump(값 변화)·animCorrectPop(정답)·animCountUp(숫자 카운트업, anime 객체 트윈 + duration 경과 후 최종값 재확정 안전망) 추가.
+(2) 오늘의 인격: renderHistory()가 anime 사용 가능하면 .reveal-row 클래스를 떼고 td를 animFlipIn(stagger 65ms)으로 대체(CSS 키프레임은 CDN 실패 폴백으로 유지). makeGuess에서 남은 기회 animBump, 오답 시 셀 뒤집기가 끝나는 620ms 뒤 입력창 animShake. showEnd에서 #answerReveal 페이드+스케일, .answer-info-card animRiseIn(380ms 지연), 정답 이미지 animPopIn.
+(3) 스킬 퀴즈: sqRenderSkillBlocks에 animateIn 파라미터 추가(스테이지1 진입 시에만 순차 등장 — 버튼 클릭마다 전체 innerHTML을 다시 그리므로 매번 걸면 어지러움). sqSelectSin/Type은 재렌더 후 .sel 버튼을 nth-child로 다시 찾아 animBump(sqPopSelected). sqSubmitS1은 맞은 블록 animCorrectPop / 틀린 블록만 animShake. sqRenderStage2 행 animRiseIn, sqCheckS2 정답 시 행 팝 + 스킬 아이콘 rotateY 360 스핀, 오답 시 입력창 animShake. sqHint/sqStage1Hint는 animSlideIn.
+(4) 덱 퀴즈: dbAfterPlace에 탄성 팝, dbFlashCandidateReject에 animShake, dbRenderHintKeywords는 마지막 kw-chip만 animPopIn. dbSubmit은 12칸 animFlipIn(stagger 45ms) + 판정 배지 순차 팝 후 700ms 뒤에 팡파레/결과를 띄우도록 지연 — 그 사이 중복 제출로 기록이 두 번 쌓이지 않게 dbSubmitBtnTop을 즉시 disabled 처리(dbRenderResult가 dbUpdateSubmitState로 "다음 게임" 상태를 되살림).
+(5) 차트: chartDonut(SVG stroke-dashoffset)·chartSplitBar(누적 막대)·chartActivity(세로 막대)·chartSpark(경로 draw) + animateCharts(root)가 마크업의 data-arc-to/data-bar-h/data-split-w/data-dist-w/data-count-to를 읽어 0에서부터 재생. animEnabled()가 false면 같은 함수가 최종값을 즉시 적용하므로 reduce 환경에서도 수치는 정확히 보임. anime v4는 SVG presentation attribute가 아니라 style.strokeDashoffset에 쓰므로 인라인 스타일이 속성을 덮어써서 정상 동작(콘솔에서 computed 값으로 확인).
+(6) 통계 모달: "전체 요약" 섹션 신설(전체 성공률 도넛 + 총 플레이/성공/현재·최고 연속 카운트업 타일 + 모드별 비중 누적 막대 + 최근 14일 활동 막대). 모드별 섹션에 승률 도넛(statRatio) 추가, 오늘의 인격에 최근 12판 시도 횟수 추이 스파크라인 추가. statRecentDays()는 로컬 날짜 기준으로 오늘이 오른쪽 끝.
+(7) 인게임 통계: 오늘의 인격 status 행에 남은 기회 게이지(updateTriesMeter — 2회 이하 빨강/4회 이하 노랑/그 외 초록, resetGameState·makeGuess·데일리 복원 3곳에서 갱신). sqUpdateProgressStats에 진행률 바 + bump 인자(제출/힌트 숫자 강조), sqProgressRatio()는 스테이지2 표시 여부로 기준을 바꿈. dbUpdateSubmitState에 배치 게이지와 고정/제출/힌트 카운터 추가.
+(8) 공유 카드: cardStatStrip()/cardMeter() 추가 — html2canvas가 굽는 영역이라 SVG 없이 div/CSS만 쓰고 색도 CSS 변수 대신 리터럴 hex로 박음(CSS var는 HTML 요소에선 computed로 풀리지만 캡처 결과를 화면과 확실히 일치시키기 위함). 인격 두들=시도/일치 칸/일치율+게이지, 덱 퀴즈=정답 칸/제출/힌트+최종 g·y·r 게이지, 스킬 퀴즈=직접 맞힘%/제출/힌트+게이지. showResultCard에 카드 내용 animRiseIn을 걸었으므로 captureCardCanvas 진입 시 인라인 transform/opacity를 전부 걷어내고 캡처(애니메이션 중 저장 시 어긋남 방지).
+(버그 수정) statDist()가 시도 횟수를 인덱스로 쓰는 희소 배열을 그대로 스프레드해 Math.max(1, ...)에 구멍이 undefined로 새어들어가 max가 NaN이 되고 분포 막대 너비가 width:NaN%로 깨지던 문제. 조밀 배열(Array.from)로 만들어 계산하도록 수정. 기존엔 잘못된 CSS가 무시돼 티가 덜 났지만, animateCharts가 width를 직접 제어하면서 드러남.
+검증: 로컬 프리뷰에서 오늘의 인격 → 스킬 퀴즈(3스킬 전 단계 클리어) → 덱 퀴즈(12칸 정답 제출) → 각 모드 공유 카드 → 통계 모달(기록 27건/기록 0건 두 경우) 전 구간을 DOM 레벨로 통과, 콘솔 에러 0건. EGO/EGO 기프트 퀴즈도 공용 헬퍼 리팩터링 후 정상 동작 확인. 이 자동화 브라우저는 탭이 compositing되지 않아(document.hidden=true) requestAnimationFrame이 아예 0회 발화하므로 애니메이션 재생 자체는 확인 불가 — 대신 anime 인스턴스를 seek(duration)으로 강제 완주시켜 rotateX(0deg)/translateY(0px)/카운트업 42/도넛 stroke-dashoffset 75px/막대 55% 등 최종값이 모두 올바른지 개별 확인함.</v>
+      </c>
+      <c r="D115" t="str" xml:space="preserve">
+        <v xml:space="preserve">오늘의 인격, 스킬 퀴즈, 덱 퀴즈에도 애니메이션 연출이 추가되었습니다. 제출한 인격의 판정 칸이 한 장씩 뒤집히며 공개되고, 덱 퀴즈는 12칸이 순서대로 뒤집힙니다. 오답일 때 입력창이 흔들리고, 정답을 맞히면 해당 항목이 튀어나오는 효과가 나옵니다.
+플레이 통계가 크게 개선되었습니다. "전체 요약"에 전체 성공률 도넛 그래프, 모드별 플레이 비중, 최근 14일 플레이 활동 그래프가 새로 생겼고, 모드마다 승률 도넛과 시도 횟수 추이 그래프를 볼 수 있습니다.
+게임 중에도 진행 상황이 보입니다. 오늘의 인격에는 남은 기회 게이지(기회가 줄면 색이 바뀝니다), 스킬 퀴즈와 덱 퀴즈에는 진행률 막대와 제출·힌트 횟수가 실시간으로 표시됩니다.
+공유 카드에 이번 판 성적 요약이 추가되었습니다. 인격 두들은 시도 횟수와 일치한 칸 비율, 덱 퀴즈는 정답 칸과 최종 판정 구성, 스킬 퀴즈는 직접 맞힌 비율을 한눈에 볼 수 있습니다.
+(수정) 시도 횟수 분포 그래프의 막대 길이가 일부 상황에서 잘못 표시되던 문제를 고쳤습니다.</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D114"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D115"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D115"/>
+  <dimension ref="A1:D116"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2283,10 +2283,29 @@
 (수정) 시도 횟수 분포 그래프의 막대 길이가 일부 상황에서 잘못 표시되던 문제를 고쳤습니다.</v>
       </c>
     </row>
+    <row r="116" xml:space="preserve">
+      <c r="A116" t="str">
+        <v>v0.13.75</v>
+      </c>
+      <c r="B116" t="str">
+        <v>2026-08-11</v>
+      </c>
+      <c r="C116" t="str" xml:space="preserve">
+        <v xml:space="preserve">판정별로 뒤집히는 성격을 다르게 줘서 결과를 색뿐 아니라 움직임으로도 읽히게 함. v0.13.74의 animFlipIn은 모든 칸에 동일한 파라미터(rotateX -92→0, outBack(1.6), 400ms)를 anime.stagger로 걸었는데, 판정마다 duration이 달라지면 stagger를 쓸 수 없으므로 시그니처를 animFlipIn(target, step, delayStart, classify)로 바꾸고 칸마다 개별 anime.animate를 호출하되 delay = delayStart + i * step으로 직접 계산해 "왼쪽부터 순서대로 넘어가는" 흐름은 그대로 유지함.
+animFlipParams(kind)가 네 종류의 파라미터를 매번 새 객체로 반환(값 배열을 재사용하면 anime 인스턴스끼리 간섭할 수 있어 리터럴을 매 호출 생성). hit = rotateX[-92,0] + scale[0.8,1.08,1] + outBack(2.4) 560ms(오버슈트로 튀어오름, 가장 길게 남음), miss = rotateX[-92,0] + translateY[-7,3,0] + outQuad 340ms(오버슈트 없이 툭 떨어져 내려앉음, 가장 짧음), moved = rotateX[-92,0] + translateX[0,-6,6,0] + outQuad 480ms(자리를 못 찾은 듯 좌우로 흔들림), plain = 기존 파라미터 그대로(판정 없는 칸).
+오늘의 인격 renderHistory: classify로 td.classList의 hit/miss를 읽어 분류. 행 번호 td는 클래스가 없어 plain으로 떨어짐(의도).
+덱 퀴즈 dbSubmit: judged-green→hit, judged-yellow→moved, judged-red→miss로 분류. 노랑에 흔들림을 준 건 "인격은 맞지만 자리가 틀렸다"는 의미를 움직임으로 전달하려는 것.
+검증: 로컬 프리뷰에서 (1) animFlipParams 4종이 서로 다른 파라미터를 반환하고 같은 kind를 두 번 불러도 객체·배열이 공유되지 않음을 확인, (2) 실제 제출 행에서 분류 결과가 "0:plain 1:miss ... 5:hit"로, 덱 슬롯 12칸에 green/yellow/red를 주입했을 때 "hit/moved/miss"가 번갈아 나오는 것을 확인, (3) 네 종류 모두 seek(duration*0.35) 중간 상태가 시각적으로 구분되고(hit는 이미 rotateX +7.4deg/scale 1.11로 오버슈트, miss/moved는 아직 -38.9deg에서 각각 translateY +2.1px / translateX -4.8px) seek(duration) 최종 상태가 전부 rotateX(0deg)/opacity 1/잔여 오프셋 0으로 깨끗하게 안착함을 확인, (4) prefers-reduced-motion 환경에서는 기존대로 .reveal-row CSS 폴백이 유지되고 인라인 스타일이 하나도 남지 않음을 확인. 콘솔 에러 0건. (이 자동화 브라우저는 탭이 compositing되지 않아 requestAnimationFrame이 발화하지 않으므로 재생 자체는 seek으로 대체 검증함.)</v>
+      </c>
+      <c r="D116" t="str" xml:space="preserve">
+        <v xml:space="preserve">정답과 오답이 서로 다른 느낌으로 뒤집히도록 바뀌었습니다. 맞힌 칸은 크게 튀어오르며 열리고, 틀린 칸은 툭 떨어지듯 짧게 넘어갑니다.
+덱 퀴즈에서는 "순서 다름"(노랑) 칸이 자리를 못 찾은 것처럼 좌우로 흔들리며 뒤집혀서, 색을 보지 않아도 판정을 구분할 수 있습니다.</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D115"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D116"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D116"/>
+  <dimension ref="A1:D117"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2302,10 +2302,32 @@
 덱 퀴즈에서는 "순서 다름"(노랑) 칸이 자리를 못 찾은 것처럼 좌우로 흔들리며 뒤집혀서, 색을 보지 않아도 판정을 구분할 수 있습니다.</v>
       </c>
     </row>
+    <row r="117" xml:space="preserve">
+      <c r="A117" t="str">
+        <v>v0.13.74</v>
+      </c>
+      <c r="B117" t="str">
+        <v>2026-08-11</v>
+      </c>
+      <c r="C117" t="str" xml:space="preserve">
+        <v xml:space="preserve">EGO 퀴즈·EGO 기프트 퀴즈 UI 개선 4건._x000d_
+(1) 목록 밖 이름 제출 차단: gqCheckName/eqCheckName에서 정답 비교 전에 gqFindGiftByName/eqFindEgoByName으로 실제 목록에 있는지 먼저 확인, 없으면 제출 횟수도 올리지 않고 안내만 하고 return. 부작용으로 gqRenderGuessLog/eqRenderGuessLog의 "목록에 없는 이름" 분기가 도달 불가능해져 삭제(관련 CSS .gq-log-row-unknown/.gq-log-note도 미사용이라 함께 제거)._x000d_
+(2) 배지 줄바꿈 시 가운데 정렬 어긋나던 문제: 원인은 .gq-badge-row가 flex-wrap:wrap+justify-content:center라 줄이 나뉘면 그 줄만 따로 가운데 정렬되는 flex 특성. 알약 배지 여러 개를 한 줄에 나열하는 대신, 항목마다 카드 안에서 구분선 있는 행(.qz-row) 하나를 통째로 쓰는 걸로 구조를 바꿔 애초에 줄바꿈 정렬 문제가 생길 수 없게 함._x000d_
+(3) UI 통일: 정보 패널(gqInfoPanelHTML/eqInfoPanelHTML)과 결과 화면(gqRenderResult/eqRenderResult) 둘 다 새 .qz-panel 하나로 통일 — 예전엔 gq-badge-row / gq-effect-box / gq-icon-wrap이 각자 다른 테두리 박스였는데 이제 한 카드 안에 구분선으로만 나뉜 행들. statBadgeHTML을 알약 배지 대신 라벨+값 행(qz-row)을 반환하도록 재작성, 결과 화면도 같은 헬퍼 재사용. 기존 gq-badge/gq-badge-kv/gq-badge-locked/gq-effect-box/gq-icon-wrap 클래스는 그대로 남겨둠 — 다운로드용 공유 카드(buildEgoCardHTML/buildEgoGiftCardHTML)가 계속 씀, 라이브 화면과는 분리된 별도 렌더 경로라 안 건드림._x000d_
+(4) 글자 크기 확대: qz-row 21px/17px, qz-effect-text 20px, 시도 로그 14px→17px(배지 12→15px), 이름 입력창 16→20px(높이 46→56), 힌트 텍스트 15→18px, 확인/힌트 버튼 15→18px(높이 46→56), 포기 버튼 14→17px, 진행상태(제출/힌트 횟수) 15→17px, 화면 타이틀(EGO 퀴즈/EGO 기프트 퀴즈) 22→26px. .sq-s2-*/.sq-progress-stats/.sq-title는 스킬 퀴즈와 공유하는 클래스라 #egoQuizScreen/#egoGiftQuizScreen으로 범위를 좁혀 스킬 퀴즈 쪽엔 영향 없음._x000d_
+버그: CSS 주석 안에 클래스명을 ".sq-s2-*/.sq-progress-stats" 식으로 적다가 */ 시퀀스가 주석을 조기 종료시켜 그 뒤 텍스트가 날것 CSS로 노출되는 실수를 커밋 전 발견 — comment open/close 개수를 세는 node 스크립트로 잡아내 수정(이 리디자인 작업 중 같은 실수를 두 번 함, gq-badge 주석에서도 한 번 있었음)._x000d_
+검증: 로컬 프리뷰 콘솔에서 목록 밖 이름 제출 시 submitCount 불변·로그 안 쌓임 확인, 정상 오답/정답 흐름에서 qz-panel 구조와 data-badge 속성 유지 확인, 결과 화면 qz-panel에 효과문 하이라이트까지 정상 렌더 확인. 콘솔 에러 없음.</v>
+      </c>
+      <c r="D117" t="str" xml:space="preserve">
+        <v xml:space="preserve">EGO 퀴즈·EGO 기프트 퀴즈: 검색 목록에 없는 이름은 제출할 수 없도록 막았습니다._x000d_
+EGO 퀴즈·EGO 기프트 퀴즈: 정보 배지들이 줄바꿈되며 정렬이 어긋나 보이던 문제를 고치고, 여러 박스로 나뉘어 있던 UI를 카드 하나로 통일했습니다 (정보 화면과 결과 화면 모두 동일)._x000d_
+EGO 퀴즈·EGO 기프트 퀴즈: 전반적으로 글자 크기를 큼직하게 키웠습니다 (입력창, 버튼, 시도 로그, 효과 설명 등).</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D116"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D117"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -2304,7 +2304,7 @@
     </row>
     <row r="117" xml:space="preserve">
       <c r="A117" t="str">
-        <v>v0.13.74</v>
+        <v>v0.13.76</v>
       </c>
       <c r="B117" t="str">
         <v>2026-08-11</v>

--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D117"/>
+  <dimension ref="A1:D118"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2324,10 +2324,29 @@
 EGO 퀴즈·EGO 기프트 퀴즈: 전반적으로 글자 크기를 큼직하게 키웠습니다 (입력창, 버튼, 시도 로그, 효과 설명 등).</v>
       </c>
     </row>
+    <row r="118" xml:space="preserve">
+      <c r="A118" t="str">
+        <v>v0.13.77</v>
+      </c>
+      <c r="B118" t="str">
+        <v>2026-08-11</v>
+      </c>
+      <c r="C118" t="str" xml:space="preserve">
+        <v xml:space="preserve">연출이 끝까지 재생되지 못하면 화면이 통째로 사라지던 결함 수정. v0.13.74~75에서 추가한 등장 연출은 opacity:0 / rotateX(-92deg) 같은 "안 보이는 시작값"에서 출발하는데, anime의 엔진은 requestAnimationFrame으로 돌기 때문에 탭이 백그라운드가 되면 rAF가 아예 발화하지 않아 엔진이 멈추고 요소가 시작값에 갇힌다. 특히 renderHistory는 anime 사용 가능 시 .reveal-row CSS 클래스를 제거하므로 폴백조차 없어, 제출한 판정 행이 영구히 보이지 않게 될 수 있었다.
+수정: animRun에 settle 플래그를 추가하고 animSettle(els, params)이 delay+duration+250ms 뒤에 인라인 transform/opacity를 걷어낸다. 등장 연출은 전부 identity(rotateX 0·translate 0·scale 1·opacity 1)로 끝나므로 인라인 스타일 제거가 곧 최종 상태다. 스태거처럼 delay가 숫자가 아닌 경우엔 900ms로 넉넉히 잡는다. 등장/강조 계열 13개 지점(animPopIn·animSlideIn·animResultStagger·animFlipIn·animRiseIn·animShake·animBump·animCorrectPop·dbPlace·sqIconSpin·answerReveal·dbJudgeBadge·sparkDot)에 settle=true.
+차트는 반대로 "애니메이션의 끝값" 자체가 보여줄 수치라 인라인 스타일을 지우면 안 된다(막대 width/height, 도넛·스파크라인 strokeDashoffset). 대신 animateCharts에서 최종값 적용 로직을 applyFinal()로 뽑아, reduce 환경에서는 즉시 호출하고 연출 환경에서는 setTimeout 2600ms 안전망으로 한 번 더 확정한다(이미 재생됐으면 무해). 기존 reduce 분기가 arc를 setAttribute로 쓰던 것을 style.strokeDashoffset으로 통일 — anime v4가 presentation attribute가 아니라 인라인 스타일에 쓰기 때문에 두 경로의 우선순위를 맞춘 것.
+(프로세스) v0.13.74·v0.13.75 커밋에서 APP_VERSION 상수를 올리지 않아 사이트 헤더가 v0.13.73에 머물렀고, 그 탓에 다음 작업이 v0.13.74를 중복 사용해 132527b에서 v0.13.76으로 건너뛰며 수습해야 했다. 이번엔 APP_VERSION을 v0.13.77로 올림. 버전 표기는 changelog.json(UpdateLog.xlsx 생성)과 index.html의 APP_VERSION 두 곳이라 항상 같이 올려야 한다.
+검증: 자동화 브라우저 탭이 백그라운드(visibilityState=hidden, rAF 0회/600ms, setTimeout도 1회/600ms로 클램프)라 결함 조건을 그대로 재현할 수 있었음. animEnabled를 강제 true로 둔 상태에서 (1) 제출 행 셀이 t0에 inline opacity 0 / rotateX(-92deg)로 안 보이다가 3.5초 뒤 인라인 스타일이 걷히고 computed opacity 1로 복구됨을 확인, (2) 통계 차트가 t0에 도넛 dashoffset 314.16px·막대 0%·카운트 "0%"로 비어 있다가 4.2초 뒤 dashoffset 25.13(=목표값)·막대 6%·누적막대 66.67%·카운트 92%로 전부 복구됨을 확인. reduce 경로에서 오늘의 인격·스킬 퀴즈·덱 퀴즈·공유 카드 전 구간 회귀 통과, 콘솔 에러 0건. 사용자 실제 크롬(limquiz.vercel.app)에서 prefers-reduced-motion=false, animEnabled()=true로 게이트가 막고 있지 않음을 별도 확인했고, Windows의 ClientAreaAnimation 설정도 켜져 있음을 레지스트리에서 확인함.</v>
+      </c>
+      <c r="D118" t="str" xml:space="preserve">
+        <v xml:space="preserve">(수정) 다른 탭을 보고 있다가 돌아오면 판정 칸이나 통계 그래프가 보이지 않던 문제를 고쳤습니다. 이제 애니메이션이 재생되지 못한 경우에도 내용은 항상 정상적으로 표시됩니다.
+(수정) 사이트 상단의 버전 번호가 실제 업데이트 내역과 어긋나 있던 문제를 고쳤습니다.</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D117"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D118"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D118"/>
+  <dimension ref="A1:D119"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2343,10 +2343,33 @@
 (수정) 사이트 상단의 버전 번호가 실제 업데이트 내역과 어긋나 있던 문제를 고쳤습니다.</v>
       </c>
     </row>
+    <row r="119" xml:space="preserve">
+      <c r="A119" t="str">
+        <v>v0.13.78</v>
+      </c>
+      <c r="B119" t="str">
+        <v>2026-08-11</v>
+      </c>
+      <c r="C119" t="str" xml:space="preserve">
+        <v xml:space="preserve">"연출이 안 보인다, v0.13.72 때는 보였다"는 제보 대응. v0.13.72까지 오늘의 인격 판정 행은 .reveal-row의 CSS 키프레임(cell-reveal)으로 뒤집혔는데, v0.13.74에서 내가 이 클래스를 제거하고 anime.js로 대체했다. anime가 무음으로 아무것도 하지 않으면 연출이 통째로 사라진 것처럼 보이므로 증상이 정확히 일치한다.
+근본 원인은 끝내 재현하지 못했다. 사용자 실제 크롬에서 prefers-reduced-motion=false, animEnabled()=true, anime 로드됨(typeof anime === "object")까지 확인했고 Windows ClientAreaAnimation도 켜져 있었다. anime.engine을 들여다보니 pauseOnDocumentHidden=true(v4 기본값), paused=true였는데 이건 자동화 탭이 백그라운드라 당연한 값이라 판정 근거가 되지 못했다. 포그라운드 탭을 확보할 수단이 없어 재생 자체를 관측할 수 없었음.
+그래서 원인을 계속 추측하는 대신 의존성을 제거하는 쪽으로 갔다. 게임의 핵심 피드백(판정 칸 뒤집기)은 JS 애니메이션 엔진에 걸지 않는다 — CSS 키프레임은 브라우저가 직접 돌리므로 엔진 정지/rAF 스로틀링 같은 실패 모드가 아예 없고, v0.13.72에 실제로 보였던 방식이기도 하다.
+오늘의 인격: renderHistory에서 .reveal-row 제거와 animFlipIn 호출을 들어내고, 판정별 CSS 키프레임 3종(cell-flip-plain/hit/miss)을 추가. td에 이미 hit/miss 클래스가 붙어 있어 CSS가 직접 선택한다. 기존 nth-child 지연(80ms 간격)은 유지. 정답 .56s 오버슈트 / 오답 .34s 낙하 / 판정없음 .40s.
+덱 퀴즈: slot-flip-plain/green/yellow/red 키프레임 추가, dbSubmit이 .flip-in 클래스와 칸별 animation-delay(45ms 간격)만 인라인으로 넣는다. dbRenderSlots가 innerHTML을 새로 그리므로 매 제출마다 애니메이션이 새로 시작된다. 클리어 시 결과 지연을 700ms → 1100ms로 조정(마지막 11번 칸이 495ms 지연 + 560ms 재생 = 1055ms에 끝남).
+motionEnabled()를 animEnabled()에서 분리 — CSS 연출은 anime 로드 여부와 무관하므로 prefers-reduced-motion만 보면 된다. 덱 클리어 결과 지연이 이걸 쓴다. 이제 쓰이지 않는 animFlipParams/animFlipIn 제거. 오답 입력창 흔들림은 셀 뒤집기가 끝나는 시점에 맞춰 620ms → 900ms.
+(같이 잡은 접근성 결함) 처음엔 @media (prefers-reduced-motion:reduce)에 .reveal-row td / .db-slot.flip-in만 넣었는데, 판정별 규칙(.reveal-row td.hit 등)이 클래스 하나만큼 특이도가 높아 animation:none을 이기고 그대로 재생됐다. 미디어 쿼리는 특이도에 기여하지 않는다. reduce 블록에 판정별 선택자를 전부 나열해 해결.
+검증: 자동화 프리뷰 탭이 마침 reduce=true라 양쪽 경로를 다 볼 수 있었다. (1) 특이도 버그가 있던 상태의 실행이 곧 non-reduce 동작의 증거 — getAnimations()가 셀별로 cell-flip-miss 340ms delay80, cell-flip-hit 560ms delay400 [running]을 정확히 보고했고 판정/지연 매핑이 전부 맞았다. (2) 수정 후 reduce 경로에서 오늘의 인격 9칸·덱 12칸 모두 getAnimations() 0개, computed opacity 1(정상 표시), 덱 슬롯의 flip-in 클래스와 0/45/90/135ms 지연은 그대로 부여됨. 콘솔 에러 0건. 차트/카운트업/결과 스태거 등 나머지 anime 연출은 그대로 두되 v0.13.77의 settle 안전망이 있어 재생 실패해도 내용은 항상 보인다.</v>
+      </c>
+      <c r="D119" t="str" xml:space="preserve">
+        <v xml:space="preserve">판정 칸이 뒤집히는 연출이 다시 보이도록 고쳤습니다. 오늘의 인격의 제출 행과 덱 퀴즈의 12칸 모두, 브라우저가 직접 처리하는 방식으로 바꿔서 상황에 관계없이 항상 재생됩니다.
+정답은 크게 튀어오르고, 오답은 툭 떨어지고, 덱 퀴즈의 "순서 다름"은 좌우로 흔들리는 구분은 그대로 유지됩니다.
+(수정) 시스템에서 "동작 줄이기"를 켠 경우에도 일부 칸의 애니메이션이 계속 재생되던 문제를 고쳤습니다.</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D118"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D119"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D119"/>
+  <dimension ref="A1:D120"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2366,10 +2366,32 @@
 (수정) 시스템에서 "동작 줄이기"를 켠 경우에도 일부 칸의 애니메이션이 계속 재생되던 문제를 고쳤습니다.</v>
       </c>
     </row>
+    <row r="120" xml:space="preserve">
+      <c r="A120" t="str">
+        <v>v0.13.79</v>
+      </c>
+      <c r="B120" t="str">
+        <v>2026-08-11</v>
+      </c>
+      <c r="C120" t="str" xml:space="preserve">
+        <v xml:space="preserve">"일치/불일치 칸이 애니메이션 없이 바로 뿅 나온다"는 제보 원인 규명. 사용자 실제 크롬(limquiz.vercel.app, v0.13.78)에서 직접 측정한 결과 연출은 정상적으로 붙어 돌고 있었음 — prefers-reduced-motion=false, 행에 .reveal-row 부여됨, 각 td에 cell-flip-miss 340ms d80 / cell-flip-hit 560ms d400이 [running] 상태. 즉 "재생 안 됨"이 아니라 "너무 약해서 즉시 나타난 것처럼 읽힘"이 문제였다.
+근본 이유는 원근 부재. rotateX는 perspective가 없으면 직교 투영이라 사실상 scaleY(cos θ)로만 보인다. rotateX(-92deg)→0은 세로로 눌렸다 펴지는 정도의 변화라 v0.13.72의 scaleY(.4)→scaleY(1.06)→scaleY(1) 보다도 덜 극적으로 읽혔다. tr(.reveal-row)과 .db-board-item에 perspective:900px을 걸어 자식이 실제로 넘어가는 3D 뒤집기가 되게 함 (computed transform이 matrix에서 matrix3d로 바뀐 것 확인).
+동작도 전반적으로 키움. 회전 시작각 -92deg → -100deg, transform-origin을 center → center top으로 바꿔 위쪽 경첩을 축으로 넘어가게 하고, 모든 키프레임에 오버슈트 구간 추가(정답은 rotateX(14deg) scale(1.12) → rotateX(-5deg) scale(.98) → 정착, 오답은 rotateX(8deg) translateY(5px) → 정착, 덱 노랑은 translateX -9 → +9 → -4로 흔들림 강화). backface-visibility:hidden 추가.
+길이와 간격도 늘림. 오늘의 인격: 칸 간 지연 80ms → 110ms(9칸 전체 640ms → 880ms), duration plain .40→.52s / hit .56→.72s / miss .34→.50s. 덱 퀴즈: duration plain .40→.52s / green .56→.72s / yellow .48→.62s / red .34→.50s (칸 간 지연은 45ms 유지). 뒤따르는 타이밍도 재조정 — 덱 클리어 결과 지연 1100 → 1300ms(마지막 칸이 495+720=1215ms에 끝남), 오답 입력창 흔들림 900 → 1400ms.
+정답 공개(showEnd)도 anime에서 CSS로 이관. answer-reveal-in(.42s d.2s) / answer-card-in(.42s, 카드별 d.38~.66s) / answer-img-in(.48s d.5s) 키프레임 추가하고 animRun/animRiseIn/animPopIn 호출 제거. 이걸로 인격 두들에서 내용 표시가 anime 상태에 좌우되는 지점이 전부 사라졌고, v0.13.77 settle이 주던 최대 1.6초 지연도 없어졌다.
+(정정) v0.13.78 커밋 메시지와 주석에 "CSS 키프레임은 브라우저가 직접 돌리므로 재생 실패가 없다"고 적었는데 부정확했다. 렌더링이 멈춘 탭에서는 document.timeline.currentTime 자체가 0에 멈춰 CSS 애니메이션도 진행되지 않는다(프리뷰 탭에서 직접 확인: 1.6초 경과 후에도 animCurrent=0, playState=running, opacity=0). CSS의 실제 이점은 "재생이 보장된다"가 아니라 "라이브러리 로드/엔진 상태에 좌우되지 않는다"는 것. 주석을 이 내용으로 고쳤다.
+검증: 로컬에서 CSS 파싱 정상(키프레임 12종 모두 존재, 규칙 479개 — 편집 중 주석 블록을 깨뜨렸다가 즉시 복구), .reveal-row의 computed perspective=900px, 칸별 타이밍 cell-flip-miss 500ms d110/d220 확인, 애니메이션을 수동 시킹해 0→25→50→75→100% 중간 프레임이 matrix3d로 실제 3D 회전함을 확인. reduce 경로에서는 오늘의 인격 9칸·덱 12칸 모두 애니메이션 0개 + opacity 1로 정상 표시. 덱 결과 화면 정상 출력. 콘솔 오류는 프리뷰 서버 재시작으로 남은 stale 버퍼였고 현재 페이지 이미지 0개/깨짐 0개, 데이터 JSON 전부 200으로 확인.</v>
+      </c>
+      <c r="D120" t="str" xml:space="preserve">
+        <v xml:space="preserve">판정 칸 뒤집기 연출을 훨씬 뚜렷하게 다듬었습니다. 원근을 넣어 칸이 실제로 넘어가듯 회전하고, 칸이 넘어가는 간격과 시간도 늘려서 왼쪽부터 차례로 열리는 흐름이 확실히 보입니다.
+정답은 크게 튀어올랐다 자리를 잡고, 오답은 툭 떨어지며, 덱 퀴즈의 "순서 다름"은 좌우로 더 크게 흔들립니다.
+정답 공개 화면(결과 카드와 이미지)도 순서대로 나타나도록 정리했습니다.</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D119"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D120"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D120"/>
+  <dimension ref="A1:D121"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2388,10 +2388,31 @@
 정답 공개 화면(결과 카드와 이미지)도 순서대로 나타나도록 정리했습니다.</v>
       </c>
     </row>
+    <row r="121" xml:space="preserve">
+      <c r="A121" t="str">
+        <v>v0.13.80</v>
+      </c>
+      <c r="B121" t="str">
+        <v>2026-08-11</v>
+      </c>
+      <c r="C121" t="str" xml:space="preserve">
+        <v xml:space="preserve">"내 크롬에서만 이펙트가 안 나온다"의 최종 원인 규명: 사용자 PC의 Windows에서 애니메이션 효과가 꺼져 있었다. SystemParametersInfo(SPI_GETCLIENTAREAANIMATION=0x1042)를 P/Invoke로 직접 호출해 ClientAreaAnimation=False 확인. 크롬이 이걸 prefers-reduced-motion:reduce로 보고하고, v0.13.78에서 추가한 reduce 규칙이 의도대로 연출을 끈 것. 코드 결함이 아니라 설정이었다.
+(내 오진 2건 정정) ① 앞서 HKCU\Control Panel\Desktop\UserPreferencesMask의 byte2 비트 0x02를 읽고 "애니메이션 켜져 있음"이라고 판단했는데 비트 해석이 틀렸다. 이 값은 SPI_GETCLIENTAREAANIMATION과 대응하지 않는다 — 앞으로는 SystemParametersInfo를 직접 호출할 것. ② claude-in-chrome으로 사용자 크롬에 새 탭을 열어 측정했을 때 prefers-reduced-motion=false가 나와 "브라우저는 정상"이라고 판단했는데, CDP 자동화가 Emulation.setEmulatedMedia로 미디어 상태를 초기화하기 때문에 나온 값이었다. 자동화 탭의 미디어 쿼리 값은 사용자 실제 환경의 근거로 쓸 수 없다.
+대응: OS 설정을 기본값으로 존중하되 사이트에서 덮어쓸 수 있는 연출 토글 추가. 미디어 쿼리는 JS로 뒤집을 수 없으므로 @media (prefers-reduced-motion:reduce) 블록을 :root의 .reduce-motion 클래스 기반 규칙으로 전환하고, CSS와 JS(animEnabled/motionEnabled)가 같은 판단을 공유하도록 applyMotionPref()가 루트 클래스를 토글한다.
+motionPref()는 localStorage(limbus_motion_pref)에 on/off만 저장하고, 값이 없으면(null=auto) OS 설정을 그대로 따른다. 토글을 누른 적이 없는 사용자에게는 접근성 기본값이 유지된다. matchMedia change 리스너를 달아, 덮어쓰지 않은 상태라면 OS 설정 변경을 새로고침 없이 즉시 반영한다.
+UI: 홈 헤더와 게임 헤더 두 곳의 top-actions에 .motion-toggle-btn 추가(스타일은 changelog-btn을 재사용). 현재 상태를 라벨로 보여준다(✨ 연출 켜짐 / 💤 연출 꺼짐), title에는 시스템 설정을 따르는 중인지도 표기. 스타일 클래스를 빌려 쓰는 탓에 기존 document.querySelectorAll(".changelog-btn") 핸들러가 이 버튼까지 잡아 업데이트 기록 모달을 열어버리므로 선택자를 :not(.motion-toggle-btn)으로 좁혔다.
+검증: 프리뷰 탭이 마침 OS reduce=true라 사용자와 동일 조건이었음. (1) 저장값 없음 → "💤 연출 꺼짐", root에 reduce-motion, motionEnabled=false, animEnabled=false. (2) 토글 클릭 → pref=on, root 클래스 제거, motionEnabled=true, 실제 제출 시 cell-flip-plain 520ms d0 / cell-flip-miss 500ms d110·d220·d330이 붙고 perspective 900px 적용 확인. (3) 한 번 더 클릭 → pref=off, root에 reduce-motion, 애니메이션 0개 + 전 칸 opacity 1로 내용 정상 표시. (4) 토글이 업데이트 기록 모달을 열지 않음 확인. 버튼 2곳 모두 인식, 콘솔 에러 0건.</v>
+      </c>
+      <c r="D121" t="str" xml:space="preserve">
+        <v xml:space="preserve">헤더에 "✨ 연출 켜짐 / 💤 연출 꺼짐" 토글이 생겼습니다. 눌러서 연출을 직접 켜고 끌 수 있고, 선택은 이 브라우저에 저장됩니다.
+Windows나 macOS에서 "애니메이션 효과 끄기"(동작 줄이기)를 켜두신 경우, 지금까지는 림퀴즈의 연출도 함께 꺼졌습니다. 이제 이 토글로 림퀴즈에서만 연출을 다시 켤 수 있습니다.
+토글을 한 번도 누르지 않으면 기존처럼 시스템 설정을 그대로 따릅니다.</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D120"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D121"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D121"/>
+  <dimension ref="A1:D122"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2409,10 +2409,33 @@
 토글을 한 번도 누르지 않으면 기존처럼 시스템 설정을 그대로 따릅니다.</v>
       </c>
     </row>
+    <row r="122" xml:space="preserve">
+      <c r="A122" t="str">
+        <v>v0.13.81</v>
+      </c>
+      <c r="B122" t="str">
+        <v>2026-08-11</v>
+      </c>
+      <c r="C122" t="str" xml:space="preserve">
+        <v xml:space="preserve">연출 기본값을 "켜짐"으로 변경. motionOn()이 저장값 없을 때 OS의 prefers-reduced-motion을 따르던 것을 무조건 true 반환으로 바꿈(사용자 요청). 접근성 기본값을 포기하는 대신 토글은 그대로 남아 있어 언제든 끌 수 있고 그 선택은 저장된다. 저장값 없을 때 OS를 더 이상 참조하지 않으므로 matchMedia change 리스너는 무의미해져 제거.
+뒤집기 동작을 v0.13.72까지 쓰던 scaleY 기반으로 되돌림(3D 원근이 과하다는 피드백). .reveal-row의 perspective 제거, transform-origin을 center top → center로 복귀, backface-visibility 제거, 시작 rotateX(-100deg) → scaleY(.4). duration은 plain .52s → .28s, hit .72s → .34s, miss .50s → .38s로, 칸 간 지연은 110ms → 80ms(9칸 전체 880ms → 640ms)로 되돌림. 덱 퀴즈 12칸도 동일하게 scaleY 기반으로 환원(.db-board-item의 perspective 제거, duration .30~.42s).
+판정 구분 방식을 "움직임"에서 "색 플래시"로 전환. 성급·소속·키워드 칸은 폭이 좁아 translateY/scale 차이가 눈에 안 들어온다는 피드백이 핵심 — 같은 칸에 두 번째 애니메이션을 얹어 테두리를 번쩍이게 했다. cell-flash-hit는 inset 2px #7ee89a + 바깥 글로우, cell-flash-miss는 inset 2px #ff8f88만(글로우 없이 짧고 둔탁하게). animation-name/-duration에 값 두 개를 넘겨 등장 모션과 플래시가 같은 animation-delay를 공유하도록 했다.
+덱 퀴즈도 3색 플래시 추가: slot-flash-green(inset 3px + 글로우) / slot-flash-yellow(inset 3px #ffd98a) / slot-flash-red(inset 3px #ff8f88). 노랑은 좌우 흔들림 모션도 유지.
+길이가 줄어든 만큼 뒤따르는 타이밍 재조정: 덱 클리어 결과 지연 1300 → 950ms(마지막 칸이 495+360=855ms에 끝남), 오답 입력창 흔들림 1400 → 1050ms(마지막 칸 640+380=1020ms).
+검증: OS reduce=true인 프리뷰 창에서 (1) 저장값 없는 신규 상태의 기본 라벨이 "✨ 연출 켜짐", root 클래스 없음, motionEnabled/animEnabled 모두 true — 기본값 변경 확인. (2) computed perspective=none으로 원근 제거 확인, 칸별로 cell-reveal 280ms d0 / cell-reveal-miss 380ms d80 + cell-flash-miss 440ms d80처럼 모션+플래시 2개가 같은 지연을 공유함을 확인. (3) 한 행에 hit/miss가 섞인 케이스(plain,hit,miss,miss,miss,hit,miss,miss,hit)에서 플래시를 정점(42%)으로 시킹해 hit는 rgba(126,232,154) inset + 글로우, miss는 rgba(255,143,136) inset이 실제로 계산됨을 확인했고 종료 시 둘 다 box-shadow가 none으로 복귀. (4) 토글 OFF → 애니메이션 0개, 전 칸 opacity 1, box-shadow none으로 내용 정상 표시. 콘솔 에러 0건(프리뷰 서버 재시작 잔여 항목 제외).
+(미해결) 사용자가 말한 "정답/오답/빗나감" 세 가지 중 세 번째가 무엇인지 확인 필요. 현재 judgeCell은 hit/miss 두 상태뿐이고, 키워드도 keywordHitAtPosition이 위치 무관으로 판정해 "맞는 키워드지만 다른 칸" 같은 중간 상태가 없다. 세 번째 상태를 원한다면 게임 판정 로직 변경이 필요하므로 별도 확인 후 진행.</v>
+      </c>
+      <c r="D122" t="str" xml:space="preserve">
+        <v xml:space="preserve">연출이 이제 기본으로 켜져 있습니다. 시스템의 "동작 줄이기" 설정과 관계없이 바로 보이며, 원하지 않으시면 헤더의 토글로 끄실 수 있습니다.
+판정 칸이 나타나는 동작을 이전의 부드러운 방식으로 되돌렸습니다.
+대신 일치/불일치를 색으로 확실히 구분합니다. 일치한 칸은 초록 테두리가 밝게 번쩍이고, 불일치한 칸은 좌우로 짧게 흔들리며 빨간 테두리가 번쩍입니다.
+덱 퀴즈의 12칸도 같은 방식으로 정답(초록)·순서 다름(노랑)·오답(빨강)이 테두리 색으로 구분됩니다.</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D121"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D122"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D122"/>
+  <dimension ref="A1:D123"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2432,10 +2432,33 @@
 덱 퀴즈의 12칸도 같은 방식으로 정답(초록)·순서 다름(노랑)·오답(빨강)이 테두리 색으로 구분됩니다.</v>
       </c>
     </row>
+    <row r="123" xml:space="preserve">
+      <c r="A123" t="str">
+        <v>v0.13.82</v>
+      </c>
+      <c r="B123" t="str">
+        <v>2026-08-11</v>
+      </c>
+      <c r="C123" t="str" xml:space="preserve">
+        <v xml:space="preserve">인격 두들 키워드 판정을 2단계에서 3단계로 확장(게임 규칙 변경). 기존에는 keywordHitAtPosition이 정답 키워드 집합에 들어있기만 하면 위치와 무관하게 일치로 판정했다. 이제 judgeKeywordCell이 hit(같은 칸 같은 키워드) / moved(정답이 가진 키워드지만 다른 칸) / miss(정답에 없음)를 반환한다. 비키워드 칸(수감자·인격명·성급·소속)은 종전대로 hit/miss 2단계.
+빈칸 처리도 정리했다. 기존 코드는 !gv일 때 ansKeywords[idx]로 판단했는데, keywordsOf()가 빈 값을 filter(Boolean)로 걸러낸 배열이라 정답의 키워드1이 비어 있으면 인덱스가 밀려 엉뚱한 칸과 비교됐다. normalize(ans[field])로 같은 칸을 직접 보도록 바꿔 빈칸끼리 맞물리면 hit, 정답에만 값이 있으면 miss가 되게 했다.
+judgeCell이 반환하던 label을 JUDGE_LABEL 맵으로 분리(일치/순서 다름/불일치).
+후보 제외 로직 연동 확인: makeGuess의 excludedKeywords는 cls==="miss"일 때만 추가하므로, moved 키워드는 제외되지 않는다. 정답이 가진 키워드를 후보 필터에서 지워버리면 게임이 망가지는데 이 경계가 정확히 지켜지는지 실제 판으로 검증했다(정답 키워드 진동/제출 파열·진동 → 파열만 제외, 진동은 유지).
+UI: .moved 셀 배경(--slot-yellow 72%), 범례에 "순서 다름 (키워드만)" pill 추가, 상단 안내 문구를 "키워드는 순서와 상관없이 판정합니다"에서 "같은 칸이면 일치, 정답에 있지만 다른 칸이면 순서 다름"으로 교체. 연출은 cell-reveal-moved(좌우로 한 번 밀림) + cell-flash-moved(노란 테두리 #facc15 + 글로우)로 초록/빨강과 구분되게 했고, .reduce-motion 목록에도 td.moved를 추가.
+기록 포맷 변경 + 하위 호환: saveGameResultV2가 칸마다 불리언 대신 판정 문자열(hit/moved/miss)을 저장한다. 기존 기록은 불리언이므로 buildCardHTML에 cellCls() 정규화를 넣어 true→hit, false→miss로 읽고, 신규 기록의 moved는 🟨로 표시한다(구버전 기록에는 moved가 존재할 수 없음). 공유 카드 통계도 3분할로 확장 — 순서 다름이 있으면 세 번째 타일이 "일치율" 대신 "순서 다름 N칸"으로 바뀌고, 미터가 초록/노랑/회색 3구간이 된다.
+검증: (1) judgeCell 단위 케이스 8종 — 완전 일치/전부 순서 뒤바뀜/1칸만 자리 바뀜/정답에 없는 키워드/섞임/빈칸 vs 값 있음/빈칸끼리/비키워드 칸 — 모두 기대값과 일치. (2) 실제 판에서 한 행에 hit·moved·miss가 동시에 나오는 케이스를 만들어 판정 클래스(plain,miss,miss,miss,miss,hit,miss,moved,hit), 라벨("순서 다름"), 노란 배경, 플래시 정점의 box-shadow rgb(250,204,21) inset 확인. (3) 범례 3종 렌더 확인. (4) 공유 카드 — 구버전 불리언 기록은 ✅❌만 나오고 미터 2분할, 신버전 문자열 기록은 ✅🟨❌에 미터 3분할(초록 12.5% / 노랑 12.5% / 회색 75%)과 캡션 "일치 1칸 · 순서 다름 1칸 / 전체 8칸" 확인. 콘솔 에러 0건.</v>
+      </c>
+      <c r="D123" t="str" xml:space="preserve">
+        <v xml:space="preserve">인격 두들의 키워드 판정이 3단계로 바뀌었습니다. 같은 칸에 같은 키워드를 넣으면 초록(일치), 정답이 가진 키워드지만 다른 칸에 넣었으면 노랑(순서 다름), 정답에 아예 없는 키워드면 빨강(불일치)입니다.
+지금까지는 키워드를 순서와 상관없이 판정했기 때문에, 이제 키워드의 순서까지 맞히는 재미가 생겼습니다.
+노란 칸은 좌우로 한 번 밀리며 노란 테두리가 번쩍여서 초록·빨강과 확실히 구분됩니다. 후보 필터에서도 노란 키워드는 제외되지 않습니다(정답이 가진 키워드이기 때문입니다).
+공유 카드에도 순서 다름이 🟨로 표시되고, 이번 판의 일치·순서 다름·불일치 비율을 막대로 볼 수 있습니다. 이전에 저장한 기록은 그대로 열립니다.</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D122"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D123"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UpdateLog" sheetId="1" r:id="R7490b6adfbdd46fe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UpdateLog_백업" sheetId="2" r:id="R074a441141b447b2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UpdateLog" sheetId="1" r:id="R0d5e20f283294ee8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UpdateLog_백업" sheetId="2" r:id="R011a78f03d204949"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3308,6 +3308,26 @@
 모바일 상단 버튼이 화면 밖으로 잘리던 문제와 게임 화면 이동 시 이전 스크롤 위치가 남던 문제를 수정했습니다.</x:v>
       </x:c>
     </x:row>
+    <x:row r="126">
+      <x:c r="A126" t="str">
+        <x:v>v0.14.1</x:v>
+      </x:c>
+      <x:c r="B126" t="str">
+        <x:v>2026-08-27</x:v>
+      </x:c>
+      <x:c r="C126" t="str">
+        <x:v>홈 화면에 EGO 랜덤 플레이 진입 카드 추가
+오늘의 EGO와 랜덤 모드가 동일한 6칸 비교 판정 및 6회 제한 엔진을 공유하도록 구조 확장
+랜덤 모드 결과에 다음 랜덤 EGO 버튼을 추가하고 직전 정답 연속 출제 방지
+랜덤 진행·결과를 일일 localStorage 상태와 28일 활동 잔디에서 분리
+EGO 랜덤 플레이 기록과 스포일러 방지 판정 격자 공유 카드 지원</x:v>
+      </x:c>
+      <x:c r="D126" t="str">
+        <x:v>홈에 EGO 랜덤 플레이가 추가되었습니다. 무작위 EGO를 6번 안에 맞히고, 결과 화면에서 바로 다음 문제에 계속 도전할 수 있습니다.
+랜덤 플레이도 오늘의 EGO와 같은 비교 판정을 사용하며 같은 EGO가 연속으로 출제되지 않습니다.
+랜덤 플레이 기록은 저장되지만 오늘의 EGO 진행 상황과 최근 28일 일일 활동에는 영향을 주지 않습니다.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UpdateLog" sheetId="1" r:id="R0d5e20f283294ee8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UpdateLog_백업" sheetId="2" r:id="R011a78f03d204949"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UpdateLog" sheetId="1" r:id="Rfbbc704c0a8e456b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UpdateLog_백업" sheetId="2" r:id="Re8370cee185b4554"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3328,6 +3328,26 @@
 랜덤 플레이 기록은 저장되지만 오늘의 EGO 진행 상황과 최근 28일 일일 활동에는 영향을 주지 않습니다.</x:v>
       </x:c>
     </x:row>
+    <x:row r="127">
+      <x:c r="A127" t="str">
+        <x:v>v0.15.0</x:v>
+      </x:c>
+      <x:c r="B127" t="str">
+        <x:v>2026-08-28</x:v>
+      </x:c>
+      <x:c r="C127" t="str">
+        <x:v>• EGO 기프트에 날짜 시드 일일 답안, 진행 복원, 일일 결과 중복 방지와 랜덤 연속 출제를 구현.
+• GQ 비교 필드 6종(등급 방향, 죄악 속성, 이름 길이 방향, 효과 줄 수 방향, 키워드 수 방향, 공통 키워드) 및 스포일러 없는 공유 카드를 추가.
+• EGO/GQ 판정 셀 순차 3D 플립, 라운드 진입, 결과 패널 스태거를 추가하고 reduce-motion 설정을 유지.
+• 홈을 TODAY'S DIRECTIVES / TRAINING ARCHIVE / TACTICAL EXAMS로 재배치하고 일일 활동을 인격·EGO·기프트 3종 기준으로 확장.
+• 데스크톱·390px 모바일, 일일 오답/복원/정답, 랜덤 다음 문제, 콘솔 오류 없음까지 브라우저 검증.</x:v>
+      </x:c>
+      <x:c r="D127" t="str">
+        <x:v>• EGO 기프트 퀴즈를 오늘의 문제와 랜덤 훈련으로 분리했습니다.
+• 6번의 추측 동안 등급·속성·이름 길이·효과 줄·키워드 정보를 비교합니다.
+• EGO와 기프트 판정 애니메이션을 개선하고 홈 모드를 세 그룹으로 정리했습니다.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UpdateLog" sheetId="1" r:id="Rfbbc704c0a8e456b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UpdateLog_백업" sheetId="2" r:id="Re8370cee185b4554"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UpdateLog" sheetId="1" r:id="R1f18fd0096d24b16"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UpdateLog_백업" sheetId="2" r:id="R80ec4d8ff1a54ed4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3348,6 +3348,26 @@
 • EGO와 기프트 판정 애니메이션을 개선하고 홈 모드를 세 그룹으로 정리했습니다.</x:v>
       </x:c>
     </x:row>
+    <x:row r="128">
+      <x:c r="A128" t="str">
+        <x:v>v0.15.1</x:v>
+      </x:c>
+      <x:c r="B128" t="str">
+        <x:v>2026-08-28</x:v>
+      </x:c>
+      <x:c r="C128" t="str">
+        <x:v>EGO 기프트 원본 keywordName을 데이터 파이프라인에 추가하고, 범용은 키워드 없음으로 정규화.
+기프트 효과 문장에 등장하는 상태이상 개수 추정 대신 실제 단일 키워드의 정확 일치 판정으로 변경.
+모든 기프트에 붙는 내부 attrKeywordId와 실제 효과 조건을 분리하고, 공명·속성 스킬 조건에서 조건속성을 계산하도록 구현.
+속성 조건 없음 및 복수 속성 조건을 지원하고, 속성 묶음이 정확히 같을 때만 일치하도록 GQ 비교·결과 UI 수정.
+검증: 기프트 441개, 키워드 없음 109개, 속성 조건 없음 361개, 복수 속성 조건 7개.</x:v>
+      </x:c>
+      <x:c r="D128" t="str">
+        <x:v>EGO 기프트 퀴즈의 키워드와 속성 판정을 수정했습니다.
+키워드는 실제 기프트 분류가 정확히 같을 때만 일치합니다.
+속성은 공명·속성 스킬로 추가 효과가 발동하는 조건만 비교하며, 조건이 없거나 여러 개인 기프트도 정확하게 표시됩니다.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UpdateLog" sheetId="1" r:id="R1f18fd0096d24b16"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UpdateLog_백업" sheetId="2" r:id="R80ec4d8ff1a54ed4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UpdateLog" sheetId="1" r:id="R908da96c949f4fe6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UpdateLog_백업" sheetId="2" r:id="Rd0a6946882a34d45"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3368,6 +3368,27 @@
 속성은 공명·속성 스킬로 추가 효과가 발동하는 조건만 비교하며, 조건이 없거나 여러 개인 기프트도 정확하게 표시됩니다.</x:v>
       </x:c>
     </x:row>
+    <x:row r="129">
+      <x:c r="A129" t="str">
+        <x:v>v0.15.2</x:v>
+      </x:c>
+      <x:c r="B129" t="str">
+        <x:v>2026-08-28</x:v>
+      </x:c>
+      <x:c r="C129" t="str">
+        <x:v>EGO 기프트 퀴즈의 효과 줄 수 비교를 제거하고, 원본 enhanceYn 기반 강화 가능 여부 판정으로 교체.
+강화 가능 기프트 ID 116개를 별도 데이터로 생성하고 빌드 파이프라인에서 각 기프트의 강화가능 필드를 구성.
+효과 설명을 문장·구절 기준 최대 6개 기록으로 나눠 첫 단서를 즉시 공개하고, 오답마다 다음 단서가 열리도록 구현.
+정답 키워드와 조건속성은 효과 문장 안에서 가리고, 해당 비교 판정이 정확히 일치한 뒤에만 원문을 해금.
+기존 일일 진행 복원·랜덤 모드·결과 공유와 호환되며 공유 요약의 효과 줄 항목을 강화 가능 여부로 변경.
+데스크톱 및 390px 모바일 렌더, 가로 넘침 없음, HTML 스크립트 파싱과 기프트 441개 재빌드 검증.</x:v>
+      </x:c>
+      <x:c r="D129" t="str">
+        <x:v>EGO 기프트 퀴즈에서 효과 줄 수 비교를 없애고 강화 가능 여부로 바꿨습니다.
+효과 기록의 첫 단서는 처음부터 보이며, 오답을 낼 때마다 다음 효과 단서가 하나씩 열립니다.
+효과 문장 속 키워드와 조건 속성은 처음에는 가려지고, 관련 판정을 정확히 맞히면 해금됩니다.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UpdateLog" sheetId="1" r:id="R908da96c949f4fe6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UpdateLog_백업" sheetId="2" r:id="Rd0a6946882a34d45"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UpdateLog" sheetId="1" r:id="R590d369223504e40"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UpdateLog_백업" sheetId="2" r:id="Ra4479cc3498c4be5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3389,6 +3389,22 @@
 효과 문장 속 키워드와 조건 속성은 처음에는 가려지고, 관련 판정을 정확히 맞히면 해금됩니다.</x:v>
       </x:c>
     </x:row>
+    <x:row r="130">
+      <x:c r="A130" t="str">
+        <x:v>v0.15.3</x:v>
+      </x:c>
+      <x:c r="B130" t="str">
+        <x:v>2026-08-28</x:v>
+      </x:c>
+      <x:c r="C130" t="str">
+        <x:v>EGO 및 EGO 기프트 결과 화면의 DOM 순서를 조정해 정답 상세 패널(정보·효과·이미지)을 추측 판정 기록보다 먼저 렌더링.
+일일·랜덤 결과 렌더러에 공통 적용하고 결과 저장·공유·다음 문제 동작은 유지.
+데스크톱과 390px 모바일에서 정답 패널이 추측 기록보다 위에 위치하고 가로 넘침이 없음을 브라우저 검증.</x:v>
+      </x:c>
+      <x:c r="D130" t="str">
+        <x:v>EGO와 EGO 기프트 결과 화면에서 정답 정보와 이미지가 추측 기록보다 먼저 보이도록 상단으로 옮겼습니다.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
